--- a/large-report.xlsx
+++ b/large-report.xlsx
@@ -505,7 +505,7 @@
         <v>approved</v>
       </c>
       <c r="D2">
-        <v>4897.394334624022</v>
+        <v>1287.6561813911403</v>
       </c>
     </row>
     <row r="3">
@@ -519,7 +519,7 @@
         <v>pending</v>
       </c>
       <c r="D3">
-        <v>4850.918842882159</v>
+        <v>4102.765704556055</v>
       </c>
     </row>
     <row r="4">
@@ -533,7 +533,7 @@
         <v>approved</v>
       </c>
       <c r="D4">
-        <v>791.9157538809152</v>
+        <v>2855.208520321342</v>
       </c>
     </row>
     <row r="5">
@@ -547,7 +547,7 @@
         <v>pending</v>
       </c>
       <c r="D5">
-        <v>1038.5125269902794</v>
+        <v>3829.374621130286</v>
       </c>
     </row>
     <row r="6">
@@ -561,7 +561,7 @@
         <v>approved</v>
       </c>
       <c r="D6">
-        <v>608.6075364974608</v>
+        <v>502.3469392459645</v>
       </c>
     </row>
     <row r="7">
@@ -575,7 +575,7 @@
         <v>pending</v>
       </c>
       <c r="D7">
-        <v>174.34545545152002</v>
+        <v>2287.510430237776</v>
       </c>
     </row>
     <row r="8">
@@ -589,7 +589,7 @@
         <v>approved</v>
       </c>
       <c r="D8">
-        <v>4225.289112816463</v>
+        <v>1270.7419266501975</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
         <v>pending</v>
       </c>
       <c r="D9">
-        <v>510.73061912390915</v>
+        <v>4396.860499542496</v>
       </c>
     </row>
     <row r="10">
@@ -617,7 +617,7 @@
         <v>approved</v>
       </c>
       <c r="D10">
-        <v>18.432593228208116</v>
+        <v>3637.971343292461</v>
       </c>
     </row>
     <row r="11">
@@ -631,7 +631,7 @@
         <v>pending</v>
       </c>
       <c r="D11">
-        <v>305.07807919162076</v>
+        <v>3900.322683470958</v>
       </c>
     </row>
     <row r="12">
@@ -645,7 +645,7 @@
         <v>approved</v>
       </c>
       <c r="D12">
-        <v>252.1771274626905</v>
+        <v>2684.000703978461</v>
       </c>
     </row>
     <row r="13">
@@ -659,7 +659,7 @@
         <v>pending</v>
       </c>
       <c r="D13">
-        <v>3224.1449653922714</v>
+        <v>2213.510422855047</v>
       </c>
     </row>
     <row r="14">
@@ -673,7 +673,7 @@
         <v>approved</v>
       </c>
       <c r="D14">
-        <v>3914.6646149019425</v>
+        <v>3417.279922376338</v>
       </c>
     </row>
     <row r="15">
@@ -687,7 +687,7 @@
         <v>pending</v>
       </c>
       <c r="D15">
-        <v>4431.100226089985</v>
+        <v>3376.3512677703666</v>
       </c>
     </row>
     <row r="16">
@@ -701,7 +701,7 @@
         <v>approved</v>
       </c>
       <c r="D16">
-        <v>1537.4513809240552</v>
+        <v>1898.8695067005667</v>
       </c>
     </row>
     <row r="17">
@@ -715,7 +715,7 @@
         <v>pending</v>
       </c>
       <c r="D17">
-        <v>3019.5374575944666</v>
+        <v>845.0364475922001</v>
       </c>
     </row>
     <row r="18">
@@ -729,7 +729,7 @@
         <v>approved</v>
       </c>
       <c r="D18">
-        <v>73.44176975462413</v>
+        <v>213.57789769917866</v>
       </c>
     </row>
     <row r="19">
@@ -743,7 +743,7 @@
         <v>pending</v>
       </c>
       <c r="D19">
-        <v>1444.837936748825</v>
+        <v>4149.424410062552</v>
       </c>
     </row>
     <row r="20">
@@ -757,7 +757,7 @@
         <v>approved</v>
       </c>
       <c r="D20">
-        <v>1912.1004172231194</v>
+        <v>4291.91590551746</v>
       </c>
     </row>
     <row r="21">
@@ -771,7 +771,7 @@
         <v>pending</v>
       </c>
       <c r="D21">
-        <v>3608.810046816826</v>
+        <v>86.40709246592326</v>
       </c>
     </row>
     <row r="22">
@@ -785,7 +785,7 @@
         <v>approved</v>
       </c>
       <c r="D22">
-        <v>2953.9557129950576</v>
+        <v>2012.0058786427287</v>
       </c>
     </row>
     <row r="23">
@@ -799,7 +799,7 @@
         <v>pending</v>
       </c>
       <c r="D23">
-        <v>3.66877716665992</v>
+        <v>2241.9190817727817</v>
       </c>
     </row>
     <row r="24">
@@ -813,7 +813,7 @@
         <v>approved</v>
       </c>
       <c r="D24">
-        <v>2341.9373503426223</v>
+        <v>437.89506803554644</v>
       </c>
     </row>
     <row r="25">
@@ -827,7 +827,7 @@
         <v>pending</v>
       </c>
       <c r="D25">
-        <v>1064.4747348155515</v>
+        <v>3185.053336654277</v>
       </c>
     </row>
     <row r="26">
@@ -841,7 +841,7 @@
         <v>approved</v>
       </c>
       <c r="D26">
-        <v>1851.085498190974</v>
+        <v>2977.8737878902907</v>
       </c>
     </row>
     <row r="27">
@@ -855,7 +855,7 @@
         <v>pending</v>
       </c>
       <c r="D27">
-        <v>1872.8644951165618</v>
+        <v>86.42151726307002</v>
       </c>
     </row>
     <row r="28">
@@ -869,7 +869,7 @@
         <v>approved</v>
       </c>
       <c r="D28">
-        <v>188.5462005690908</v>
+        <v>3899.0660657390417</v>
       </c>
     </row>
     <row r="29">
@@ -883,7 +883,7 @@
         <v>pending</v>
       </c>
       <c r="D29">
-        <v>1759.9797536883432</v>
+        <v>3573.289190524986</v>
       </c>
     </row>
     <row r="30">
@@ -897,7 +897,7 @@
         <v>approved</v>
       </c>
       <c r="D30">
-        <v>3230.3726460504176</v>
+        <v>2882.9085146653133</v>
       </c>
     </row>
     <row r="31">
@@ -911,7 +911,7 @@
         <v>pending</v>
       </c>
       <c r="D31">
-        <v>1815.5036204290952</v>
+        <v>3790.7653476512037</v>
       </c>
     </row>
     <row r="32">
@@ -925,7 +925,7 @@
         <v>approved</v>
       </c>
       <c r="D32">
-        <v>1703.148294791005</v>
+        <v>984.6290291633941</v>
       </c>
     </row>
     <row r="33">
@@ -939,7 +939,7 @@
         <v>pending</v>
       </c>
       <c r="D33">
-        <v>2020.7258609446367</v>
+        <v>3288.4581948920845</v>
       </c>
     </row>
     <row r="34">
@@ -953,7 +953,7 @@
         <v>approved</v>
       </c>
       <c r="D34">
-        <v>4588.999065322029</v>
+        <v>2523.089114339976</v>
       </c>
     </row>
     <row r="35">
@@ -967,7 +967,7 @@
         <v>pending</v>
       </c>
       <c r="D35">
-        <v>4986.688762029538</v>
+        <v>3508.270147570626</v>
       </c>
     </row>
     <row r="36">
@@ -981,7 +981,7 @@
         <v>approved</v>
       </c>
       <c r="D36">
-        <v>3381.6264395752705</v>
+        <v>1339.1849168859194</v>
       </c>
     </row>
     <row r="37">
@@ -995,7 +995,7 @@
         <v>pending</v>
       </c>
       <c r="D37">
-        <v>1983.6212508170415</v>
+        <v>2502.1436602678414</v>
       </c>
     </row>
     <row r="38">
@@ -1009,7 +1009,7 @@
         <v>approved</v>
       </c>
       <c r="D38">
-        <v>3775.1907340710477</v>
+        <v>4405.083146473393</v>
       </c>
     </row>
     <row r="39">
@@ -1023,7 +1023,7 @@
         <v>pending</v>
       </c>
       <c r="D39">
-        <v>1717.2574698058363</v>
+        <v>123.38304840634584</v>
       </c>
     </row>
     <row r="40">
@@ -1037,7 +1037,7 @@
         <v>approved</v>
       </c>
       <c r="D40">
-        <v>470.8925232455263</v>
+        <v>2324.210743289977</v>
       </c>
     </row>
     <row r="41">
@@ -1051,7 +1051,7 @@
         <v>pending</v>
       </c>
       <c r="D41">
-        <v>275.68176837318606</v>
+        <v>2364.6360862691895</v>
       </c>
     </row>
     <row r="42">
@@ -1065,7 +1065,7 @@
         <v>approved</v>
       </c>
       <c r="D42">
-        <v>1699.0156494660657</v>
+        <v>3463.0136159856884</v>
       </c>
     </row>
     <row r="43">
@@ -1079,7 +1079,7 @@
         <v>pending</v>
       </c>
       <c r="D43">
-        <v>1186.7877192289689</v>
+        <v>1576.7846091053295</v>
       </c>
     </row>
     <row r="44">
@@ -1093,7 +1093,7 @@
         <v>approved</v>
       </c>
       <c r="D44">
-        <v>4948.5676453650185</v>
+        <v>3625.359741085463</v>
       </c>
     </row>
     <row r="45">
@@ -1107,7 +1107,7 @@
         <v>pending</v>
       </c>
       <c r="D45">
-        <v>4973.755720152758</v>
+        <v>4480.179576853627</v>
       </c>
     </row>
     <row r="46">
@@ -1121,7 +1121,7 @@
         <v>approved</v>
       </c>
       <c r="D46">
-        <v>2597.237543808348</v>
+        <v>3118.824198968222</v>
       </c>
     </row>
     <row r="47">
@@ -1135,7 +1135,7 @@
         <v>pending</v>
       </c>
       <c r="D47">
-        <v>3258.632338886096</v>
+        <v>3502.6955752719223</v>
       </c>
     </row>
     <row r="48">
@@ -1149,7 +1149,7 @@
         <v>approved</v>
       </c>
       <c r="D48">
-        <v>974.2451175109202</v>
+        <v>1615.2128537530718</v>
       </c>
     </row>
     <row r="49">
@@ -1163,7 +1163,7 @@
         <v>pending</v>
       </c>
       <c r="D49">
-        <v>3848.769856203683</v>
+        <v>1894.2001488151684</v>
       </c>
     </row>
     <row r="50">
@@ -1177,7 +1177,7 @@
         <v>approved</v>
       </c>
       <c r="D50">
-        <v>1180.0103087979364</v>
+        <v>4527.768393991472</v>
       </c>
     </row>
     <row r="51">
@@ -1191,7 +1191,7 @@
         <v>pending</v>
       </c>
       <c r="D51">
-        <v>4077.999688883475</v>
+        <v>1984.3488249258723</v>
       </c>
     </row>
     <row r="52">
@@ -1205,7 +1205,7 @@
         <v>approved</v>
       </c>
       <c r="D52">
-        <v>905.0171146351049</v>
+        <v>3448.8154642081236</v>
       </c>
     </row>
     <row r="53">
@@ -1219,7 +1219,7 @@
         <v>pending</v>
       </c>
       <c r="D53">
-        <v>4395.591690122723</v>
+        <v>4485.666865147785</v>
       </c>
     </row>
     <row r="54">
@@ -1233,7 +1233,7 @@
         <v>approved</v>
       </c>
       <c r="D54">
-        <v>441.70549552495663</v>
+        <v>4688.583997056238</v>
       </c>
     </row>
     <row r="55">
@@ -1247,7 +1247,7 @@
         <v>pending</v>
       </c>
       <c r="D55">
-        <v>1032.184817095958</v>
+        <v>1498.7911868253234</v>
       </c>
     </row>
     <row r="56">
@@ -1261,7 +1261,7 @@
         <v>approved</v>
       </c>
       <c r="D56">
-        <v>432.8019647463832</v>
+        <v>768.3113866820612</v>
       </c>
     </row>
     <row r="57">
@@ -1275,7 +1275,7 @@
         <v>pending</v>
       </c>
       <c r="D57">
-        <v>2256.140302509955</v>
+        <v>359.84484833671115</v>
       </c>
     </row>
     <row r="58">
@@ -1289,7 +1289,7 @@
         <v>approved</v>
       </c>
       <c r="D58">
-        <v>1268.372622686168</v>
+        <v>4206.079175665657</v>
       </c>
     </row>
     <row r="59">
@@ -1303,7 +1303,7 @@
         <v>pending</v>
       </c>
       <c r="D59">
-        <v>2826.906227998762</v>
+        <v>3418.3635799869903</v>
       </c>
     </row>
     <row r="60">
@@ -1317,7 +1317,7 @@
         <v>approved</v>
       </c>
       <c r="D60">
-        <v>3168.3233065605486</v>
+        <v>2310.497197475919</v>
       </c>
     </row>
     <row r="61">
@@ -1331,7 +1331,7 @@
         <v>pending</v>
       </c>
       <c r="D61">
-        <v>4387.406600085889</v>
+        <v>2790.7015934323044</v>
       </c>
     </row>
     <row r="62">
@@ -1345,7 +1345,7 @@
         <v>approved</v>
       </c>
       <c r="D62">
-        <v>2635.099749310389</v>
+        <v>58.353530064720886</v>
       </c>
     </row>
     <row r="63">
@@ -1359,7 +1359,7 @@
         <v>pending</v>
       </c>
       <c r="D63">
-        <v>3874.9764118846883</v>
+        <v>3965.4530750082927</v>
       </c>
     </row>
     <row r="64">
@@ -1373,7 +1373,7 @@
         <v>approved</v>
       </c>
       <c r="D64">
-        <v>2084.6177130391975</v>
+        <v>342.1746764770006</v>
       </c>
     </row>
     <row r="65">
@@ -1387,7 +1387,7 @@
         <v>pending</v>
       </c>
       <c r="D65">
-        <v>1699.6502779547939</v>
+        <v>1565.7219538966206</v>
       </c>
     </row>
     <row r="66">
@@ -1401,7 +1401,7 @@
         <v>approved</v>
       </c>
       <c r="D66">
-        <v>4536.953470569385</v>
+        <v>3366.402941637351</v>
       </c>
     </row>
     <row r="67">
@@ -1415,7 +1415,7 @@
         <v>pending</v>
       </c>
       <c r="D67">
-        <v>1667.8475825388994</v>
+        <v>4818.458582184092</v>
       </c>
     </row>
     <row r="68">
@@ -1429,7 +1429,7 @@
         <v>approved</v>
       </c>
       <c r="D68">
-        <v>4625.547123120283</v>
+        <v>1596.902634868107</v>
       </c>
     </row>
     <row r="69">
@@ -1443,7 +1443,7 @@
         <v>pending</v>
       </c>
       <c r="D69">
-        <v>1102.7094762723011</v>
+        <v>212.76872040242756</v>
       </c>
     </row>
     <row r="70">
@@ -1457,7 +1457,7 @@
         <v>approved</v>
       </c>
       <c r="D70">
-        <v>561.6389410669742</v>
+        <v>1447.6240082172242</v>
       </c>
     </row>
     <row r="71">
@@ -1471,7 +1471,7 @@
         <v>pending</v>
       </c>
       <c r="D71">
-        <v>3881.3232678305467</v>
+        <v>4321.412811361759</v>
       </c>
     </row>
     <row r="72">
@@ -1485,7 +1485,7 @@
         <v>approved</v>
       </c>
       <c r="D72">
-        <v>3059.582875268696</v>
+        <v>2477.700061901278</v>
       </c>
     </row>
     <row r="73">
@@ -1499,7 +1499,7 @@
         <v>pending</v>
       </c>
       <c r="D73">
-        <v>689.2159426051081</v>
+        <v>2554.4596494334637</v>
       </c>
     </row>
     <row r="74">
@@ -1513,7 +1513,7 @@
         <v>approved</v>
       </c>
       <c r="D74">
-        <v>4315.517775495623</v>
+        <v>1001.3418256750883</v>
       </c>
     </row>
     <row r="75">
@@ -1527,7 +1527,7 @@
         <v>pending</v>
       </c>
       <c r="D75">
-        <v>4883.310212126866</v>
+        <v>3813.8499548372074</v>
       </c>
     </row>
     <row r="76">
@@ -1541,7 +1541,7 @@
         <v>approved</v>
       </c>
       <c r="D76">
-        <v>3124.9652641169578</v>
+        <v>2690.366790043076</v>
       </c>
     </row>
     <row r="77">
@@ -1555,7 +1555,7 @@
         <v>pending</v>
       </c>
       <c r="D77">
-        <v>4162.497932334714</v>
+        <v>825.5978691037858</v>
       </c>
     </row>
     <row r="78">
@@ -1569,7 +1569,7 @@
         <v>approved</v>
       </c>
       <c r="D78">
-        <v>820.2239198707261</v>
+        <v>2589.2401659397824</v>
       </c>
     </row>
     <row r="79">
@@ -1583,7 +1583,7 @@
         <v>pending</v>
       </c>
       <c r="D79">
-        <v>2027.0118749651156</v>
+        <v>4104.578189900651</v>
       </c>
     </row>
     <row r="80">
@@ -1597,7 +1597,7 @@
         <v>approved</v>
       </c>
       <c r="D80">
-        <v>4419.046445908125</v>
+        <v>2979.2569909447143</v>
       </c>
     </row>
     <row r="81">
@@ -1611,7 +1611,7 @@
         <v>pending</v>
       </c>
       <c r="D81">
-        <v>204.28393033361414</v>
+        <v>388.6540822736118</v>
       </c>
     </row>
     <row r="82">
@@ -1625,7 +1625,7 @@
         <v>approved</v>
       </c>
       <c r="D82">
-        <v>1873.2408989695127</v>
+        <v>3136.1527275108892</v>
       </c>
     </row>
     <row r="83">
@@ -1639,7 +1639,7 @@
         <v>pending</v>
       </c>
       <c r="D83">
-        <v>2086.0518499376044</v>
+        <v>1086.353373059995</v>
       </c>
     </row>
     <row r="84">
@@ -1653,7 +1653,7 @@
         <v>approved</v>
       </c>
       <c r="D84">
-        <v>4111.350122029134</v>
+        <v>4231.632537318514</v>
       </c>
     </row>
     <row r="85">
@@ -1667,7 +1667,7 @@
         <v>pending</v>
       </c>
       <c r="D85">
-        <v>4871.737512590326</v>
+        <v>894.4962988240845</v>
       </c>
     </row>
     <row r="86">
@@ -1681,7 +1681,7 @@
         <v>approved</v>
       </c>
       <c r="D86">
-        <v>1099.8201827269804</v>
+        <v>4066.968051178318</v>
       </c>
     </row>
     <row r="87">
@@ -1695,7 +1695,7 @@
         <v>pending</v>
       </c>
       <c r="D87">
-        <v>2174.496460835704</v>
+        <v>1596.4684921665062</v>
       </c>
     </row>
     <row r="88">
@@ -1709,7 +1709,7 @@
         <v>approved</v>
       </c>
       <c r="D88">
-        <v>3026.546719336005</v>
+        <v>3598.1441888584586</v>
       </c>
     </row>
     <row r="89">
@@ -1723,7 +1723,7 @@
         <v>pending</v>
       </c>
       <c r="D89">
-        <v>210.38710930887495</v>
+        <v>2726.5276809152892</v>
       </c>
     </row>
     <row r="90">
@@ -1737,7 +1737,7 @@
         <v>approved</v>
       </c>
       <c r="D90">
-        <v>1821.8736664127944</v>
+        <v>1130.0325637713127</v>
       </c>
     </row>
     <row r="91">
@@ -1751,7 +1751,7 @@
         <v>pending</v>
       </c>
       <c r="D91">
-        <v>1520.9848302565908</v>
+        <v>3047.0008735146203</v>
       </c>
     </row>
     <row r="92">
@@ -1765,7 +1765,7 @@
         <v>approved</v>
       </c>
       <c r="D92">
-        <v>1743.4527209452488</v>
+        <v>3443.4932972809897</v>
       </c>
     </row>
     <row r="93">
@@ -1779,7 +1779,7 @@
         <v>pending</v>
       </c>
       <c r="D93">
-        <v>2387.0184614062896</v>
+        <v>4717.374364342381</v>
       </c>
     </row>
     <row r="94">
@@ -1793,7 +1793,7 @@
         <v>approved</v>
       </c>
       <c r="D94">
-        <v>1132.4632786234845</v>
+        <v>1287.1438269202883</v>
       </c>
     </row>
     <row r="95">
@@ -1807,7 +1807,7 @@
         <v>pending</v>
       </c>
       <c r="D95">
-        <v>4965.337957162335</v>
+        <v>4959.994735133612</v>
       </c>
     </row>
     <row r="96">
@@ -1821,7 +1821,7 @@
         <v>approved</v>
       </c>
       <c r="D96">
-        <v>2801.067402256336</v>
+        <v>1644.167248699001</v>
       </c>
     </row>
     <row r="97">
@@ -1835,7 +1835,7 @@
         <v>pending</v>
       </c>
       <c r="D97">
-        <v>2546.7240512793587</v>
+        <v>2524.015402662907</v>
       </c>
     </row>
     <row r="98">
@@ -1849,7 +1849,7 @@
         <v>approved</v>
       </c>
       <c r="D98">
-        <v>170.18736741099772</v>
+        <v>485.70800058331145</v>
       </c>
     </row>
     <row r="99">
@@ -1863,7 +1863,7 @@
         <v>pending</v>
       </c>
       <c r="D99">
-        <v>1440.184571386318</v>
+        <v>1064.7461921971192</v>
       </c>
     </row>
     <row r="100">
@@ -1877,7 +1877,7 @@
         <v>approved</v>
       </c>
       <c r="D100">
-        <v>1982.8761475191682</v>
+        <v>154.52215845356275</v>
       </c>
     </row>
     <row r="101">
@@ -1891,7 +1891,7 @@
         <v>pending</v>
       </c>
       <c r="D101">
-        <v>4432.8396367128535</v>
+        <v>2519.3474851313213</v>
       </c>
     </row>
     <row r="102">
@@ -1905,7 +1905,7 @@
         <v>approved</v>
       </c>
       <c r="D102">
-        <v>1469.858168148469</v>
+        <v>1494.066592818265</v>
       </c>
     </row>
     <row r="103">
@@ -1919,7 +1919,7 @@
         <v>pending</v>
       </c>
       <c r="D103">
-        <v>19.72714603999726</v>
+        <v>4979.950307131373</v>
       </c>
     </row>
     <row r="104">
@@ -1933,7 +1933,7 @@
         <v>approved</v>
       </c>
       <c r="D104">
-        <v>3012.530693075429</v>
+        <v>2523.0516205948175</v>
       </c>
     </row>
     <row r="105">
@@ -1947,7 +1947,7 @@
         <v>pending</v>
       </c>
       <c r="D105">
-        <v>3672.797771169591</v>
+        <v>3900.877666735408</v>
       </c>
     </row>
     <row r="106">
@@ -1961,7 +1961,7 @@
         <v>approved</v>
       </c>
       <c r="D106">
-        <v>1402.9409780549463</v>
+        <v>3646.759977867673</v>
       </c>
     </row>
     <row r="107">
@@ -1975,7 +1975,7 @@
         <v>pending</v>
       </c>
       <c r="D107">
-        <v>3880.911612460772</v>
+        <v>1032.8538947097843</v>
       </c>
     </row>
     <row r="108">
@@ -1989,7 +1989,7 @@
         <v>approved</v>
       </c>
       <c r="D108">
-        <v>2926.1019992718816</v>
+        <v>3503.863953978985</v>
       </c>
     </row>
     <row r="109">
@@ -2003,7 +2003,7 @@
         <v>pending</v>
       </c>
       <c r="D109">
-        <v>1735.5659703441163</v>
+        <v>813.7534143889391</v>
       </c>
     </row>
     <row r="110">
@@ -2017,7 +2017,7 @@
         <v>approved</v>
       </c>
       <c r="D110">
-        <v>4326.189198884147</v>
+        <v>551.557207866743</v>
       </c>
     </row>
     <row r="111">
@@ -2031,7 +2031,7 @@
         <v>pending</v>
       </c>
       <c r="D111">
-        <v>1985.7882730144083</v>
+        <v>1967.0028009994721</v>
       </c>
     </row>
     <row r="112">
@@ -2045,7 +2045,7 @@
         <v>approved</v>
       </c>
       <c r="D112">
-        <v>730.1125612662962</v>
+        <v>343.2264390923567</v>
       </c>
     </row>
     <row r="113">
@@ -2059,7 +2059,7 @@
         <v>pending</v>
       </c>
       <c r="D113">
-        <v>2328.3083549915405</v>
+        <v>2755.8249054552275</v>
       </c>
     </row>
     <row r="114">
@@ -2073,7 +2073,7 @@
         <v>approved</v>
       </c>
       <c r="D114">
-        <v>2630.9584567249467</v>
+        <v>327.7871298226509</v>
       </c>
     </row>
     <row r="115">
@@ -2087,7 +2087,7 @@
         <v>pending</v>
       </c>
       <c r="D115">
-        <v>4587.875072390341</v>
+        <v>133.89206269292185</v>
       </c>
     </row>
     <row r="116">
@@ -2101,7 +2101,7 @@
         <v>approved</v>
       </c>
       <c r="D116">
-        <v>2294.542251997801</v>
+        <v>4060.993106091664</v>
       </c>
     </row>
     <row r="117">
@@ -2115,7 +2115,7 @@
         <v>pending</v>
       </c>
       <c r="D117">
-        <v>3426.8559164141157</v>
+        <v>1874.4835788636394</v>
       </c>
     </row>
     <row r="118">
@@ -2129,7 +2129,7 @@
         <v>approved</v>
       </c>
       <c r="D118">
-        <v>1817.1301647672933</v>
+        <v>4037.742835196675</v>
       </c>
     </row>
     <row r="119">
@@ -2143,7 +2143,7 @@
         <v>pending</v>
       </c>
       <c r="D119">
-        <v>744.7945055839933</v>
+        <v>3876.3894681545585</v>
       </c>
     </row>
     <row r="120">
@@ -2157,7 +2157,7 @@
         <v>approved</v>
       </c>
       <c r="D120">
-        <v>3802.0209816995375</v>
+        <v>1519.9829756022887</v>
       </c>
     </row>
     <row r="121">
@@ -2171,7 +2171,7 @@
         <v>pending</v>
       </c>
       <c r="D121">
-        <v>886.6457872403977</v>
+        <v>54.09272721752734</v>
       </c>
     </row>
     <row r="122">
@@ -2185,7 +2185,7 @@
         <v>approved</v>
       </c>
       <c r="D122">
-        <v>2335.105296828538</v>
+        <v>1160.2958769039506</v>
       </c>
     </row>
     <row r="123">
@@ -2199,7 +2199,7 @@
         <v>pending</v>
       </c>
       <c r="D123">
-        <v>1366.5837773076794</v>
+        <v>1539.0720762825006</v>
       </c>
     </row>
     <row r="124">
@@ -2213,7 +2213,7 @@
         <v>approved</v>
       </c>
       <c r="D124">
-        <v>1085.4244369362987</v>
+        <v>3680.376880324847</v>
       </c>
     </row>
     <row r="125">
@@ -2227,7 +2227,7 @@
         <v>pending</v>
       </c>
       <c r="D125">
-        <v>3535.038695160697</v>
+        <v>945.4630380391471</v>
       </c>
     </row>
     <row r="126">
@@ -2241,7 +2241,7 @@
         <v>approved</v>
       </c>
       <c r="D126">
-        <v>1023.6339061900934</v>
+        <v>732.5450552791068</v>
       </c>
     </row>
     <row r="127">
@@ -2255,7 +2255,7 @@
         <v>pending</v>
       </c>
       <c r="D127">
-        <v>440.38211485604717</v>
+        <v>4078.330856634396</v>
       </c>
     </row>
     <row r="128">
@@ -2269,7 +2269,7 @@
         <v>approved</v>
       </c>
       <c r="D128">
-        <v>3285.1222409773627</v>
+        <v>525.0721789764712</v>
       </c>
     </row>
     <row r="129">
@@ -2283,7 +2283,7 @@
         <v>pending</v>
       </c>
       <c r="D129">
-        <v>1338.33824245296</v>
+        <v>1425.543732054857</v>
       </c>
     </row>
     <row r="130">
@@ -2297,7 +2297,7 @@
         <v>approved</v>
       </c>
       <c r="D130">
-        <v>1327.8631477076863</v>
+        <v>3064.403419805769</v>
       </c>
     </row>
     <row r="131">
@@ -2311,7 +2311,7 @@
         <v>pending</v>
       </c>
       <c r="D131">
-        <v>4380.858482814133</v>
+        <v>150.30910183750245</v>
       </c>
     </row>
     <row r="132">
@@ -2325,7 +2325,7 @@
         <v>approved</v>
       </c>
       <c r="D132">
-        <v>93.45570456361752</v>
+        <v>4897.110690187507</v>
       </c>
     </row>
     <row r="133">
@@ -2339,7 +2339,7 @@
         <v>pending</v>
       </c>
       <c r="D133">
-        <v>3036.926686707496</v>
+        <v>2085.781450768669</v>
       </c>
     </row>
     <row r="134">
@@ -2353,7 +2353,7 @@
         <v>approved</v>
       </c>
       <c r="D134">
-        <v>3715.661842223029</v>
+        <v>2329.0085217663404</v>
       </c>
     </row>
     <row r="135">
@@ -2367,7 +2367,7 @@
         <v>pending</v>
       </c>
       <c r="D135">
-        <v>2698.1202871380606</v>
+        <v>3767.7770040776336</v>
       </c>
     </row>
     <row r="136">
@@ -2381,7 +2381,7 @@
         <v>approved</v>
       </c>
       <c r="D136">
-        <v>3446.8695623577696</v>
+        <v>1561.296563956075</v>
       </c>
     </row>
     <row r="137">
@@ -2395,7 +2395,7 @@
         <v>pending</v>
       </c>
       <c r="D137">
-        <v>2048.878266296652</v>
+        <v>3391.9430587013567</v>
       </c>
     </row>
     <row r="138">
@@ -2409,7 +2409,7 @@
         <v>approved</v>
       </c>
       <c r="D138">
-        <v>10.554697582644268</v>
+        <v>1151.3053454909184</v>
       </c>
     </row>
     <row r="139">
@@ -2423,7 +2423,7 @@
         <v>pending</v>
       </c>
       <c r="D139">
-        <v>766.3931309085725</v>
+        <v>389.6156062005696</v>
       </c>
     </row>
     <row r="140">
@@ -2437,7 +2437,7 @@
         <v>approved</v>
       </c>
       <c r="D140">
-        <v>2229.157885494868</v>
+        <v>4321.223470029232</v>
       </c>
     </row>
     <row r="141">
@@ -2451,7 +2451,7 @@
         <v>pending</v>
       </c>
       <c r="D141">
-        <v>2173.3613180710454</v>
+        <v>2366.9306744916994</v>
       </c>
     </row>
     <row r="142">
@@ -2465,7 +2465,7 @@
         <v>approved</v>
       </c>
       <c r="D142">
-        <v>1261.5909379681789</v>
+        <v>227.43206402409234</v>
       </c>
     </row>
     <row r="143">
@@ -2479,7 +2479,7 @@
         <v>pending</v>
       </c>
       <c r="D143">
-        <v>2718.6135316172677</v>
+        <v>1520.8144470539164</v>
       </c>
     </row>
     <row r="144">
@@ -2493,7 +2493,7 @@
         <v>approved</v>
       </c>
       <c r="D144">
-        <v>2271.9363867176935</v>
+        <v>140.8685774290508</v>
       </c>
     </row>
     <row r="145">
@@ -2507,7 +2507,7 @@
         <v>pending</v>
       </c>
       <c r="D145">
-        <v>2376.2497463970276</v>
+        <v>119.46517266569367</v>
       </c>
     </row>
     <row r="146">
@@ -2521,7 +2521,7 @@
         <v>approved</v>
       </c>
       <c r="D146">
-        <v>1073.8427820646334</v>
+        <v>3844.510777830514</v>
       </c>
     </row>
     <row r="147">
@@ -2535,7 +2535,7 @@
         <v>pending</v>
       </c>
       <c r="D147">
-        <v>4184.882997277267</v>
+        <v>1877.5776841604497</v>
       </c>
     </row>
     <row r="148">
@@ -2549,7 +2549,7 @@
         <v>approved</v>
       </c>
       <c r="D148">
-        <v>3159.5952843239293</v>
+        <v>4154.4344654755</v>
       </c>
     </row>
     <row r="149">
@@ -2563,7 +2563,7 @@
         <v>pending</v>
       </c>
       <c r="D149">
-        <v>1630.6466725327361</v>
+        <v>3555.5398525298133</v>
       </c>
     </row>
     <row r="150">
@@ -2577,7 +2577,7 @@
         <v>approved</v>
       </c>
       <c r="D150">
-        <v>4705.625777911901</v>
+        <v>1377.9819854551733</v>
       </c>
     </row>
     <row r="151">
@@ -2591,7 +2591,7 @@
         <v>pending</v>
       </c>
       <c r="D151">
-        <v>4184.046065582383</v>
+        <v>3867.7306252176336</v>
       </c>
     </row>
     <row r="152">
@@ -2605,7 +2605,7 @@
         <v>approved</v>
       </c>
       <c r="D152">
-        <v>3091.8757445165124</v>
+        <v>3261.0137166636864</v>
       </c>
     </row>
     <row r="153">
@@ -2619,7 +2619,7 @@
         <v>pending</v>
       </c>
       <c r="D153">
-        <v>4499.4102003191065</v>
+        <v>1827.5828598741139</v>
       </c>
     </row>
     <row r="154">
@@ -2633,7 +2633,7 @@
         <v>approved</v>
       </c>
       <c r="D154">
-        <v>1953.437393743589</v>
+        <v>3627.841628277546</v>
       </c>
     </row>
     <row r="155">
@@ -2647,7 +2647,7 @@
         <v>pending</v>
       </c>
       <c r="D155">
-        <v>1695.3103723628249</v>
+        <v>2175.9382152652697</v>
       </c>
     </row>
     <row r="156">
@@ -2661,7 +2661,7 @@
         <v>approved</v>
       </c>
       <c r="D156">
-        <v>4617.350619812915</v>
+        <v>4478.0946978567645</v>
       </c>
     </row>
     <row r="157">
@@ -2675,7 +2675,7 @@
         <v>pending</v>
       </c>
       <c r="D157">
-        <v>1921.1309239536256</v>
+        <v>1907.2466612289506</v>
       </c>
     </row>
     <row r="158">
@@ -2689,7 +2689,7 @@
         <v>approved</v>
       </c>
       <c r="D158">
-        <v>1733.953261165717</v>
+        <v>1927.6713727229856</v>
       </c>
     </row>
     <row r="159">
@@ -2703,7 +2703,7 @@
         <v>pending</v>
       </c>
       <c r="D159">
-        <v>295.1331192856499</v>
+        <v>4242.2257972727175</v>
       </c>
     </row>
     <row r="160">
@@ -2717,7 +2717,7 @@
         <v>approved</v>
       </c>
       <c r="D160">
-        <v>2273.1769916735943</v>
+        <v>3062.886091215011</v>
       </c>
     </row>
     <row r="161">
@@ -2731,7 +2731,7 @@
         <v>pending</v>
       </c>
       <c r="D161">
-        <v>564.1021756976006</v>
+        <v>2306.543709656569</v>
       </c>
     </row>
     <row r="162">
@@ -2745,7 +2745,7 @@
         <v>approved</v>
       </c>
       <c r="D162">
-        <v>2705.5602567755354</v>
+        <v>1342.818546194523</v>
       </c>
     </row>
     <row r="163">
@@ -2759,7 +2759,7 @@
         <v>pending</v>
       </c>
       <c r="D163">
-        <v>4633.702326910157</v>
+        <v>324.94851035096417</v>
       </c>
     </row>
     <row r="164">
@@ -2773,7 +2773,7 @@
         <v>approved</v>
       </c>
       <c r="D164">
-        <v>2579.598360861761</v>
+        <v>3776.522626214529</v>
       </c>
     </row>
     <row r="165">
@@ -2787,7 +2787,7 @@
         <v>pending</v>
       </c>
       <c r="D165">
-        <v>2168.337121051548</v>
+        <v>1965.6543185996888</v>
       </c>
     </row>
     <row r="166">
@@ -2801,7 +2801,7 @@
         <v>approved</v>
       </c>
       <c r="D166">
-        <v>3367.24297944609</v>
+        <v>3895.381322493079</v>
       </c>
     </row>
     <row r="167">
@@ -2815,7 +2815,7 @@
         <v>pending</v>
       </c>
       <c r="D167">
-        <v>4460.681171627787</v>
+        <v>4712.950183533977</v>
       </c>
     </row>
     <row r="168">
@@ -2829,7 +2829,7 @@
         <v>approved</v>
       </c>
       <c r="D168">
-        <v>920.5439108136982</v>
+        <v>3978.582614873528</v>
       </c>
     </row>
     <row r="169">
@@ -2843,7 +2843,7 @@
         <v>pending</v>
       </c>
       <c r="D169">
-        <v>3624.1569807692917</v>
+        <v>1117.8577033788195</v>
       </c>
     </row>
     <row r="170">
@@ -2857,7 +2857,7 @@
         <v>approved</v>
       </c>
       <c r="D170">
-        <v>1463.1413581688303</v>
+        <v>3069.0922953056943</v>
       </c>
     </row>
     <row r="171">
@@ -2871,7 +2871,7 @@
         <v>pending</v>
       </c>
       <c r="D171">
-        <v>1959.7706738591758</v>
+        <v>4177.285698170794</v>
       </c>
     </row>
     <row r="172">
@@ -2885,7 +2885,7 @@
         <v>approved</v>
       </c>
       <c r="D172">
-        <v>4926.486427924712</v>
+        <v>247.54599769234443</v>
       </c>
     </row>
     <row r="173">
@@ -2899,7 +2899,7 @@
         <v>pending</v>
       </c>
       <c r="D173">
-        <v>816.9138062162796</v>
+        <v>832.8836874767076</v>
       </c>
     </row>
     <row r="174">
@@ -2913,7 +2913,7 @@
         <v>approved</v>
       </c>
       <c r="D174">
-        <v>3461.586471720348</v>
+        <v>2854.5939268766297</v>
       </c>
     </row>
     <row r="175">
@@ -2927,7 +2927,7 @@
         <v>pending</v>
       </c>
       <c r="D175">
-        <v>36.998747495724515</v>
+        <v>1232.751939526574</v>
       </c>
     </row>
     <row r="176">
@@ -2941,7 +2941,7 @@
         <v>approved</v>
       </c>
       <c r="D176">
-        <v>3671.054866084642</v>
+        <v>2280.0122795759125</v>
       </c>
     </row>
     <row r="177">
@@ -2955,7 +2955,7 @@
         <v>pending</v>
       </c>
       <c r="D177">
-        <v>359.0683090766089</v>
+        <v>3045.8866439795697</v>
       </c>
     </row>
     <row r="178">
@@ -2969,7 +2969,7 @@
         <v>approved</v>
       </c>
       <c r="D178">
-        <v>668.2810458027644</v>
+        <v>1647.351223726008</v>
       </c>
     </row>
     <row r="179">
@@ -2983,7 +2983,7 @@
         <v>pending</v>
       </c>
       <c r="D179">
-        <v>4447.094099357462</v>
+        <v>139.12784100137188</v>
       </c>
     </row>
     <row r="180">
@@ -2997,7 +2997,7 @@
         <v>approved</v>
       </c>
       <c r="D180">
-        <v>21.26082910265059</v>
+        <v>1564.0544968841841</v>
       </c>
     </row>
     <row r="181">
@@ -3011,7 +3011,7 @@
         <v>pending</v>
       </c>
       <c r="D181">
-        <v>1622.1676432926579</v>
+        <v>2241.5877268864037</v>
       </c>
     </row>
     <row r="182">
@@ -3025,7 +3025,7 @@
         <v>approved</v>
       </c>
       <c r="D182">
-        <v>787.0975004717106</v>
+        <v>90.69749725581167</v>
       </c>
     </row>
     <row r="183">
@@ -3039,7 +3039,7 @@
         <v>pending</v>
       </c>
       <c r="D183">
-        <v>1011.2662811691797</v>
+        <v>588.3952422320205</v>
       </c>
     </row>
     <row r="184">
@@ -3053,7 +3053,7 @@
         <v>approved</v>
       </c>
       <c r="D184">
-        <v>2343.780630126894</v>
+        <v>4408.892978033668</v>
       </c>
     </row>
     <row r="185">
@@ -3067,7 +3067,7 @@
         <v>pending</v>
       </c>
       <c r="D185">
-        <v>2406.7873903244595</v>
+        <v>3605.994151985511</v>
       </c>
     </row>
     <row r="186">
@@ -3081,7 +3081,7 @@
         <v>approved</v>
       </c>
       <c r="D186">
-        <v>2629.9777757775246</v>
+        <v>1396.9088313205402</v>
       </c>
     </row>
     <row r="187">
@@ -3095,7 +3095,7 @@
         <v>pending</v>
       </c>
       <c r="D187">
-        <v>910.6396581231779</v>
+        <v>3542.0109575743063</v>
       </c>
     </row>
     <row r="188">
@@ -3109,7 +3109,7 @@
         <v>approved</v>
       </c>
       <c r="D188">
-        <v>1780.8711228112395</v>
+        <v>4974.595933301484</v>
       </c>
     </row>
     <row r="189">
@@ -3123,7 +3123,7 @@
         <v>pending</v>
       </c>
       <c r="D189">
-        <v>4723.578999774371</v>
+        <v>2432.839403384618</v>
       </c>
     </row>
     <row r="190">
@@ -3137,7 +3137,7 @@
         <v>approved</v>
       </c>
       <c r="D190">
-        <v>2384.458670595394</v>
+        <v>4290.81937658629</v>
       </c>
     </row>
     <row r="191">
@@ -3151,7 +3151,7 @@
         <v>pending</v>
       </c>
       <c r="D191">
-        <v>4984.037552239532</v>
+        <v>4763.2457801918035</v>
       </c>
     </row>
     <row r="192">
@@ -3165,7 +3165,7 @@
         <v>approved</v>
       </c>
       <c r="D192">
-        <v>2789.771584621689</v>
+        <v>4471.47178609262</v>
       </c>
     </row>
     <row r="193">
@@ -3179,7 +3179,7 @@
         <v>pending</v>
       </c>
       <c r="D193">
-        <v>4876.620490887873</v>
+        <v>4238.530877227301</v>
       </c>
     </row>
     <row r="194">
@@ -3193,7 +3193,7 @@
         <v>approved</v>
       </c>
       <c r="D194">
-        <v>2778.850182057988</v>
+        <v>369.7402382147375</v>
       </c>
     </row>
     <row r="195">
@@ -3207,7 +3207,7 @@
         <v>pending</v>
       </c>
       <c r="D195">
-        <v>2357.7863335949855</v>
+        <v>945.5400600928865</v>
       </c>
     </row>
     <row r="196">
@@ -3221,7 +3221,7 @@
         <v>approved</v>
       </c>
       <c r="D196">
-        <v>2315.354050322168</v>
+        <v>963.9943108455906</v>
       </c>
     </row>
     <row r="197">
@@ -3235,7 +3235,7 @@
         <v>pending</v>
       </c>
       <c r="D197">
-        <v>591.7036916766782</v>
+        <v>4300.206222338154</v>
       </c>
     </row>
     <row r="198">
@@ -3249,7 +3249,7 @@
         <v>approved</v>
       </c>
       <c r="D198">
-        <v>3225.180390013337</v>
+        <v>3618.188100379446</v>
       </c>
     </row>
     <row r="199">
@@ -3263,7 +3263,7 @@
         <v>pending</v>
       </c>
       <c r="D199">
-        <v>1887.1437664162572</v>
+        <v>1040.1071984523169</v>
       </c>
     </row>
     <row r="200">
@@ -3277,7 +3277,7 @@
         <v>approved</v>
       </c>
       <c r="D200">
-        <v>3926.6056118192314</v>
+        <v>915.1110864556689</v>
       </c>
     </row>
     <row r="201">
@@ -3291,7 +3291,7 @@
         <v>pending</v>
       </c>
       <c r="D201">
-        <v>2837.054861778694</v>
+        <v>4499.353761271431</v>
       </c>
     </row>
     <row r="202">
@@ -3305,7 +3305,7 @@
         <v>approved</v>
       </c>
       <c r="D202">
-        <v>639.4675210195045</v>
+        <v>3685.8918987920983</v>
       </c>
     </row>
     <row r="203">
@@ -3319,7 +3319,7 @@
         <v>pending</v>
       </c>
       <c r="D203">
-        <v>2912.7485418380493</v>
+        <v>1039.192937010418</v>
       </c>
     </row>
     <row r="204">
@@ -3333,7 +3333,7 @@
         <v>approved</v>
       </c>
       <c r="D204">
-        <v>171.08305676100443</v>
+        <v>1397.7139025795316</v>
       </c>
     </row>
     <row r="205">
@@ -3347,7 +3347,7 @@
         <v>pending</v>
       </c>
       <c r="D205">
-        <v>1759.534943751514</v>
+        <v>1581.0651386673503</v>
       </c>
     </row>
     <row r="206">
@@ -3361,7 +3361,7 @@
         <v>approved</v>
       </c>
       <c r="D206">
-        <v>836.9657212332793</v>
+        <v>2477.981694356922</v>
       </c>
     </row>
     <row r="207">
@@ -3375,7 +3375,7 @@
         <v>pending</v>
       </c>
       <c r="D207">
-        <v>2107.6566612972815</v>
+        <v>1076.8175708491744</v>
       </c>
     </row>
     <row r="208">
@@ -3389,7 +3389,7 @@
         <v>approved</v>
       </c>
       <c r="D208">
-        <v>1462.7367533784618</v>
+        <v>2547.208544779931</v>
       </c>
     </row>
     <row r="209">
@@ -3403,7 +3403,7 @@
         <v>pending</v>
       </c>
       <c r="D209">
-        <v>1766.4721503072744</v>
+        <v>1672.649311178165</v>
       </c>
     </row>
     <row r="210">
@@ -3417,7 +3417,7 @@
         <v>approved</v>
       </c>
       <c r="D210">
-        <v>4656.506774446471</v>
+        <v>3320.3056413092236</v>
       </c>
     </row>
     <row r="211">
@@ -3431,7 +3431,7 @@
         <v>pending</v>
       </c>
       <c r="D211">
-        <v>127.73972603406291</v>
+        <v>171.68638433285867</v>
       </c>
     </row>
     <row r="212">
@@ -3445,7 +3445,7 @@
         <v>approved</v>
       </c>
       <c r="D212">
-        <v>4805.408788184195</v>
+        <v>867.519707818849</v>
       </c>
     </row>
     <row r="213">
@@ -3459,7 +3459,7 @@
         <v>pending</v>
       </c>
       <c r="D213">
-        <v>4942.2067718954995</v>
+        <v>1787.5584940100819</v>
       </c>
     </row>
     <row r="214">
@@ -3473,7 +3473,7 @@
         <v>approved</v>
       </c>
       <c r="D214">
-        <v>4135.634807731498</v>
+        <v>2678.7894935883814</v>
       </c>
     </row>
     <row r="215">
@@ -3487,7 +3487,7 @@
         <v>pending</v>
       </c>
       <c r="D215">
-        <v>697.2289388638886</v>
+        <v>4967.632398376272</v>
       </c>
     </row>
     <row r="216">
@@ -3501,7 +3501,7 @@
         <v>approved</v>
       </c>
       <c r="D216">
-        <v>2161.481153804082</v>
+        <v>4984.528143592229</v>
       </c>
     </row>
     <row r="217">
@@ -3515,7 +3515,7 @@
         <v>pending</v>
       </c>
       <c r="D217">
-        <v>4342.211827846134</v>
+        <v>3833.572727504101</v>
       </c>
     </row>
     <row r="218">
@@ -3529,7 +3529,7 @@
         <v>approved</v>
       </c>
       <c r="D218">
-        <v>1508.900517891606</v>
+        <v>843.7222620759566</v>
       </c>
     </row>
     <row r="219">
@@ -3543,7 +3543,7 @@
         <v>pending</v>
       </c>
       <c r="D219">
-        <v>455.51688469957276</v>
+        <v>1939.6642135174247</v>
       </c>
     </row>
     <row r="220">
@@ -3557,7 +3557,7 @@
         <v>approved</v>
       </c>
       <c r="D220">
-        <v>2476.5253925536144</v>
+        <v>551.4599854494295</v>
       </c>
     </row>
     <row r="221">
@@ -3571,7 +3571,7 @@
         <v>pending</v>
       </c>
       <c r="D221">
-        <v>1999.7829571130244</v>
+        <v>2126.739666711478</v>
       </c>
     </row>
     <row r="222">
@@ -3585,7 +3585,7 @@
         <v>approved</v>
       </c>
       <c r="D222">
-        <v>4686.834792015231</v>
+        <v>163.81291844119627</v>
       </c>
     </row>
     <row r="223">
@@ -3599,7 +3599,7 @@
         <v>pending</v>
       </c>
       <c r="D223">
-        <v>1666.514791503272</v>
+        <v>3451.4044695853563</v>
       </c>
     </row>
     <row r="224">
@@ -3613,7 +3613,7 @@
         <v>approved</v>
       </c>
       <c r="D224">
-        <v>4521.4595595815035</v>
+        <v>3237.2803180890173</v>
       </c>
     </row>
     <row r="225">
@@ -3627,7 +3627,7 @@
         <v>pending</v>
       </c>
       <c r="D225">
-        <v>1579.5826235559896</v>
+        <v>2634.5238553278737</v>
       </c>
     </row>
     <row r="226">
@@ -3641,7 +3641,7 @@
         <v>approved</v>
       </c>
       <c r="D226">
-        <v>4897.548736491548</v>
+        <v>505.240695809408</v>
       </c>
     </row>
     <row r="227">
@@ -3655,7 +3655,7 @@
         <v>pending</v>
       </c>
       <c r="D227">
-        <v>3973.4341982516476</v>
+        <v>1990.6747220473596</v>
       </c>
     </row>
     <row r="228">
@@ -3669,7 +3669,7 @@
         <v>approved</v>
       </c>
       <c r="D228">
-        <v>4392.291198773999</v>
+        <v>4712.877603005786</v>
       </c>
     </row>
     <row r="229">
@@ -3683,7 +3683,7 @@
         <v>pending</v>
       </c>
       <c r="D229">
-        <v>3397.681429962404</v>
+        <v>2419.805487771759</v>
       </c>
     </row>
     <row r="230">
@@ -3697,7 +3697,7 @@
         <v>approved</v>
       </c>
       <c r="D230">
-        <v>2963.824185244367</v>
+        <v>2536.2688569598504</v>
       </c>
     </row>
     <row r="231">
@@ -3711,7 +3711,7 @@
         <v>pending</v>
       </c>
       <c r="D231">
-        <v>447.1499768035825</v>
+        <v>1198.8710038539618</v>
       </c>
     </row>
     <row r="232">
@@ -3725,7 +3725,7 @@
         <v>approved</v>
       </c>
       <c r="D232">
-        <v>3149.450496091184</v>
+        <v>606.9127555385923</v>
       </c>
     </row>
     <row r="233">
@@ -3739,7 +3739,7 @@
         <v>pending</v>
       </c>
       <c r="D233">
-        <v>4907.704770762659</v>
+        <v>5.291183974296398</v>
       </c>
     </row>
     <row r="234">
@@ -3753,7 +3753,7 @@
         <v>approved</v>
       </c>
       <c r="D234">
-        <v>1790.8722202196925</v>
+        <v>2152.0468254399207</v>
       </c>
     </row>
     <row r="235">
@@ -3767,7 +3767,7 @@
         <v>pending</v>
       </c>
       <c r="D235">
-        <v>1431.3959557222634</v>
+        <v>3599.6579149586737</v>
       </c>
     </row>
     <row r="236">
@@ -3781,7 +3781,7 @@
         <v>approved</v>
       </c>
       <c r="D236">
-        <v>446.7421528455162</v>
+        <v>46.84736024742509</v>
       </c>
     </row>
     <row r="237">
@@ -3795,7 +3795,7 @@
         <v>pending</v>
       </c>
       <c r="D237">
-        <v>190.224921955231</v>
+        <v>2161.574858537659</v>
       </c>
     </row>
     <row r="238">
@@ -3809,7 +3809,7 @@
         <v>approved</v>
       </c>
       <c r="D238">
-        <v>4913.479026755762</v>
+        <v>889.3161015777284</v>
       </c>
     </row>
     <row r="239">
@@ -3823,7 +3823,7 @@
         <v>pending</v>
       </c>
       <c r="D239">
-        <v>4613.953302767591</v>
+        <v>799.3429458926105</v>
       </c>
     </row>
     <row r="240">
@@ -3837,7 +3837,7 @@
         <v>approved</v>
       </c>
       <c r="D240">
-        <v>2978.706693242934</v>
+        <v>2375.0802804710315</v>
       </c>
     </row>
     <row r="241">
@@ -3851,7 +3851,7 @@
         <v>pending</v>
       </c>
       <c r="D241">
-        <v>956.9634596268561</v>
+        <v>1645.3623894785896</v>
       </c>
     </row>
     <row r="242">
@@ -3865,7 +3865,7 @@
         <v>approved</v>
       </c>
       <c r="D242">
-        <v>1735.0858093034649</v>
+        <v>4669.810986929892</v>
       </c>
     </row>
     <row r="243">
@@ -3879,7 +3879,7 @@
         <v>pending</v>
       </c>
       <c r="D243">
-        <v>3272.942788263753</v>
+        <v>267.110891977157</v>
       </c>
     </row>
     <row r="244">
@@ -3893,7 +3893,7 @@
         <v>approved</v>
       </c>
       <c r="D244">
-        <v>854.0051174066698</v>
+        <v>1366.7271456205642</v>
       </c>
     </row>
     <row r="245">
@@ -3907,7 +3907,7 @@
         <v>pending</v>
       </c>
       <c r="D245">
-        <v>1063.1339118522242</v>
+        <v>4849.947504753639</v>
       </c>
     </row>
     <row r="246">
@@ -3921,7 +3921,7 @@
         <v>approved</v>
       </c>
       <c r="D246">
-        <v>3605.1700386682282</v>
+        <v>1013.9891837217563</v>
       </c>
     </row>
     <row r="247">
@@ -3935,7 +3935,7 @@
         <v>pending</v>
       </c>
       <c r="D247">
-        <v>2078.803117802459</v>
+        <v>300.48773821690577</v>
       </c>
     </row>
     <row r="248">
@@ -3949,7 +3949,7 @@
         <v>approved</v>
       </c>
       <c r="D248">
-        <v>4235.420846671826</v>
+        <v>924.7184261075225</v>
       </c>
     </row>
     <row r="249">
@@ -3963,7 +3963,7 @@
         <v>pending</v>
       </c>
       <c r="D249">
-        <v>1631.829666959186</v>
+        <v>9.325817817184001</v>
       </c>
     </row>
     <row r="250">
@@ -3977,7 +3977,7 @@
         <v>approved</v>
       </c>
       <c r="D250">
-        <v>3735.8535548345626</v>
+        <v>1647.5930704566722</v>
       </c>
     </row>
     <row r="251">
@@ -3991,7 +3991,7 @@
         <v>pending</v>
       </c>
       <c r="D251">
-        <v>4805.94581657143</v>
+        <v>1372.3642062049835</v>
       </c>
     </row>
     <row r="252">
@@ -4005,7 +4005,7 @@
         <v>approved</v>
       </c>
       <c r="D252">
-        <v>1464.8807103248907</v>
+        <v>1890.9886171703915</v>
       </c>
     </row>
     <row r="253">
@@ -4019,7 +4019,7 @@
         <v>pending</v>
       </c>
       <c r="D253">
-        <v>4280.824899305897</v>
+        <v>1086.521188727605</v>
       </c>
     </row>
     <row r="254">
@@ -4033,7 +4033,7 @@
         <v>approved</v>
       </c>
       <c r="D254">
-        <v>3249.079115846616</v>
+        <v>4618.454414958038</v>
       </c>
     </row>
     <row r="255">
@@ -4047,7 +4047,7 @@
         <v>pending</v>
       </c>
       <c r="D255">
-        <v>311.1412809264924</v>
+        <v>4256.328945581434</v>
       </c>
     </row>
     <row r="256">
@@ -4061,7 +4061,7 @@
         <v>approved</v>
       </c>
       <c r="D256">
-        <v>3163.211364889387</v>
+        <v>2078.799828783928</v>
       </c>
     </row>
     <row r="257">
@@ -4075,7 +4075,7 @@
         <v>pending</v>
       </c>
       <c r="D257">
-        <v>3104.286903783222</v>
+        <v>887.7465849237731</v>
       </c>
     </row>
     <row r="258">
@@ -4089,7 +4089,7 @@
         <v>approved</v>
       </c>
       <c r="D258">
-        <v>2869.7172876280965</v>
+        <v>4459.983490570751</v>
       </c>
     </row>
     <row r="259">
@@ -4103,7 +4103,7 @@
         <v>pending</v>
       </c>
       <c r="D259">
-        <v>1524.7745859684715</v>
+        <v>2868.311023210892</v>
       </c>
     </row>
     <row r="260">
@@ -4117,7 +4117,7 @@
         <v>approved</v>
       </c>
       <c r="D260">
-        <v>3283.216629405222</v>
+        <v>1746.249906520162</v>
       </c>
     </row>
     <row r="261">
@@ -4131,7 +4131,7 @@
         <v>pending</v>
       </c>
       <c r="D261">
-        <v>1074.8456814328079</v>
+        <v>4316.016489842306</v>
       </c>
     </row>
     <row r="262">
@@ -4145,7 +4145,7 @@
         <v>approved</v>
       </c>
       <c r="D262">
-        <v>2610.117259199959</v>
+        <v>2572.227730710228</v>
       </c>
     </row>
     <row r="263">
@@ -4159,7 +4159,7 @@
         <v>pending</v>
       </c>
       <c r="D263">
-        <v>4980.85218873017</v>
+        <v>3937.1362860826243</v>
       </c>
     </row>
     <row r="264">
@@ -4173,7 +4173,7 @@
         <v>approved</v>
       </c>
       <c r="D264">
-        <v>4573.529103184018</v>
+        <v>215.1359644409645</v>
       </c>
     </row>
     <row r="265">
@@ -4187,7 +4187,7 @@
         <v>pending</v>
       </c>
       <c r="D265">
-        <v>3330.354540782793</v>
+        <v>879.6768999079496</v>
       </c>
     </row>
     <row r="266">
@@ -4201,7 +4201,7 @@
         <v>approved</v>
       </c>
       <c r="D266">
-        <v>4528.947266010427</v>
+        <v>405.0542104686694</v>
       </c>
     </row>
     <row r="267">
@@ -4215,7 +4215,7 @@
         <v>pending</v>
       </c>
       <c r="D267">
-        <v>3260.2124930250443</v>
+        <v>2955.217172800325</v>
       </c>
     </row>
     <row r="268">
@@ -4229,7 +4229,7 @@
         <v>approved</v>
       </c>
       <c r="D268">
-        <v>3020.0850117891596</v>
+        <v>2927.880338644925</v>
       </c>
     </row>
     <row r="269">
@@ -4243,7 +4243,7 @@
         <v>pending</v>
       </c>
       <c r="D269">
-        <v>4163.305110757907</v>
+        <v>2507.3674385782497</v>
       </c>
     </row>
     <row r="270">
@@ -4257,7 +4257,7 @@
         <v>approved</v>
       </c>
       <c r="D270">
-        <v>1283.425721918815</v>
+        <v>3722.942869840743</v>
       </c>
     </row>
     <row r="271">
@@ -4271,7 +4271,7 @@
         <v>pending</v>
       </c>
       <c r="D271">
-        <v>2711.148332605321</v>
+        <v>3037.0477715304487</v>
       </c>
     </row>
     <row r="272">
@@ -4285,7 +4285,7 @@
         <v>approved</v>
       </c>
       <c r="D272">
-        <v>4183.735915694182</v>
+        <v>1965.167674931091</v>
       </c>
     </row>
     <row r="273">
@@ -4299,7 +4299,7 @@
         <v>pending</v>
       </c>
       <c r="D273">
-        <v>3447.8872559206607</v>
+        <v>1664.2097636187514</v>
       </c>
     </row>
     <row r="274">
@@ -4313,7 +4313,7 @@
         <v>approved</v>
       </c>
       <c r="D274">
-        <v>1912.428753781249</v>
+        <v>4931.380631937491</v>
       </c>
     </row>
     <row r="275">
@@ -4327,7 +4327,7 @@
         <v>pending</v>
       </c>
       <c r="D275">
-        <v>1908.6877649109401</v>
+        <v>3667.632384472428</v>
       </c>
     </row>
     <row r="276">
@@ -4341,7 +4341,7 @@
         <v>approved</v>
       </c>
       <c r="D276">
-        <v>4496.000945536045</v>
+        <v>474.8912898201829</v>
       </c>
     </row>
     <row r="277">
@@ -4355,7 +4355,7 @@
         <v>pending</v>
       </c>
       <c r="D277">
-        <v>3943.779651052558</v>
+        <v>3709.485601763852</v>
       </c>
     </row>
     <row r="278">
@@ -4369,7 +4369,7 @@
         <v>approved</v>
       </c>
       <c r="D278">
-        <v>3163.84527402205</v>
+        <v>2924.2165014567713</v>
       </c>
     </row>
     <row r="279">
@@ -4383,7 +4383,7 @@
         <v>pending</v>
       </c>
       <c r="D279">
-        <v>2948.020098035128</v>
+        <v>1933.886584224096</v>
       </c>
     </row>
     <row r="280">
@@ -4397,7 +4397,7 @@
         <v>approved</v>
       </c>
       <c r="D280">
-        <v>3742.083629088324</v>
+        <v>1857.9576388171715</v>
       </c>
     </row>
     <row r="281">
@@ -4411,7 +4411,7 @@
         <v>pending</v>
       </c>
       <c r="D281">
-        <v>687.1414423847133</v>
+        <v>1357.4209654750002</v>
       </c>
     </row>
     <row r="282">
@@ -4425,7 +4425,7 @@
         <v>approved</v>
       </c>
       <c r="D282">
-        <v>4615.964556293679</v>
+        <v>3102.256368243117</v>
       </c>
     </row>
     <row r="283">
@@ -4439,7 +4439,7 @@
         <v>pending</v>
       </c>
       <c r="D283">
-        <v>994.0254632634027</v>
+        <v>4850.266659624306</v>
       </c>
     </row>
     <row r="284">
@@ -4453,7 +4453,7 @@
         <v>approved</v>
       </c>
       <c r="D284">
-        <v>3688.9012959543</v>
+        <v>682.8142806394311</v>
       </c>
     </row>
     <row r="285">
@@ -4467,7 +4467,7 @@
         <v>pending</v>
       </c>
       <c r="D285">
-        <v>2654.517315848043</v>
+        <v>533.3881125258011</v>
       </c>
     </row>
     <row r="286">
@@ -4481,7 +4481,7 @@
         <v>approved</v>
       </c>
       <c r="D286">
-        <v>4084.5453228990436</v>
+        <v>271.5290811835913</v>
       </c>
     </row>
     <row r="287">
@@ -4495,7 +4495,7 @@
         <v>pending</v>
       </c>
       <c r="D287">
-        <v>2864.0090031939667</v>
+        <v>3894.6418878739696</v>
       </c>
     </row>
     <row r="288">
@@ -4509,7 +4509,7 @@
         <v>approved</v>
       </c>
       <c r="D288">
-        <v>1288.0146560356466</v>
+        <v>420.2329344600386</v>
       </c>
     </row>
     <row r="289">
@@ -4523,7 +4523,7 @@
         <v>pending</v>
       </c>
       <c r="D289">
-        <v>1279.4730505561724</v>
+        <v>2281.360417087943</v>
       </c>
     </row>
     <row r="290">
@@ -4537,7 +4537,7 @@
         <v>approved</v>
       </c>
       <c r="D290">
-        <v>92.0069328821782</v>
+        <v>2141.8780388203486</v>
       </c>
     </row>
     <row r="291">
@@ -4551,7 +4551,7 @@
         <v>pending</v>
       </c>
       <c r="D291">
-        <v>306.5647429837215</v>
+        <v>635.6276430549291</v>
       </c>
     </row>
     <row r="292">
@@ -4565,7 +4565,7 @@
         <v>approved</v>
       </c>
       <c r="D292">
-        <v>1493.1173796260412</v>
+        <v>1491.1538396855995</v>
       </c>
     </row>
     <row r="293">
@@ -4579,7 +4579,7 @@
         <v>pending</v>
       </c>
       <c r="D293">
-        <v>2816.473739117892</v>
+        <v>231.53031020309635</v>
       </c>
     </row>
     <row r="294">
@@ -4593,7 +4593,7 @@
         <v>approved</v>
       </c>
       <c r="D294">
-        <v>949.6789724771637</v>
+        <v>1566.656287070214</v>
       </c>
     </row>
     <row r="295">
@@ -4607,7 +4607,7 @@
         <v>pending</v>
       </c>
       <c r="D295">
-        <v>67.25409033973673</v>
+        <v>4582.676108247354</v>
       </c>
     </row>
     <row r="296">
@@ -4621,7 +4621,7 @@
         <v>approved</v>
       </c>
       <c r="D296">
-        <v>1259.6878119871324</v>
+        <v>2421.6835233650513</v>
       </c>
     </row>
     <row r="297">
@@ -4635,7 +4635,7 @@
         <v>pending</v>
       </c>
       <c r="D297">
-        <v>1979.7838626455355</v>
+        <v>3347.489969410167</v>
       </c>
     </row>
     <row r="298">
@@ -4649,7 +4649,7 @@
         <v>approved</v>
       </c>
       <c r="D298">
-        <v>2046.4958573967606</v>
+        <v>1555.6792152320277</v>
       </c>
     </row>
     <row r="299">
@@ -4663,7 +4663,7 @@
         <v>pending</v>
       </c>
       <c r="D299">
-        <v>738.3633599180795</v>
+        <v>3743.666027277525</v>
       </c>
     </row>
     <row r="300">
@@ -4677,7 +4677,7 @@
         <v>approved</v>
       </c>
       <c r="D300">
-        <v>459.93486925735016</v>
+        <v>1613.7079209617466</v>
       </c>
     </row>
     <row r="301">
@@ -4691,7 +4691,7 @@
         <v>pending</v>
       </c>
       <c r="D301">
-        <v>1109.864261633947</v>
+        <v>690.1000775449572</v>
       </c>
     </row>
     <row r="302">
@@ -4705,7 +4705,7 @@
         <v>approved</v>
       </c>
       <c r="D302">
-        <v>3505.7196676052517</v>
+        <v>1314.4260389912288</v>
       </c>
     </row>
     <row r="303">
@@ -4719,7 +4719,7 @@
         <v>pending</v>
       </c>
       <c r="D303">
-        <v>2139.165937361491</v>
+        <v>2133.5243054279485</v>
       </c>
     </row>
     <row r="304">
@@ -4733,7 +4733,7 @@
         <v>approved</v>
       </c>
       <c r="D304">
-        <v>2637.0646664573314</v>
+        <v>2452.4339006204323</v>
       </c>
     </row>
     <row r="305">
@@ -4747,7 +4747,7 @@
         <v>pending</v>
       </c>
       <c r="D305">
-        <v>3173.410466333825</v>
+        <v>1364.4935689872939</v>
       </c>
     </row>
     <row r="306">
@@ -4761,7 +4761,7 @@
         <v>approved</v>
       </c>
       <c r="D306">
-        <v>2240.6073468122436</v>
+        <v>2229.1089837133404</v>
       </c>
     </row>
     <row r="307">
@@ -4775,7 +4775,7 @@
         <v>pending</v>
       </c>
       <c r="D307">
-        <v>3209.1816993270563</v>
+        <v>4385.481978430635</v>
       </c>
     </row>
     <row r="308">
@@ -4789,7 +4789,7 @@
         <v>approved</v>
       </c>
       <c r="D308">
-        <v>3346.9507043830727</v>
+        <v>856.4273860346506</v>
       </c>
     </row>
     <row r="309">
@@ -4803,7 +4803,7 @@
         <v>pending</v>
       </c>
       <c r="D309">
-        <v>892.6511617612198</v>
+        <v>4105.229436830033</v>
       </c>
     </row>
     <row r="310">
@@ -4817,7 +4817,7 @@
         <v>approved</v>
       </c>
       <c r="D310">
-        <v>4177.926376011363</v>
+        <v>165.00946509034887</v>
       </c>
     </row>
     <row r="311">
@@ -4831,7 +4831,7 @@
         <v>pending</v>
       </c>
       <c r="D311">
-        <v>2085.0041941974896</v>
+        <v>3065.5200935763273</v>
       </c>
     </row>
     <row r="312">
@@ -4845,7 +4845,7 @@
         <v>approved</v>
       </c>
       <c r="D312">
-        <v>1363.5438563515113</v>
+        <v>2298.3574149464225</v>
       </c>
     </row>
     <row r="313">
@@ -4859,7 +4859,7 @@
         <v>pending</v>
       </c>
       <c r="D313">
-        <v>2384.8225666269186</v>
+        <v>4587.8213731015185</v>
       </c>
     </row>
     <row r="314">
@@ -4873,7 +4873,7 @@
         <v>approved</v>
       </c>
       <c r="D314">
-        <v>1900.3780896932233</v>
+        <v>3664.9704839302212</v>
       </c>
     </row>
     <row r="315">
@@ -4887,7 +4887,7 @@
         <v>pending</v>
       </c>
       <c r="D315">
-        <v>3005.0805270254923</v>
+        <v>3828.148593316666</v>
       </c>
     </row>
     <row r="316">
@@ -4901,7 +4901,7 @@
         <v>approved</v>
       </c>
       <c r="D316">
-        <v>3065.0147155136087</v>
+        <v>730.4545370040994</v>
       </c>
     </row>
     <row r="317">
@@ -4915,7 +4915,7 @@
         <v>pending</v>
       </c>
       <c r="D317">
-        <v>210.60887718304167</v>
+        <v>1799.7054691937942</v>
       </c>
     </row>
     <row r="318">
@@ -4929,7 +4929,7 @@
         <v>approved</v>
       </c>
       <c r="D318">
-        <v>1366.2277623972009</v>
+        <v>1708.7722901321144</v>
       </c>
     </row>
     <row r="319">
@@ -4943,7 +4943,7 @@
         <v>pending</v>
       </c>
       <c r="D319">
-        <v>4979.973253236498</v>
+        <v>3026.9524865705835</v>
       </c>
     </row>
     <row r="320">
@@ -4957,7 +4957,7 @@
         <v>approved</v>
       </c>
       <c r="D320">
-        <v>1563.5466087315087</v>
+        <v>4817.86145635105</v>
       </c>
     </row>
     <row r="321">
@@ -4971,7 +4971,7 @@
         <v>pending</v>
       </c>
       <c r="D321">
-        <v>3567.7010388367557</v>
+        <v>1592.6618824330496</v>
       </c>
     </row>
     <row r="322">
@@ -4985,7 +4985,7 @@
         <v>approved</v>
       </c>
       <c r="D322">
-        <v>1217.580346713275</v>
+        <v>720.5483405047108</v>
       </c>
     </row>
     <row r="323">
@@ -4999,7 +4999,7 @@
         <v>pending</v>
       </c>
       <c r="D323">
-        <v>306.94397001678084</v>
+        <v>4628.95786491227</v>
       </c>
     </row>
     <row r="324">
@@ -5013,7 +5013,7 @@
         <v>approved</v>
       </c>
       <c r="D324">
-        <v>3709.487645072447</v>
+        <v>2822.2527206094937</v>
       </c>
     </row>
     <row r="325">
@@ -5027,7 +5027,7 @@
         <v>pending</v>
       </c>
       <c r="D325">
-        <v>3018.7512394779237</v>
+        <v>4673.87412254653</v>
       </c>
     </row>
     <row r="326">
@@ -5041,7 +5041,7 @@
         <v>approved</v>
       </c>
       <c r="D326">
-        <v>3108.9137315454586</v>
+        <v>2964.9018705732956</v>
       </c>
     </row>
     <row r="327">
@@ -5055,7 +5055,7 @@
         <v>pending</v>
       </c>
       <c r="D327">
-        <v>449.8732524627491</v>
+        <v>663.386195592115</v>
       </c>
     </row>
     <row r="328">
@@ -5069,7 +5069,7 @@
         <v>approved</v>
       </c>
       <c r="D328">
-        <v>532.6888416672792</v>
+        <v>2648.1802428024557</v>
       </c>
     </row>
     <row r="329">
@@ -5083,7 +5083,7 @@
         <v>pending</v>
       </c>
       <c r="D329">
-        <v>4488.791771271996</v>
+        <v>4477.350272616621</v>
       </c>
     </row>
     <row r="330">
@@ -5097,7 +5097,7 @@
         <v>approved</v>
       </c>
       <c r="D330">
-        <v>2107.2468660812638</v>
+        <v>1460.0081192754944</v>
       </c>
     </row>
     <row r="331">
@@ -5111,7 +5111,7 @@
         <v>pending</v>
       </c>
       <c r="D331">
-        <v>4847.310460404908</v>
+        <v>4203.24711312346</v>
       </c>
     </row>
     <row r="332">
@@ -5125,7 +5125,7 @@
         <v>approved</v>
       </c>
       <c r="D332">
-        <v>1782.147756203455</v>
+        <v>3676.8192837627876</v>
       </c>
     </row>
     <row r="333">
@@ -5139,7 +5139,7 @@
         <v>pending</v>
       </c>
       <c r="D333">
-        <v>2611.8225759422367</v>
+        <v>343.6443091414465</v>
       </c>
     </row>
     <row r="334">
@@ -5153,7 +5153,7 @@
         <v>approved</v>
       </c>
       <c r="D334">
-        <v>1205.9979960801381</v>
+        <v>3793.2338936480824</v>
       </c>
     </row>
     <row r="335">
@@ -5167,7 +5167,7 @@
         <v>pending</v>
       </c>
       <c r="D335">
-        <v>2156.0620292926615</v>
+        <v>4669.844649528361</v>
       </c>
     </row>
     <row r="336">
@@ -5181,7 +5181,7 @@
         <v>approved</v>
       </c>
       <c r="D336">
-        <v>693.0705547046567</v>
+        <v>2997.234883618751</v>
       </c>
     </row>
     <row r="337">
@@ -5195,7 +5195,7 @@
         <v>pending</v>
       </c>
       <c r="D337">
-        <v>1128.5134890235727</v>
+        <v>2596.707312900217</v>
       </c>
     </row>
     <row r="338">
@@ -5209,7 +5209,7 @@
         <v>approved</v>
       </c>
       <c r="D338">
-        <v>3101.2413009288166</v>
+        <v>2110.194828241153</v>
       </c>
     </row>
     <row r="339">
@@ -5223,7 +5223,7 @@
         <v>pending</v>
       </c>
       <c r="D339">
-        <v>1987.7778058555061</v>
+        <v>992.4005582326889</v>
       </c>
     </row>
     <row r="340">
@@ -5237,7 +5237,7 @@
         <v>approved</v>
       </c>
       <c r="D340">
-        <v>4616.890008149753</v>
+        <v>1191.9250426926087</v>
       </c>
     </row>
     <row r="341">
@@ -5251,7 +5251,7 @@
         <v>pending</v>
       </c>
       <c r="D341">
-        <v>386.1234206127206</v>
+        <v>3020.018090816439</v>
       </c>
     </row>
     <row r="342">
@@ -5265,7 +5265,7 @@
         <v>approved</v>
       </c>
       <c r="D342">
-        <v>2237.376303344185</v>
+        <v>1708.810294265528</v>
       </c>
     </row>
     <row r="343">
@@ -5279,7 +5279,7 @@
         <v>pending</v>
       </c>
       <c r="D343">
-        <v>4895.674353191724</v>
+        <v>2418.566770416293</v>
       </c>
     </row>
     <row r="344">
@@ -5293,7 +5293,7 @@
         <v>approved</v>
       </c>
       <c r="D344">
-        <v>4100.886792460041</v>
+        <v>4082.2595303688736</v>
       </c>
     </row>
     <row r="345">
@@ -5307,7 +5307,7 @@
         <v>pending</v>
       </c>
       <c r="D345">
-        <v>608.2083016763007</v>
+        <v>3145.14639756552</v>
       </c>
     </row>
     <row r="346">
@@ -5321,7 +5321,7 @@
         <v>approved</v>
       </c>
       <c r="D346">
-        <v>811.824740995507</v>
+        <v>4225.4076347816235</v>
       </c>
     </row>
     <row r="347">
@@ -5335,7 +5335,7 @@
         <v>pending</v>
       </c>
       <c r="D347">
-        <v>27.06481101947822</v>
+        <v>4081.9732323900316</v>
       </c>
     </row>
     <row r="348">
@@ -5349,7 +5349,7 @@
         <v>approved</v>
       </c>
       <c r="D348">
-        <v>1800.0086882514377</v>
+        <v>3066.463818911248</v>
       </c>
     </row>
     <row r="349">
@@ -5363,7 +5363,7 @@
         <v>pending</v>
       </c>
       <c r="D349">
-        <v>771.9686506411971</v>
+        <v>4885.560106157306</v>
       </c>
     </row>
     <row r="350">
@@ -5377,7 +5377,7 @@
         <v>approved</v>
       </c>
       <c r="D350">
-        <v>3192.2774595900605</v>
+        <v>4470.494100308745</v>
       </c>
     </row>
     <row r="351">
@@ -5391,7 +5391,7 @@
         <v>pending</v>
       </c>
       <c r="D351">
-        <v>3413.431742694799</v>
+        <v>4334.840036956133</v>
       </c>
     </row>
     <row r="352">
@@ -5405,7 +5405,7 @@
         <v>approved</v>
       </c>
       <c r="D352">
-        <v>46.72471391305888</v>
+        <v>673.0616730770589</v>
       </c>
     </row>
     <row r="353">
@@ -5419,7 +5419,7 @@
         <v>pending</v>
       </c>
       <c r="D353">
-        <v>86.15771492235358</v>
+        <v>3002.7827020423347</v>
       </c>
     </row>
     <row r="354">
@@ -5433,7 +5433,7 @@
         <v>approved</v>
       </c>
       <c r="D354">
-        <v>3125.960617341654</v>
+        <v>2289.9960329671608</v>
       </c>
     </row>
     <row r="355">
@@ -5447,7 +5447,7 @@
         <v>pending</v>
       </c>
       <c r="D355">
-        <v>589.5487831262413</v>
+        <v>329.22445878508233</v>
       </c>
     </row>
     <row r="356">
@@ -5461,7 +5461,7 @@
         <v>approved</v>
       </c>
       <c r="D356">
-        <v>3111.3118711713882</v>
+        <v>940.7999129248956</v>
       </c>
     </row>
     <row r="357">
@@ -5475,7 +5475,7 @@
         <v>pending</v>
       </c>
       <c r="D357">
-        <v>970.31932511217</v>
+        <v>1203.3135383941517</v>
       </c>
     </row>
     <row r="358">
@@ -5489,7 +5489,7 @@
         <v>approved</v>
       </c>
       <c r="D358">
-        <v>826.1951913295218</v>
+        <v>921.1612553785642</v>
       </c>
     </row>
     <row r="359">
@@ -5503,7 +5503,7 @@
         <v>pending</v>
       </c>
       <c r="D359">
-        <v>4078.894730681597</v>
+        <v>1699.0496317889247</v>
       </c>
     </row>
     <row r="360">
@@ -5517,7 +5517,7 @@
         <v>approved</v>
       </c>
       <c r="D360">
-        <v>1282.753784242152</v>
+        <v>2415.1510057340242</v>
       </c>
     </row>
     <row r="361">
@@ -5531,7 +5531,7 @@
         <v>pending</v>
       </c>
       <c r="D361">
-        <v>3627.856468710252</v>
+        <v>4556.183079519574</v>
       </c>
     </row>
     <row r="362">
@@ -5545,7 +5545,7 @@
         <v>approved</v>
       </c>
       <c r="D362">
-        <v>2695.044544364218</v>
+        <v>889.0001461722263</v>
       </c>
     </row>
     <row r="363">
@@ -5559,7 +5559,7 @@
         <v>pending</v>
       </c>
       <c r="D363">
-        <v>2084.70544544781</v>
+        <v>3877.3411565485317</v>
       </c>
     </row>
     <row r="364">
@@ -5573,7 +5573,7 @@
         <v>approved</v>
       </c>
       <c r="D364">
-        <v>266.8924965515496</v>
+        <v>328.26363065123655</v>
       </c>
     </row>
     <row r="365">
@@ -5587,7 +5587,7 @@
         <v>pending</v>
       </c>
       <c r="D365">
-        <v>3588.565647399675</v>
+        <v>4540.0811690353985</v>
       </c>
     </row>
     <row r="366">
@@ -5601,7 +5601,7 @@
         <v>approved</v>
       </c>
       <c r="D366">
-        <v>2435.7347344976433</v>
+        <v>4951.9550164404545</v>
       </c>
     </row>
     <row r="367">
@@ -5615,7 +5615,7 @@
         <v>pending</v>
       </c>
       <c r="D367">
-        <v>3787.7780452883126</v>
+        <v>3220.1910165719937</v>
       </c>
     </row>
     <row r="368">
@@ -5629,7 +5629,7 @@
         <v>approved</v>
       </c>
       <c r="D368">
-        <v>1077.56527709171</v>
+        <v>4244.810640814558</v>
       </c>
     </row>
     <row r="369">
@@ -5643,7 +5643,7 @@
         <v>pending</v>
       </c>
       <c r="D369">
-        <v>4143.659553695122</v>
+        <v>1326.431777304915</v>
       </c>
     </row>
     <row r="370">
@@ -5657,7 +5657,7 @@
         <v>approved</v>
       </c>
       <c r="D370">
-        <v>3287.5730362005993</v>
+        <v>3753.489466777555</v>
       </c>
     </row>
     <row r="371">
@@ -5671,7 +5671,7 @@
         <v>pending</v>
       </c>
       <c r="D371">
-        <v>1394.363779265173</v>
+        <v>1125.9452867835196</v>
       </c>
     </row>
     <row r="372">
@@ -5685,7 +5685,7 @@
         <v>approved</v>
       </c>
       <c r="D372">
-        <v>1231.983192605909</v>
+        <v>3397.952514802456</v>
       </c>
     </row>
     <row r="373">
@@ -5699,7 +5699,7 @@
         <v>pending</v>
       </c>
       <c r="D373">
-        <v>1953.9082713671207</v>
+        <v>4975.282798696591</v>
       </c>
     </row>
     <row r="374">
@@ -5713,7 +5713,7 @@
         <v>approved</v>
       </c>
       <c r="D374">
-        <v>1156.908497527126</v>
+        <v>2830.9629943801574</v>
       </c>
     </row>
     <row r="375">
@@ -5727,7 +5727,7 @@
         <v>pending</v>
       </c>
       <c r="D375">
-        <v>4892.477778039965</v>
+        <v>110.70395796915378</v>
       </c>
     </row>
     <row r="376">
@@ -5741,7 +5741,7 @@
         <v>approved</v>
       </c>
       <c r="D376">
-        <v>373.40153557255064</v>
+        <v>3843.541335232933</v>
       </c>
     </row>
     <row r="377">
@@ -5755,7 +5755,7 @@
         <v>pending</v>
       </c>
       <c r="D377">
-        <v>761.337763650749</v>
+        <v>4714.384190748026</v>
       </c>
     </row>
     <row r="378">
@@ -5769,7 +5769,7 @@
         <v>approved</v>
       </c>
       <c r="D378">
-        <v>4415.203835631637</v>
+        <v>2698.4862971944535</v>
       </c>
     </row>
     <row r="379">
@@ -5783,7 +5783,7 @@
         <v>pending</v>
       </c>
       <c r="D379">
-        <v>3264.875644499294</v>
+        <v>2141.4346036722054</v>
       </c>
     </row>
     <row r="380">
@@ -5797,7 +5797,7 @@
         <v>approved</v>
       </c>
       <c r="D380">
-        <v>52.01594800835152</v>
+        <v>4246.461537903945</v>
       </c>
     </row>
     <row r="381">
@@ -5811,7 +5811,7 @@
         <v>pending</v>
       </c>
       <c r="D381">
-        <v>2875.1875243808513</v>
+        <v>862.8002388622202</v>
       </c>
     </row>
     <row r="382">
@@ -5825,7 +5825,7 @@
         <v>approved</v>
       </c>
       <c r="D382">
-        <v>4272.952851264144</v>
+        <v>920.8177644444615</v>
       </c>
     </row>
     <row r="383">
@@ -5839,7 +5839,7 @@
         <v>pending</v>
       </c>
       <c r="D383">
-        <v>4165.321953335416</v>
+        <v>295.22719811357456</v>
       </c>
     </row>
     <row r="384">
@@ -5853,7 +5853,7 @@
         <v>approved</v>
       </c>
       <c r="D384">
-        <v>3540.664154115275</v>
+        <v>2842.949446565186</v>
       </c>
     </row>
     <row r="385">
@@ -5867,7 +5867,7 @@
         <v>pending</v>
       </c>
       <c r="D385">
-        <v>4277.749497113244</v>
+        <v>213.54888680240046</v>
       </c>
     </row>
     <row r="386">
@@ -5881,7 +5881,7 @@
         <v>approved</v>
       </c>
       <c r="D386">
-        <v>2862.2955008357176</v>
+        <v>3803.825587108963</v>
       </c>
     </row>
     <row r="387">
@@ -5895,7 +5895,7 @@
         <v>pending</v>
       </c>
       <c r="D387">
-        <v>3278.639871460374</v>
+        <v>3289.3290377162807</v>
       </c>
     </row>
     <row r="388">
@@ -5909,7 +5909,7 @@
         <v>approved</v>
       </c>
       <c r="D388">
-        <v>4265.119393955795</v>
+        <v>96.20453759146885</v>
       </c>
     </row>
     <row r="389">
@@ -5923,7 +5923,7 @@
         <v>pending</v>
       </c>
       <c r="D389">
-        <v>2988.7478903782217</v>
+        <v>3347.791451791633</v>
       </c>
     </row>
     <row r="390">
@@ -5937,7 +5937,7 @@
         <v>approved</v>
       </c>
       <c r="D390">
-        <v>3890.974829975582</v>
+        <v>1465.3610543088623</v>
       </c>
     </row>
     <row r="391">
@@ -5951,7 +5951,7 @@
         <v>pending</v>
       </c>
       <c r="D391">
-        <v>4744.484231006137</v>
+        <v>1685.8558129593794</v>
       </c>
     </row>
     <row r="392">
@@ -5965,7 +5965,7 @@
         <v>approved</v>
       </c>
       <c r="D392">
-        <v>2395.3356209045783</v>
+        <v>3829.6543649822347</v>
       </c>
     </row>
     <row r="393">
@@ -5979,7 +5979,7 @@
         <v>pending</v>
       </c>
       <c r="D393">
-        <v>3698.611383015005</v>
+        <v>4582.019133648999</v>
       </c>
     </row>
     <row r="394">
@@ -5993,7 +5993,7 @@
         <v>approved</v>
       </c>
       <c r="D394">
-        <v>1356.513208139636</v>
+        <v>2836.9705374445166</v>
       </c>
     </row>
     <row r="395">
@@ -6007,7 +6007,7 @@
         <v>pending</v>
       </c>
       <c r="D395">
-        <v>2732.6073957629947</v>
+        <v>1879.0090734317898</v>
       </c>
     </row>
     <row r="396">
@@ -6021,7 +6021,7 @@
         <v>approved</v>
       </c>
       <c r="D396">
-        <v>4189.162908301921</v>
+        <v>368.59982569716567</v>
       </c>
     </row>
     <row r="397">
@@ -6035,7 +6035,7 @@
         <v>pending</v>
       </c>
       <c r="D397">
-        <v>3831.6622975488135</v>
+        <v>4229.071537090043</v>
       </c>
     </row>
     <row r="398">
@@ -6049,7 +6049,7 @@
         <v>approved</v>
       </c>
       <c r="D398">
-        <v>1546.4713366196258</v>
+        <v>1643.4565896406173</v>
       </c>
     </row>
     <row r="399">
@@ -6063,7 +6063,7 @@
         <v>pending</v>
       </c>
       <c r="D399">
-        <v>3262.028796669947</v>
+        <v>2445.7144402040067</v>
       </c>
     </row>
     <row r="400">
@@ -6077,7 +6077,7 @@
         <v>approved</v>
       </c>
       <c r="D400">
-        <v>259.31113733673294</v>
+        <v>213.12483575478436</v>
       </c>
     </row>
     <row r="401">
@@ -6091,7 +6091,7 @@
         <v>pending</v>
       </c>
       <c r="D401">
-        <v>1190.7288960860851</v>
+        <v>4534.16205934557</v>
       </c>
     </row>
     <row r="402">
@@ -6105,7 +6105,7 @@
         <v>approved</v>
       </c>
       <c r="D402">
-        <v>2873.2995006177985</v>
+        <v>1489.9609576067073</v>
       </c>
     </row>
     <row r="403">
@@ -6119,7 +6119,7 @@
         <v>pending</v>
       </c>
       <c r="D403">
-        <v>3587.7150864260275</v>
+        <v>1186.1762982538494</v>
       </c>
     </row>
     <row r="404">
@@ -6133,7 +6133,7 @@
         <v>approved</v>
       </c>
       <c r="D404">
-        <v>2485.140775253346</v>
+        <v>616.7974681557364</v>
       </c>
     </row>
     <row r="405">
@@ -6147,7 +6147,7 @@
         <v>pending</v>
       </c>
       <c r="D405">
-        <v>3212.759748457401</v>
+        <v>4556.614035713476</v>
       </c>
     </row>
     <row r="406">
@@ -6161,7 +6161,7 @@
         <v>approved</v>
       </c>
       <c r="D406">
-        <v>3438.1481523032844</v>
+        <v>4258.179769064023</v>
       </c>
     </row>
     <row r="407">
@@ -6175,7 +6175,7 @@
         <v>pending</v>
       </c>
       <c r="D407">
-        <v>1940.795460617186</v>
+        <v>1142.1960806389209</v>
       </c>
     </row>
     <row r="408">
@@ -6189,7 +6189,7 @@
         <v>approved</v>
       </c>
       <c r="D408">
-        <v>4343.100220535858</v>
+        <v>2302.9134180149426</v>
       </c>
     </row>
     <row r="409">
@@ -6203,7 +6203,7 @@
         <v>pending</v>
       </c>
       <c r="D409">
-        <v>1438.3691285106315</v>
+        <v>4489.874640601447</v>
       </c>
     </row>
     <row r="410">
@@ -6217,7 +6217,7 @@
         <v>approved</v>
       </c>
       <c r="D410">
-        <v>4566.45756541707</v>
+        <v>2262.5988065651904</v>
       </c>
     </row>
     <row r="411">
@@ -6231,7 +6231,7 @@
         <v>pending</v>
       </c>
       <c r="D411">
-        <v>2202.8319924823136</v>
+        <v>2201.03138716618</v>
       </c>
     </row>
     <row r="412">
@@ -6245,7 +6245,7 @@
         <v>approved</v>
       </c>
       <c r="D412">
-        <v>2196.2654065931297</v>
+        <v>3757.20367584464</v>
       </c>
     </row>
     <row r="413">
@@ -6259,7 +6259,7 @@
         <v>pending</v>
       </c>
       <c r="D413">
-        <v>747.6819468326734</v>
+        <v>3289.9404145291633</v>
       </c>
     </row>
     <row r="414">
@@ -6273,7 +6273,7 @@
         <v>approved</v>
       </c>
       <c r="D414">
-        <v>624.6657896674212</v>
+        <v>2191.3946236303063</v>
       </c>
     </row>
     <row r="415">
@@ -6287,7 +6287,7 @@
         <v>pending</v>
       </c>
       <c r="D415">
-        <v>4538.227808452136</v>
+        <v>1549.405211324777</v>
       </c>
     </row>
     <row r="416">
@@ -6301,7 +6301,7 @@
         <v>approved</v>
       </c>
       <c r="D416">
-        <v>1813.8245760812854</v>
+        <v>820.4854032832487</v>
       </c>
     </row>
     <row r="417">
@@ -6315,7 +6315,7 @@
         <v>pending</v>
       </c>
       <c r="D417">
-        <v>2286.5395284966585</v>
+        <v>2978.1025582337274</v>
       </c>
     </row>
     <row r="418">
@@ -6329,7 +6329,7 @@
         <v>approved</v>
       </c>
       <c r="D418">
-        <v>3166.889278009578</v>
+        <v>3521.6796542939032</v>
       </c>
     </row>
     <row r="419">
@@ -6343,7 +6343,7 @@
         <v>pending</v>
       </c>
       <c r="D419">
-        <v>1914.6994996037236</v>
+        <v>2374.0335314614003</v>
       </c>
     </row>
     <row r="420">
@@ -6357,7 +6357,7 @@
         <v>approved</v>
       </c>
       <c r="D420">
-        <v>3196.367257135957</v>
+        <v>4055.9750851542144</v>
       </c>
     </row>
     <row r="421">
@@ -6371,7 +6371,7 @@
         <v>pending</v>
       </c>
       <c r="D421">
-        <v>3075.04019902353</v>
+        <v>3419.092952176034</v>
       </c>
     </row>
     <row r="422">
@@ -6385,7 +6385,7 @@
         <v>approved</v>
       </c>
       <c r="D422">
-        <v>4856.6125484540635</v>
+        <v>2888.7700737991527</v>
       </c>
     </row>
     <row r="423">
@@ -6399,7 +6399,7 @@
         <v>pending</v>
       </c>
       <c r="D423">
-        <v>3467.9095920646673</v>
+        <v>3117.2905197672217</v>
       </c>
     </row>
     <row r="424">
@@ -6413,7 +6413,7 @@
         <v>approved</v>
       </c>
       <c r="D424">
-        <v>1304.2086639382167</v>
+        <v>4768.833500196169</v>
       </c>
     </row>
     <row r="425">
@@ -6427,7 +6427,7 @@
         <v>pending</v>
       </c>
       <c r="D425">
-        <v>2720.62389183393</v>
+        <v>3672.139550796948</v>
       </c>
     </row>
     <row r="426">
@@ -6441,7 +6441,7 @@
         <v>approved</v>
       </c>
       <c r="D426">
-        <v>3365.8077704007205</v>
+        <v>1695.061397921206</v>
       </c>
     </row>
     <row r="427">
@@ -6455,7 +6455,7 @@
         <v>pending</v>
       </c>
       <c r="D427">
-        <v>350.7007447043242</v>
+        <v>3131.5352269953833</v>
       </c>
     </row>
     <row r="428">
@@ -6469,7 +6469,7 @@
         <v>approved</v>
       </c>
       <c r="D428">
-        <v>1035.3494233369431</v>
+        <v>1709.3382056277496</v>
       </c>
     </row>
     <row r="429">
@@ -6483,7 +6483,7 @@
         <v>pending</v>
       </c>
       <c r="D429">
-        <v>2433.114755591235</v>
+        <v>4409.538558882246</v>
       </c>
     </row>
     <row r="430">
@@ -6497,7 +6497,7 @@
         <v>approved</v>
       </c>
       <c r="D430">
-        <v>2787.6214849683533</v>
+        <v>4074.2850311947577</v>
       </c>
     </row>
     <row r="431">
@@ -6511,7 +6511,7 @@
         <v>pending</v>
       </c>
       <c r="D431">
-        <v>4308.8931932949745</v>
+        <v>3486.7658982873418</v>
       </c>
     </row>
     <row r="432">
@@ -6525,7 +6525,7 @@
         <v>approved</v>
       </c>
       <c r="D432">
-        <v>1305.263081886736</v>
+        <v>3720.3561430626464</v>
       </c>
     </row>
     <row r="433">
@@ -6539,7 +6539,7 @@
         <v>pending</v>
       </c>
       <c r="D433">
-        <v>2834.458982890855</v>
+        <v>4742.305870609619</v>
       </c>
     </row>
     <row r="434">
@@ -6553,7 +6553,7 @@
         <v>approved</v>
       </c>
       <c r="D434">
-        <v>366.89624425976564</v>
+        <v>4183.643224012779</v>
       </c>
     </row>
     <row r="435">
@@ -6567,7 +6567,7 @@
         <v>pending</v>
       </c>
       <c r="D435">
-        <v>4431.681859292406</v>
+        <v>1334.117876132206</v>
       </c>
     </row>
     <row r="436">
@@ -6581,7 +6581,7 @@
         <v>approved</v>
       </c>
       <c r="D436">
-        <v>4096.848447627691</v>
+        <v>4515.757833814156</v>
       </c>
     </row>
     <row r="437">
@@ -6595,7 +6595,7 @@
         <v>pending</v>
       </c>
       <c r="D437">
-        <v>4973.644496661319</v>
+        <v>3253.2245058476274</v>
       </c>
     </row>
     <row r="438">
@@ -6609,7 +6609,7 @@
         <v>approved</v>
       </c>
       <c r="D438">
-        <v>3447.2081789460917</v>
+        <v>2446.8620049080546</v>
       </c>
     </row>
     <row r="439">
@@ -6623,7 +6623,7 @@
         <v>pending</v>
       </c>
       <c r="D439">
-        <v>483.7067940172546</v>
+        <v>18.45708850560568</v>
       </c>
     </row>
     <row r="440">
@@ -6637,7 +6637,7 @@
         <v>approved</v>
       </c>
       <c r="D440">
-        <v>3874.9214607946337</v>
+        <v>4822.843399267001</v>
       </c>
     </row>
     <row r="441">
@@ -6651,7 +6651,7 @@
         <v>pending</v>
       </c>
       <c r="D441">
-        <v>2612.2250294412065</v>
+        <v>4242.587795343829</v>
       </c>
     </row>
     <row r="442">
@@ -6665,7 +6665,7 @@
         <v>approved</v>
       </c>
       <c r="D442">
-        <v>2018.703307258246</v>
+        <v>788.7846411119382</v>
       </c>
     </row>
     <row r="443">
@@ -6679,7 +6679,7 @@
         <v>pending</v>
       </c>
       <c r="D443">
-        <v>1362.1584497296924</v>
+        <v>3962.338109321326</v>
       </c>
     </row>
     <row r="444">
@@ -6693,7 +6693,7 @@
         <v>approved</v>
       </c>
       <c r="D444">
-        <v>1831.7440132932672</v>
+        <v>1894.914218506687</v>
       </c>
     </row>
     <row r="445">
@@ -6707,7 +6707,7 @@
         <v>pending</v>
       </c>
       <c r="D445">
-        <v>4909.766845142739</v>
+        <v>1578.257072442264</v>
       </c>
     </row>
     <row r="446">
@@ -6721,7 +6721,7 @@
         <v>approved</v>
       </c>
       <c r="D446">
-        <v>139.10033208187622</v>
+        <v>4572.023069176285</v>
       </c>
     </row>
     <row r="447">
@@ -6735,7 +6735,7 @@
         <v>pending</v>
       </c>
       <c r="D447">
-        <v>19.452563728536987</v>
+        <v>38.83107365504568</v>
       </c>
     </row>
     <row r="448">
@@ -6749,7 +6749,7 @@
         <v>approved</v>
       </c>
       <c r="D448">
-        <v>3178.2237564799943</v>
+        <v>2244.1140400486856</v>
       </c>
     </row>
     <row r="449">
@@ -6763,7 +6763,7 @@
         <v>pending</v>
       </c>
       <c r="D449">
-        <v>540.9662284884142</v>
+        <v>3909.384448087061</v>
       </c>
     </row>
     <row r="450">
@@ -6777,7 +6777,7 @@
         <v>approved</v>
       </c>
       <c r="D450">
-        <v>403.81293197782054</v>
+        <v>255.17029658503776</v>
       </c>
     </row>
     <row r="451">
@@ -6791,7 +6791,7 @@
         <v>pending</v>
       </c>
       <c r="D451">
-        <v>3321.9919470895898</v>
+        <v>1012.7329614255631</v>
       </c>
     </row>
     <row r="452">
@@ -6805,7 +6805,7 @@
         <v>approved</v>
       </c>
       <c r="D452">
-        <v>2159.7944576784566</v>
+        <v>1392.8428143377791</v>
       </c>
     </row>
     <row r="453">
@@ -6819,7 +6819,7 @@
         <v>pending</v>
       </c>
       <c r="D453">
-        <v>769.8070348917496</v>
+        <v>4477.720003999025</v>
       </c>
     </row>
     <row r="454">
@@ -6833,7 +6833,7 @@
         <v>approved</v>
       </c>
       <c r="D454">
-        <v>3767.64210197285</v>
+        <v>2558.5801175984325</v>
       </c>
     </row>
     <row r="455">
@@ -6847,7 +6847,7 @@
         <v>pending</v>
       </c>
       <c r="D455">
-        <v>3488.35786127749</v>
+        <v>4620.19356710199</v>
       </c>
     </row>
     <row r="456">
@@ -6861,7 +6861,7 @@
         <v>approved</v>
       </c>
       <c r="D456">
-        <v>3876.510085607938</v>
+        <v>3474.4023521628233</v>
       </c>
     </row>
     <row r="457">
@@ -6875,7 +6875,7 @@
         <v>pending</v>
       </c>
       <c r="D457">
-        <v>4860.291211447197</v>
+        <v>3989.5442528136396</v>
       </c>
     </row>
     <row r="458">
@@ -6889,7 +6889,7 @@
         <v>approved</v>
       </c>
       <c r="D458">
-        <v>223.1450141533542</v>
+        <v>4488.085863217083</v>
       </c>
     </row>
     <row r="459">
@@ -6903,7 +6903,7 @@
         <v>pending</v>
       </c>
       <c r="D459">
-        <v>4187.734811248549</v>
+        <v>1314.560423560217</v>
       </c>
     </row>
     <row r="460">
@@ -6917,7 +6917,7 @@
         <v>approved</v>
       </c>
       <c r="D460">
-        <v>355.64351638324723</v>
+        <v>4974.479880673713</v>
       </c>
     </row>
     <row r="461">
@@ -6931,7 +6931,7 @@
         <v>pending</v>
       </c>
       <c r="D461">
-        <v>4889.340545141376</v>
+        <v>1506.6879635162156</v>
       </c>
     </row>
     <row r="462">
@@ -6945,7 +6945,7 @@
         <v>approved</v>
       </c>
       <c r="D462">
-        <v>3939.3050265958486</v>
+        <v>4.2168508199547095</v>
       </c>
     </row>
     <row r="463">
@@ -6959,7 +6959,7 @@
         <v>pending</v>
       </c>
       <c r="D463">
-        <v>176.06331711681133</v>
+        <v>3278.5069449084094</v>
       </c>
     </row>
     <row r="464">
@@ -6973,7 +6973,7 @@
         <v>approved</v>
       </c>
       <c r="D464">
-        <v>2174.1197628039968</v>
+        <v>1940.799813505083</v>
       </c>
     </row>
     <row r="465">
@@ -6987,7 +6987,7 @@
         <v>pending</v>
       </c>
       <c r="D465">
-        <v>3941.9738564823792</v>
+        <v>3864.5857604568337</v>
       </c>
     </row>
     <row r="466">
@@ -7001,7 +7001,7 @@
         <v>approved</v>
       </c>
       <c r="D466">
-        <v>4552.385396254689</v>
+        <v>3183.6003193513184</v>
       </c>
     </row>
     <row r="467">
@@ -7015,7 +7015,7 @@
         <v>pending</v>
       </c>
       <c r="D467">
-        <v>2806.775978440994</v>
+        <v>809.7644514827284</v>
       </c>
     </row>
     <row r="468">
@@ -7029,7 +7029,7 @@
         <v>approved</v>
       </c>
       <c r="D468">
-        <v>2025.3068233781835</v>
+        <v>3713.8075854495787</v>
       </c>
     </row>
     <row r="469">
@@ -7043,7 +7043,7 @@
         <v>pending</v>
       </c>
       <c r="D469">
-        <v>547.9246099579404</v>
+        <v>4027.007430546581</v>
       </c>
     </row>
     <row r="470">
@@ -7057,7 +7057,7 @@
         <v>approved</v>
       </c>
       <c r="D470">
-        <v>844.6939673781828</v>
+        <v>750.607453275629</v>
       </c>
     </row>
     <row r="471">
@@ -7071,7 +7071,7 @@
         <v>pending</v>
       </c>
       <c r="D471">
-        <v>961.5463158970816</v>
+        <v>75.28002281417923</v>
       </c>
     </row>
     <row r="472">
@@ -7085,7 +7085,7 @@
         <v>approved</v>
       </c>
       <c r="D472">
-        <v>2057.432800826264</v>
+        <v>1697.588831578729</v>
       </c>
     </row>
     <row r="473">
@@ -7099,7 +7099,7 @@
         <v>pending</v>
       </c>
       <c r="D473">
-        <v>3790.2835628135967</v>
+        <v>2252.2378861386705</v>
       </c>
     </row>
     <row r="474">
@@ -7113,7 +7113,7 @@
         <v>approved</v>
       </c>
       <c r="D474">
-        <v>4680.621784378999</v>
+        <v>3623.590237085896</v>
       </c>
     </row>
     <row r="475">
@@ -7127,7 +7127,7 @@
         <v>pending</v>
       </c>
       <c r="D475">
-        <v>314.80207497122325</v>
+        <v>1644.2535048598838</v>
       </c>
     </row>
     <row r="476">
@@ -7141,7 +7141,7 @@
         <v>approved</v>
       </c>
       <c r="D476">
-        <v>944.1011024778834</v>
+        <v>4019.0304080793203</v>
       </c>
     </row>
     <row r="477">
@@ -7155,7 +7155,7 @@
         <v>pending</v>
       </c>
       <c r="D477">
-        <v>4037.1489128579465</v>
+        <v>325.35108098779574</v>
       </c>
     </row>
     <row r="478">
@@ -7169,7 +7169,7 @@
         <v>approved</v>
       </c>
       <c r="D478">
-        <v>1029.718989429631</v>
+        <v>124.1879798716039</v>
       </c>
     </row>
     <row r="479">
@@ -7183,7 +7183,7 @@
         <v>pending</v>
       </c>
       <c r="D479">
-        <v>3038.7159474639525</v>
+        <v>159.55693751393608</v>
       </c>
     </row>
     <row r="480">
@@ -7197,7 +7197,7 @@
         <v>approved</v>
       </c>
       <c r="D480">
-        <v>1407.3907750122728</v>
+        <v>1203.2772319346495</v>
       </c>
     </row>
     <row r="481">
@@ -7211,7 +7211,7 @@
         <v>pending</v>
       </c>
       <c r="D481">
-        <v>2614.598475097568</v>
+        <v>3815.5507830011493</v>
       </c>
     </row>
     <row r="482">
@@ -7225,7 +7225,7 @@
         <v>approved</v>
       </c>
       <c r="D482">
-        <v>3869.4739616538855</v>
+        <v>4381.496977492847</v>
       </c>
     </row>
     <row r="483">
@@ -7239,7 +7239,7 @@
         <v>pending</v>
       </c>
       <c r="D483">
-        <v>4851.767261669554</v>
+        <v>3300.093738297799</v>
       </c>
     </row>
     <row r="484">
@@ -7253,7 +7253,7 @@
         <v>approved</v>
       </c>
       <c r="D484">
-        <v>604.5270723493745</v>
+        <v>4325.480809975505</v>
       </c>
     </row>
     <row r="485">
@@ -7267,7 +7267,7 @@
         <v>pending</v>
       </c>
       <c r="D485">
-        <v>4064.0170651856542</v>
+        <v>4380.3933769825635</v>
       </c>
     </row>
     <row r="486">
@@ -7281,7 +7281,7 @@
         <v>approved</v>
       </c>
       <c r="D486">
-        <v>1405.829510425195</v>
+        <v>3469.8984320218683</v>
       </c>
     </row>
     <row r="487">
@@ -7295,7 +7295,7 @@
         <v>pending</v>
       </c>
       <c r="D487">
-        <v>2348.824105386784</v>
+        <v>1278.2234340540122</v>
       </c>
     </row>
     <row r="488">
@@ -7309,7 +7309,7 @@
         <v>approved</v>
       </c>
       <c r="D488">
-        <v>4258.343516249523</v>
+        <v>2833.401192408669</v>
       </c>
     </row>
     <row r="489">
@@ -7323,7 +7323,7 @@
         <v>pending</v>
       </c>
       <c r="D489">
-        <v>3302.4382854783976</v>
+        <v>3017.875130495553</v>
       </c>
     </row>
     <row r="490">
@@ -7337,7 +7337,7 @@
         <v>approved</v>
       </c>
       <c r="D490">
-        <v>4381.35837030257</v>
+        <v>1631.4568186294675</v>
       </c>
     </row>
     <row r="491">
@@ -7351,7 +7351,7 @@
         <v>pending</v>
       </c>
       <c r="D491">
-        <v>3194.9775918109844</v>
+        <v>196.88294051552145</v>
       </c>
     </row>
     <row r="492">
@@ -7365,7 +7365,7 @@
         <v>approved</v>
       </c>
       <c r="D492">
-        <v>3495.488628983069</v>
+        <v>1371.9177983641994</v>
       </c>
     </row>
     <row r="493">
@@ -7379,7 +7379,7 @@
         <v>pending</v>
       </c>
       <c r="D493">
-        <v>2986.5153447866655</v>
+        <v>1857.5811832944423</v>
       </c>
     </row>
     <row r="494">
@@ -7393,7 +7393,7 @@
         <v>approved</v>
       </c>
       <c r="D494">
-        <v>499.4900233778432</v>
+        <v>723.7937998707966</v>
       </c>
     </row>
     <row r="495">
@@ -7407,7 +7407,7 @@
         <v>pending</v>
       </c>
       <c r="D495">
-        <v>4067.2852501009825</v>
+        <v>2575.140526358839</v>
       </c>
     </row>
     <row r="496">
@@ -7421,7 +7421,7 @@
         <v>approved</v>
       </c>
       <c r="D496">
-        <v>4963.384996045842</v>
+        <v>1996.8967161175021</v>
       </c>
     </row>
     <row r="497">
@@ -7435,7 +7435,7 @@
         <v>pending</v>
       </c>
       <c r="D497">
-        <v>2043.2032796278831</v>
+        <v>461.44184253646193</v>
       </c>
     </row>
     <row r="498">
@@ -7449,7 +7449,7 @@
         <v>approved</v>
       </c>
       <c r="D498">
-        <v>4247.988052118544</v>
+        <v>4584.97202807456</v>
       </c>
     </row>
     <row r="499">
@@ -7463,7 +7463,7 @@
         <v>pending</v>
       </c>
       <c r="D499">
-        <v>4710.045607683224</v>
+        <v>4951.987864723021</v>
       </c>
     </row>
     <row r="500">
@@ -7477,7 +7477,7 @@
         <v>approved</v>
       </c>
       <c r="D500">
-        <v>2264.297818093962</v>
+        <v>808.2140939581284</v>
       </c>
     </row>
     <row r="501">
@@ -7491,7 +7491,7 @@
         <v>pending</v>
       </c>
       <c r="D501">
-        <v>908.1564394566777</v>
+        <v>431.3437710334789</v>
       </c>
     </row>
     <row r="502">
@@ -7505,7 +7505,7 @@
         <v>approved</v>
       </c>
       <c r="D502">
-        <v>144.53789910176317</v>
+        <v>757.7944400721904</v>
       </c>
     </row>
     <row r="503">
@@ -7519,7 +7519,7 @@
         <v>pending</v>
       </c>
       <c r="D503">
-        <v>3416.4086169269012</v>
+        <v>1707.9391509054565</v>
       </c>
     </row>
     <row r="504">
@@ -7533,7 +7533,7 @@
         <v>approved</v>
       </c>
       <c r="D504">
-        <v>3863.538755954662</v>
+        <v>3827.07816152686</v>
       </c>
     </row>
     <row r="505">
@@ -7547,7 +7547,7 @@
         <v>pending</v>
       </c>
       <c r="D505">
-        <v>462.9900971402101</v>
+        <v>1450.8192957912192</v>
       </c>
     </row>
     <row r="506">
@@ -7561,7 +7561,7 @@
         <v>approved</v>
       </c>
       <c r="D506">
-        <v>412.7352108938209</v>
+        <v>371.0845747792435</v>
       </c>
     </row>
     <row r="507">
@@ -7575,7 +7575,7 @@
         <v>pending</v>
       </c>
       <c r="D507">
-        <v>3830.978736952335</v>
+        <v>159.7245424128757</v>
       </c>
     </row>
     <row r="508">
@@ -7589,7 +7589,7 @@
         <v>approved</v>
       </c>
       <c r="D508">
-        <v>2324.705510424251</v>
+        <v>4782.394724985975</v>
       </c>
     </row>
     <row r="509">
@@ -7603,7 +7603,7 @@
         <v>pending</v>
       </c>
       <c r="D509">
-        <v>2593.8249936606585</v>
+        <v>2343.01062999713</v>
       </c>
     </row>
     <row r="510">
@@ -7617,7 +7617,7 @@
         <v>approved</v>
       </c>
       <c r="D510">
-        <v>2694.2553981821525</v>
+        <v>2304.041364352708</v>
       </c>
     </row>
     <row r="511">
@@ -7631,7 +7631,7 @@
         <v>pending</v>
       </c>
       <c r="D511">
-        <v>260.27798751265595</v>
+        <v>209.49902180504188</v>
       </c>
     </row>
     <row r="512">
@@ -7645,7 +7645,7 @@
         <v>approved</v>
       </c>
       <c r="D512">
-        <v>2113.981788547912</v>
+        <v>4823.636137208186</v>
       </c>
     </row>
     <row r="513">
@@ -7659,7 +7659,7 @@
         <v>pending</v>
       </c>
       <c r="D513">
-        <v>3951.8676214560655</v>
+        <v>414.214677774708</v>
       </c>
     </row>
     <row r="514">
@@ -7673,7 +7673,7 @@
         <v>approved</v>
       </c>
       <c r="D514">
-        <v>1795.518988582233</v>
+        <v>4468.270556641058</v>
       </c>
     </row>
     <row r="515">
@@ -7687,7 +7687,7 @@
         <v>pending</v>
       </c>
       <c r="D515">
-        <v>4299.9537605260575</v>
+        <v>1460.3339024250206</v>
       </c>
     </row>
     <row r="516">
@@ -7701,7 +7701,7 @@
         <v>approved</v>
       </c>
       <c r="D516">
-        <v>3467.189795947222</v>
+        <v>2295.818840011131</v>
       </c>
     </row>
     <row r="517">
@@ -7715,7 +7715,7 @@
         <v>pending</v>
       </c>
       <c r="D517">
-        <v>3505.929629733433</v>
+        <v>986.5200840952104</v>
       </c>
     </row>
     <row r="518">
@@ -7729,7 +7729,7 @@
         <v>approved</v>
       </c>
       <c r="D518">
-        <v>3301.527898402329</v>
+        <v>4257.0278770000805</v>
       </c>
     </row>
     <row r="519">
@@ -7743,7 +7743,7 @@
         <v>pending</v>
       </c>
       <c r="D519">
-        <v>4131.017795400427</v>
+        <v>2623.878375461162</v>
       </c>
     </row>
     <row r="520">
@@ -7757,7 +7757,7 @@
         <v>approved</v>
       </c>
       <c r="D520">
-        <v>4484.897030448228</v>
+        <v>834.9790921974065</v>
       </c>
     </row>
     <row r="521">
@@ -7771,7 +7771,7 @@
         <v>pending</v>
       </c>
       <c r="D521">
-        <v>851.5918947116219</v>
+        <v>779.5623212425573</v>
       </c>
     </row>
     <row r="522">
@@ -7785,7 +7785,7 @@
         <v>approved</v>
       </c>
       <c r="D522">
-        <v>4851.780660252717</v>
+        <v>1334.195307920678</v>
       </c>
     </row>
     <row r="523">
@@ -7799,7 +7799,7 @@
         <v>pending</v>
       </c>
       <c r="D523">
-        <v>4558.8083439532265</v>
+        <v>3819.2800436292273</v>
       </c>
     </row>
     <row r="524">
@@ -7813,7 +7813,7 @@
         <v>approved</v>
       </c>
       <c r="D524">
-        <v>2909.7733040774065</v>
+        <v>3038.929170762409</v>
       </c>
     </row>
     <row r="525">
@@ -7827,7 +7827,7 @@
         <v>pending</v>
       </c>
       <c r="D525">
-        <v>1920.2370191043506</v>
+        <v>3467.960901513383</v>
       </c>
     </row>
     <row r="526">
@@ -7841,7 +7841,7 @@
         <v>approved</v>
       </c>
       <c r="D526">
-        <v>341.6799936176207</v>
+        <v>2416.470836921164</v>
       </c>
     </row>
     <row r="527">
@@ -7855,7 +7855,7 @@
         <v>pending</v>
       </c>
       <c r="D527">
-        <v>1710.1819175975008</v>
+        <v>3100.5634845653717</v>
       </c>
     </row>
     <row r="528">
@@ -7869,7 +7869,7 @@
         <v>approved</v>
       </c>
       <c r="D528">
-        <v>3257.1893190222722</v>
+        <v>2262.625449495896</v>
       </c>
     </row>
     <row r="529">
@@ -7883,7 +7883,7 @@
         <v>pending</v>
       </c>
       <c r="D529">
-        <v>1457.6850736307433</v>
+        <v>1727.2983237435203</v>
       </c>
     </row>
     <row r="530">
@@ -7897,7 +7897,7 @@
         <v>approved</v>
       </c>
       <c r="D530">
-        <v>2212.0747648742044</v>
+        <v>83.78636065138222</v>
       </c>
     </row>
     <row r="531">
@@ -7911,7 +7911,7 @@
         <v>pending</v>
       </c>
       <c r="D531">
-        <v>2742.1478729756923</v>
+        <v>2478.980503132654</v>
       </c>
     </row>
     <row r="532">
@@ -7925,7 +7925,7 @@
         <v>approved</v>
       </c>
       <c r="D532">
-        <v>3032.9068899975964</v>
+        <v>3506.109586789448</v>
       </c>
     </row>
     <row r="533">
@@ -7939,7 +7939,7 @@
         <v>pending</v>
       </c>
       <c r="D533">
-        <v>3457.430391938322</v>
+        <v>1627.9015648469097</v>
       </c>
     </row>
     <row r="534">
@@ -7953,7 +7953,7 @@
         <v>approved</v>
       </c>
       <c r="D534">
-        <v>730.1581259486256</v>
+        <v>3047.2597406971913</v>
       </c>
     </row>
     <row r="535">
@@ -7967,7 +7967,7 @@
         <v>pending</v>
       </c>
       <c r="D535">
-        <v>3058.804890565464</v>
+        <v>4822.465911759658</v>
       </c>
     </row>
     <row r="536">
@@ -7981,7 +7981,7 @@
         <v>approved</v>
       </c>
       <c r="D536">
-        <v>959.9313345855531</v>
+        <v>3980.67452278406</v>
       </c>
     </row>
     <row r="537">
@@ -7995,7 +7995,7 @@
         <v>pending</v>
       </c>
       <c r="D537">
-        <v>213.76171916794084</v>
+        <v>1301.2871135139437</v>
       </c>
     </row>
     <row r="538">
@@ -8009,7 +8009,7 @@
         <v>approved</v>
       </c>
       <c r="D538">
-        <v>2955.5199586807003</v>
+        <v>343.178270823975</v>
       </c>
     </row>
     <row r="539">
@@ -8023,7 +8023,7 @@
         <v>pending</v>
       </c>
       <c r="D539">
-        <v>4220.781488635637</v>
+        <v>490.61554058940084</v>
       </c>
     </row>
     <row r="540">
@@ -8037,7 +8037,7 @@
         <v>approved</v>
       </c>
       <c r="D540">
-        <v>836.020944461372</v>
+        <v>3473.6178660193873</v>
       </c>
     </row>
     <row r="541">
@@ -8051,7 +8051,7 @@
         <v>pending</v>
       </c>
       <c r="D541">
-        <v>2295.3859141958387</v>
+        <v>176.5338373521852</v>
       </c>
     </row>
     <row r="542">
@@ -8065,7 +8065,7 @@
         <v>approved</v>
       </c>
       <c r="D542">
-        <v>3898.3056528014004</v>
+        <v>610.6845465977195</v>
       </c>
     </row>
     <row r="543">
@@ -8079,7 +8079,7 @@
         <v>pending</v>
       </c>
       <c r="D543">
-        <v>3542.614000474026</v>
+        <v>610.1626377499236</v>
       </c>
     </row>
     <row r="544">
@@ -8093,7 +8093,7 @@
         <v>approved</v>
       </c>
       <c r="D544">
-        <v>1382.5292611653595</v>
+        <v>525.1134061393014</v>
       </c>
     </row>
     <row r="545">
@@ -8107,7 +8107,7 @@
         <v>pending</v>
       </c>
       <c r="D545">
-        <v>3420.7936296084927</v>
+        <v>4032.857892200118</v>
       </c>
     </row>
     <row r="546">
@@ -8121,7 +8121,7 @@
         <v>approved</v>
       </c>
       <c r="D546">
-        <v>3017.1677181258938</v>
+        <v>139.99272999393742</v>
       </c>
     </row>
     <row r="547">
@@ -8135,7 +8135,7 @@
         <v>pending</v>
       </c>
       <c r="D547">
-        <v>3229.7870889575343</v>
+        <v>3388.8270818350575</v>
       </c>
     </row>
     <row r="548">
@@ -8149,7 +8149,7 @@
         <v>approved</v>
       </c>
       <c r="D548">
-        <v>1504.3285166256692</v>
+        <v>93.13206752293301</v>
       </c>
     </row>
     <row r="549">
@@ -8163,7 +8163,7 @@
         <v>pending</v>
       </c>
       <c r="D549">
-        <v>1334.9197339404607</v>
+        <v>2166.9624925209773</v>
       </c>
     </row>
     <row r="550">
@@ -8177,7 +8177,7 @@
         <v>approved</v>
       </c>
       <c r="D550">
-        <v>40.385749433478054</v>
+        <v>4471.379255055964</v>
       </c>
     </row>
     <row r="551">
@@ -8191,7 +8191,7 @@
         <v>pending</v>
       </c>
       <c r="D551">
-        <v>2139.862281691699</v>
+        <v>4737.177771957424</v>
       </c>
     </row>
     <row r="552">
@@ -8205,7 +8205,7 @@
         <v>approved</v>
       </c>
       <c r="D552">
-        <v>1051.7188028451274</v>
+        <v>3830.916775050257</v>
       </c>
     </row>
     <row r="553">
@@ -8219,7 +8219,7 @@
         <v>pending</v>
       </c>
       <c r="D553">
-        <v>2409.610233822779</v>
+        <v>982.3721761088755</v>
       </c>
     </row>
     <row r="554">
@@ -8233,7 +8233,7 @@
         <v>approved</v>
       </c>
       <c r="D554">
-        <v>1357.9553621906982</v>
+        <v>4143.647631420493</v>
       </c>
     </row>
     <row r="555">
@@ -8247,7 +8247,7 @@
         <v>pending</v>
       </c>
       <c r="D555">
-        <v>2027.9993700090272</v>
+        <v>2022.282783598125</v>
       </c>
     </row>
     <row r="556">
@@ -8261,7 +8261,7 @@
         <v>approved</v>
       </c>
       <c r="D556">
-        <v>3188.6086307078544</v>
+        <v>3846.3941012993664</v>
       </c>
     </row>
     <row r="557">
@@ -8275,7 +8275,7 @@
         <v>pending</v>
       </c>
       <c r="D557">
-        <v>1087.08051135047</v>
+        <v>394.1629624300802</v>
       </c>
     </row>
     <row r="558">
@@ -8289,7 +8289,7 @@
         <v>approved</v>
       </c>
       <c r="D558">
-        <v>382.4630553970365</v>
+        <v>1358.7290340327152</v>
       </c>
     </row>
     <row r="559">
@@ -8303,7 +8303,7 @@
         <v>pending</v>
       </c>
       <c r="D559">
-        <v>1268.2839595267549</v>
+        <v>578.14370658693</v>
       </c>
     </row>
     <row r="560">
@@ -8317,7 +8317,7 @@
         <v>approved</v>
       </c>
       <c r="D560">
-        <v>2676.5542347918313</v>
+        <v>2950.1824430596403</v>
       </c>
     </row>
     <row r="561">
@@ -8331,7 +8331,7 @@
         <v>pending</v>
       </c>
       <c r="D561">
-        <v>4046.2309280622444</v>
+        <v>3199.213839484435</v>
       </c>
     </row>
     <row r="562">
@@ -8345,7 +8345,7 @@
         <v>approved</v>
       </c>
       <c r="D562">
-        <v>1532.8562454279127</v>
+        <v>807.5541946960285</v>
       </c>
     </row>
     <row r="563">
@@ -8359,7 +8359,7 @@
         <v>pending</v>
       </c>
       <c r="D563">
-        <v>4061.0613272003425</v>
+        <v>4489.721318928586</v>
       </c>
     </row>
     <row r="564">
@@ -8373,7 +8373,7 @@
         <v>approved</v>
       </c>
       <c r="D564">
-        <v>268.80714188676103</v>
+        <v>2504.16177486386</v>
       </c>
     </row>
     <row r="565">
@@ -8387,7 +8387,7 @@
         <v>pending</v>
       </c>
       <c r="D565">
-        <v>4471.9536016851025</v>
+        <v>2254.2536782921275</v>
       </c>
     </row>
     <row r="566">
@@ -8401,7 +8401,7 @@
         <v>approved</v>
       </c>
       <c r="D566">
-        <v>3546.0694803167057</v>
+        <v>3616.712266675448</v>
       </c>
     </row>
     <row r="567">
@@ -8415,7 +8415,7 @@
         <v>pending</v>
       </c>
       <c r="D567">
-        <v>3357.6905600786076</v>
+        <v>3055.097065350093</v>
       </c>
     </row>
     <row r="568">
@@ -8429,7 +8429,7 @@
         <v>approved</v>
       </c>
       <c r="D568">
-        <v>1857.9669326419723</v>
+        <v>4730.772281618665</v>
       </c>
     </row>
     <row r="569">
@@ -8443,7 +8443,7 @@
         <v>pending</v>
       </c>
       <c r="D569">
-        <v>3191.7508496896708</v>
+        <v>3489.3088717563946</v>
       </c>
     </row>
     <row r="570">
@@ -8457,7 +8457,7 @@
         <v>approved</v>
       </c>
       <c r="D570">
-        <v>4850.800642946075</v>
+        <v>1433.6723321270872</v>
       </c>
     </row>
     <row r="571">
@@ -8471,7 +8471,7 @@
         <v>pending</v>
       </c>
       <c r="D571">
-        <v>4965.621617264172</v>
+        <v>4259.625752090631</v>
       </c>
     </row>
     <row r="572">
@@ -8485,7 +8485,7 @@
         <v>approved</v>
       </c>
       <c r="D572">
-        <v>4416.369135717257</v>
+        <v>4128.883034199878</v>
       </c>
     </row>
     <row r="573">
@@ -8499,7 +8499,7 @@
         <v>pending</v>
       </c>
       <c r="D573">
-        <v>2098.656574533573</v>
+        <v>4744.335998777193</v>
       </c>
     </row>
     <row r="574">
@@ -8513,7 +8513,7 @@
         <v>approved</v>
       </c>
       <c r="D574">
-        <v>4010.089198681861</v>
+        <v>1581.1225433837494</v>
       </c>
     </row>
     <row r="575">
@@ -8527,7 +8527,7 @@
         <v>pending</v>
       </c>
       <c r="D575">
-        <v>2877.2778563491797</v>
+        <v>1655.7663466190274</v>
       </c>
     </row>
     <row r="576">
@@ -8541,7 +8541,7 @@
         <v>approved</v>
       </c>
       <c r="D576">
-        <v>2626.6556058198785</v>
+        <v>4794.713224538429</v>
       </c>
     </row>
     <row r="577">
@@ -8555,7 +8555,7 @@
         <v>pending</v>
       </c>
       <c r="D577">
-        <v>1039.629653312174</v>
+        <v>2839.98977585009</v>
       </c>
     </row>
     <row r="578">
@@ -8569,7 +8569,7 @@
         <v>approved</v>
       </c>
       <c r="D578">
-        <v>3923.391391638754</v>
+        <v>1200.2625162240965</v>
       </c>
     </row>
     <row r="579">
@@ -8583,7 +8583,7 @@
         <v>pending</v>
       </c>
       <c r="D579">
-        <v>3918.632989445925</v>
+        <v>10.826393426751624</v>
       </c>
     </row>
     <row r="580">
@@ -8597,7 +8597,7 @@
         <v>approved</v>
       </c>
       <c r="D580">
-        <v>793.6264036184626</v>
+        <v>2176.367236752188</v>
       </c>
     </row>
     <row r="581">
@@ -8611,7 +8611,7 @@
         <v>pending</v>
       </c>
       <c r="D581">
-        <v>937.6077726613929</v>
+        <v>4777.607683779875</v>
       </c>
     </row>
     <row r="582">
@@ -8625,7 +8625,7 @@
         <v>approved</v>
       </c>
       <c r="D582">
-        <v>2465.166688381948</v>
+        <v>4406.419085358047</v>
       </c>
     </row>
     <row r="583">
@@ -8639,7 +8639,7 @@
         <v>pending</v>
       </c>
       <c r="D583">
-        <v>4237.922185106244</v>
+        <v>1316.107712670267</v>
       </c>
     </row>
     <row r="584">
@@ -8653,7 +8653,7 @@
         <v>approved</v>
       </c>
       <c r="D584">
-        <v>1408.4755974305597</v>
+        <v>4039.483322227891</v>
       </c>
     </row>
     <row r="585">
@@ -8667,7 +8667,7 @@
         <v>pending</v>
       </c>
       <c r="D585">
-        <v>1647.367339450877</v>
+        <v>947.3238819979413</v>
       </c>
     </row>
     <row r="586">
@@ -8681,7 +8681,7 @@
         <v>approved</v>
       </c>
       <c r="D586">
-        <v>2527.4095617553394</v>
+        <v>1928.7351439083168</v>
       </c>
     </row>
     <row r="587">
@@ -8695,7 +8695,7 @@
         <v>pending</v>
       </c>
       <c r="D587">
-        <v>1778.2649728487265</v>
+        <v>3216.2463453573964</v>
       </c>
     </row>
     <row r="588">
@@ -8709,7 +8709,7 @@
         <v>approved</v>
       </c>
       <c r="D588">
-        <v>4418.0209756529875</v>
+        <v>293.6916271818413</v>
       </c>
     </row>
     <row r="589">
@@ -8723,7 +8723,7 @@
         <v>pending</v>
       </c>
       <c r="D589">
-        <v>1111.3050623108045</v>
+        <v>1042.2811633880458</v>
       </c>
     </row>
     <row r="590">
@@ -8737,7 +8737,7 @@
         <v>approved</v>
       </c>
       <c r="D590">
-        <v>1912.0584316276768</v>
+        <v>3226.37952723009</v>
       </c>
     </row>
     <row r="591">
@@ -8751,7 +8751,7 @@
         <v>pending</v>
       </c>
       <c r="D591">
-        <v>3772.0761265048654</v>
+        <v>4053.690060694657</v>
       </c>
     </row>
     <row r="592">
@@ -8765,7 +8765,7 @@
         <v>approved</v>
       </c>
       <c r="D592">
-        <v>3783.2566384835363</v>
+        <v>4516.429634547945</v>
       </c>
     </row>
     <row r="593">
@@ -8779,7 +8779,7 @@
         <v>pending</v>
       </c>
       <c r="D593">
-        <v>1859.007104620687</v>
+        <v>675.9101389107446</v>
       </c>
     </row>
     <row r="594">
@@ -8793,7 +8793,7 @@
         <v>approved</v>
       </c>
       <c r="D594">
-        <v>1897.5853913235185</v>
+        <v>214.55217002519623</v>
       </c>
     </row>
     <row r="595">
@@ -8807,7 +8807,7 @@
         <v>pending</v>
       </c>
       <c r="D595">
-        <v>4831.103555300366</v>
+        <v>3075.2198143906217</v>
       </c>
     </row>
     <row r="596">
@@ -8821,7 +8821,7 @@
         <v>approved</v>
       </c>
       <c r="D596">
-        <v>1667.8927910751506</v>
+        <v>2517.936880221655</v>
       </c>
     </row>
     <row r="597">
@@ -8835,7 +8835,7 @@
         <v>pending</v>
       </c>
       <c r="D597">
-        <v>299.1638645309624</v>
+        <v>2752.0630170990944</v>
       </c>
     </row>
     <row r="598">
@@ -8849,7 +8849,7 @@
         <v>approved</v>
       </c>
       <c r="D598">
-        <v>2412.719805110779</v>
+        <v>620.042131520756</v>
       </c>
     </row>
     <row r="599">
@@ -8863,7 +8863,7 @@
         <v>pending</v>
       </c>
       <c r="D599">
-        <v>1800.7905243790112</v>
+        <v>2567.4128908850425</v>
       </c>
     </row>
     <row r="600">
@@ -8877,7 +8877,7 @@
         <v>approved</v>
       </c>
       <c r="D600">
-        <v>3448.7912598046555</v>
+        <v>4036.921454793929</v>
       </c>
     </row>
     <row r="601">
@@ -8891,7 +8891,7 @@
         <v>pending</v>
       </c>
       <c r="D601">
-        <v>1.736238392412437</v>
+        <v>1430.5436727357212</v>
       </c>
     </row>
     <row r="602">
@@ -8905,7 +8905,7 @@
         <v>approved</v>
       </c>
       <c r="D602">
-        <v>1579.2059162010275</v>
+        <v>3253.5553749364685</v>
       </c>
     </row>
     <row r="603">
@@ -8919,7 +8919,7 @@
         <v>pending</v>
       </c>
       <c r="D603">
-        <v>3509.164385971518</v>
+        <v>2469.781380722813</v>
       </c>
     </row>
     <row r="604">
@@ -8933,7 +8933,7 @@
         <v>approved</v>
       </c>
       <c r="D604">
-        <v>394.9761187760881</v>
+        <v>2821.4915296427134</v>
       </c>
     </row>
     <row r="605">
@@ -8947,7 +8947,7 @@
         <v>pending</v>
       </c>
       <c r="D605">
-        <v>1440.5643528495993</v>
+        <v>1190.9263278353133</v>
       </c>
     </row>
     <row r="606">
@@ -8961,7 +8961,7 @@
         <v>approved</v>
       </c>
       <c r="D606">
-        <v>3325.8020685670854</v>
+        <v>3150.271805416458</v>
       </c>
     </row>
     <row r="607">
@@ -8975,7 +8975,7 @@
         <v>pending</v>
       </c>
       <c r="D607">
-        <v>4854.4759187902255</v>
+        <v>479.3754341653855</v>
       </c>
     </row>
     <row r="608">
@@ -8989,7 +8989,7 @@
         <v>approved</v>
       </c>
       <c r="D608">
-        <v>1300.8451841709468</v>
+        <v>2395.493247077611</v>
       </c>
     </row>
     <row r="609">
@@ -9003,7 +9003,7 @@
         <v>pending</v>
       </c>
       <c r="D609">
-        <v>942.0481561132765</v>
+        <v>2281.395250210695</v>
       </c>
     </row>
     <row r="610">
@@ -9017,7 +9017,7 @@
         <v>approved</v>
       </c>
       <c r="D610">
-        <v>3942.5586058696317</v>
+        <v>3414.7522615723515</v>
       </c>
     </row>
     <row r="611">
@@ -9031,7 +9031,7 @@
         <v>pending</v>
       </c>
       <c r="D611">
-        <v>1375.5629946331937</v>
+        <v>4678.955798836318</v>
       </c>
     </row>
     <row r="612">
@@ -9045,7 +9045,7 @@
         <v>approved</v>
       </c>
       <c r="D612">
-        <v>344.13255322743083</v>
+        <v>650.4454464488218</v>
       </c>
     </row>
     <row r="613">
@@ -9059,7 +9059,7 @@
         <v>pending</v>
       </c>
       <c r="D613">
-        <v>502.202097022999</v>
+        <v>2380.0752847636854</v>
       </c>
     </row>
     <row r="614">
@@ -9073,7 +9073,7 @@
         <v>approved</v>
       </c>
       <c r="D614">
-        <v>277.38095751714263</v>
+        <v>3392.3929676661423</v>
       </c>
     </row>
     <row r="615">
@@ -9087,7 +9087,7 @@
         <v>pending</v>
       </c>
       <c r="D615">
-        <v>3965.4134877740044</v>
+        <v>3446.293706364909</v>
       </c>
     </row>
     <row r="616">
@@ -9101,7 +9101,7 @@
         <v>approved</v>
       </c>
       <c r="D616">
-        <v>926.9648284071075</v>
+        <v>389.2404171195074</v>
       </c>
     </row>
     <row r="617">
@@ -9115,7 +9115,7 @@
         <v>pending</v>
       </c>
       <c r="D617">
-        <v>3198.5046148621454</v>
+        <v>3191.8013118171407</v>
       </c>
     </row>
     <row r="618">
@@ -9129,7 +9129,7 @@
         <v>approved</v>
       </c>
       <c r="D618">
-        <v>372.6515910484829</v>
+        <v>2219.617220424721</v>
       </c>
     </row>
     <row r="619">
@@ -9143,7 +9143,7 @@
         <v>pending</v>
       </c>
       <c r="D619">
-        <v>2020.020987216158</v>
+        <v>3353.8696017863867</v>
       </c>
     </row>
     <row r="620">
@@ -9157,7 +9157,7 @@
         <v>approved</v>
       </c>
       <c r="D620">
-        <v>4658.713939065165</v>
+        <v>556.5737337413112</v>
       </c>
     </row>
     <row r="621">
@@ -9171,7 +9171,7 @@
         <v>pending</v>
       </c>
       <c r="D621">
-        <v>2649.170791901826</v>
+        <v>1338.1081523611538</v>
       </c>
     </row>
     <row r="622">
@@ -9185,7 +9185,7 @@
         <v>approved</v>
       </c>
       <c r="D622">
-        <v>3948.5261660564643</v>
+        <v>773.267145953822</v>
       </c>
     </row>
     <row r="623">
@@ -9199,7 +9199,7 @@
         <v>pending</v>
       </c>
       <c r="D623">
-        <v>3061.926256162054</v>
+        <v>3782.8137278322747</v>
       </c>
     </row>
     <row r="624">
@@ -9213,7 +9213,7 @@
         <v>approved</v>
       </c>
       <c r="D624">
-        <v>2578.3591413017625</v>
+        <v>4646.360901806415</v>
       </c>
     </row>
     <row r="625">
@@ -9227,7 +9227,7 @@
         <v>pending</v>
       </c>
       <c r="D625">
-        <v>2567.4257327555038</v>
+        <v>1089.7434398223504</v>
       </c>
     </row>
     <row r="626">
@@ -9241,7 +9241,7 @@
         <v>approved</v>
       </c>
       <c r="D626">
-        <v>1252.2365325776796</v>
+        <v>3367.4993884564874</v>
       </c>
     </row>
     <row r="627">
@@ -9255,7 +9255,7 @@
         <v>pending</v>
       </c>
       <c r="D627">
-        <v>1997.3776609818583</v>
+        <v>2411.5245809034345</v>
       </c>
     </row>
     <row r="628">
@@ -9269,7 +9269,7 @@
         <v>approved</v>
       </c>
       <c r="D628">
-        <v>2298.835711353899</v>
+        <v>419.45323911566913</v>
       </c>
     </row>
     <row r="629">
@@ -9283,7 +9283,7 @@
         <v>pending</v>
       </c>
       <c r="D629">
-        <v>1031.5383392283995</v>
+        <v>2598.730276946901</v>
       </c>
     </row>
     <row r="630">
@@ -9297,7 +9297,7 @@
         <v>approved</v>
       </c>
       <c r="D630">
-        <v>2752.5048273523744</v>
+        <v>1645.4802553211234</v>
       </c>
     </row>
     <row r="631">
@@ -9311,7 +9311,7 @@
         <v>pending</v>
       </c>
       <c r="D631">
-        <v>2731.0873286615424</v>
+        <v>1377.9691414359963</v>
       </c>
     </row>
     <row r="632">
@@ -9325,7 +9325,7 @@
         <v>approved</v>
       </c>
       <c r="D632">
-        <v>4128.312963074091</v>
+        <v>298.40476335933676</v>
       </c>
     </row>
     <row r="633">
@@ -9339,7 +9339,7 @@
         <v>pending</v>
       </c>
       <c r="D633">
-        <v>2871.1091250662034</v>
+        <v>4610.982923469703</v>
       </c>
     </row>
     <row r="634">
@@ -9353,7 +9353,7 @@
         <v>approved</v>
       </c>
       <c r="D634">
-        <v>185.39266925893915</v>
+        <v>1727.7066296744993</v>
       </c>
     </row>
     <row r="635">
@@ -9367,7 +9367,7 @@
         <v>pending</v>
       </c>
       <c r="D635">
-        <v>1594.3466403126527</v>
+        <v>146.4579699636015</v>
       </c>
     </row>
     <row r="636">
@@ -9381,7 +9381,7 @@
         <v>approved</v>
       </c>
       <c r="D636">
-        <v>689.6659628834645</v>
+        <v>253.27225213335635</v>
       </c>
     </row>
     <row r="637">
@@ -9395,7 +9395,7 @@
         <v>pending</v>
       </c>
       <c r="D637">
-        <v>4463.764779263257</v>
+        <v>4918.533527198927</v>
       </c>
     </row>
     <row r="638">
@@ -9409,7 +9409,7 @@
         <v>approved</v>
       </c>
       <c r="D638">
-        <v>4242.531133233606</v>
+        <v>4351.21307596776</v>
       </c>
     </row>
     <row r="639">
@@ -9423,7 +9423,7 @@
         <v>pending</v>
       </c>
       <c r="D639">
-        <v>708.0132374249282</v>
+        <v>4092.597338807482</v>
       </c>
     </row>
     <row r="640">
@@ -9437,7 +9437,7 @@
         <v>approved</v>
       </c>
       <c r="D640">
-        <v>4521.716895877309</v>
+        <v>569.163007661474</v>
       </c>
     </row>
     <row r="641">
@@ -9451,7 +9451,7 @@
         <v>pending</v>
       </c>
       <c r="D641">
-        <v>2649.5315236803417</v>
+        <v>4429.101455999947</v>
       </c>
     </row>
     <row r="642">
@@ -9465,7 +9465,7 @@
         <v>approved</v>
       </c>
       <c r="D642">
-        <v>426.65807061462056</v>
+        <v>749.5724258617997</v>
       </c>
     </row>
     <row r="643">
@@ -9479,7 +9479,7 @@
         <v>pending</v>
       </c>
       <c r="D643">
-        <v>1211.101218339863</v>
+        <v>4184.37366047199</v>
       </c>
     </row>
     <row r="644">
@@ -9493,7 +9493,7 @@
         <v>approved</v>
       </c>
       <c r="D644">
-        <v>1628.6834904986104</v>
+        <v>2963.219526958385</v>
       </c>
     </row>
     <row r="645">
@@ -9507,7 +9507,7 @@
         <v>pending</v>
       </c>
       <c r="D645">
-        <v>3300.672633631425</v>
+        <v>1487.8636916496669</v>
       </c>
     </row>
     <row r="646">
@@ -9521,7 +9521,7 @@
         <v>approved</v>
       </c>
       <c r="D646">
-        <v>1415.5660288048455</v>
+        <v>35.97548767959036</v>
       </c>
     </row>
     <row r="647">
@@ -9535,7 +9535,7 @@
         <v>pending</v>
       </c>
       <c r="D647">
-        <v>725.24116757539</v>
+        <v>2444.255465809888</v>
       </c>
     </row>
     <row r="648">
@@ -9549,7 +9549,7 @@
         <v>approved</v>
       </c>
       <c r="D648">
-        <v>1011.0058602797145</v>
+        <v>2627.809630883684</v>
       </c>
     </row>
     <row r="649">
@@ -9563,7 +9563,7 @@
         <v>pending</v>
       </c>
       <c r="D649">
-        <v>4397.393445898303</v>
+        <v>2877.7101099753354</v>
       </c>
     </row>
     <row r="650">
@@ -9577,7 +9577,7 @@
         <v>approved</v>
       </c>
       <c r="D650">
-        <v>2486.4427318318594</v>
+        <v>4841.315080972143</v>
       </c>
     </row>
     <row r="651">
@@ -9591,7 +9591,7 @@
         <v>pending</v>
       </c>
       <c r="D651">
-        <v>907.1258830443074</v>
+        <v>3328.4364986765845</v>
       </c>
     </row>
     <row r="652">
@@ -9605,7 +9605,7 @@
         <v>approved</v>
       </c>
       <c r="D652">
-        <v>815.4395059649866</v>
+        <v>363.5479861199598</v>
       </c>
     </row>
     <row r="653">
@@ -9619,7 +9619,7 @@
         <v>pending</v>
       </c>
       <c r="D653">
-        <v>357.1564470672828</v>
+        <v>2380.027624715274</v>
       </c>
     </row>
     <row r="654">
@@ -9633,7 +9633,7 @@
         <v>approved</v>
       </c>
       <c r="D654">
-        <v>3952.8250366410934</v>
+        <v>2764.8966918638753</v>
       </c>
     </row>
     <row r="655">
@@ -9647,7 +9647,7 @@
         <v>pending</v>
       </c>
       <c r="D655">
-        <v>4890.133222695484</v>
+        <v>4524.060534120495</v>
       </c>
     </row>
     <row r="656">
@@ -9661,7 +9661,7 @@
         <v>approved</v>
       </c>
       <c r="D656">
-        <v>4734.564279983502</v>
+        <v>3149.3489701720046</v>
       </c>
     </row>
     <row r="657">
@@ -9675,7 +9675,7 @@
         <v>pending</v>
       </c>
       <c r="D657">
-        <v>4333.759448094351</v>
+        <v>967.161336684662</v>
       </c>
     </row>
     <row r="658">
@@ -9689,7 +9689,7 @@
         <v>approved</v>
       </c>
       <c r="D658">
-        <v>2098.866861758826</v>
+        <v>4607.364226522458</v>
       </c>
     </row>
     <row r="659">
@@ -9703,7 +9703,7 @@
         <v>pending</v>
       </c>
       <c r="D659">
-        <v>240.96353622748978</v>
+        <v>3463.646423112854</v>
       </c>
     </row>
     <row r="660">
@@ -9717,7 +9717,7 @@
         <v>approved</v>
       </c>
       <c r="D660">
-        <v>662.8640154704212</v>
+        <v>381.491950788293</v>
       </c>
     </row>
     <row r="661">
@@ -9731,7 +9731,7 @@
         <v>pending</v>
       </c>
       <c r="D661">
-        <v>2759.1393163544485</v>
+        <v>2037.9548020110406</v>
       </c>
     </row>
     <row r="662">
@@ -9745,7 +9745,7 @@
         <v>approved</v>
       </c>
       <c r="D662">
-        <v>4610.844405031329</v>
+        <v>4734.320365189215</v>
       </c>
     </row>
     <row r="663">
@@ -9759,7 +9759,7 @@
         <v>pending</v>
       </c>
       <c r="D663">
-        <v>1361.4846134682457</v>
+        <v>2041.6956831005796</v>
       </c>
     </row>
     <row r="664">
@@ -9773,7 +9773,7 @@
         <v>approved</v>
       </c>
       <c r="D664">
-        <v>4512.810890228371</v>
+        <v>1533.3472667853764</v>
       </c>
     </row>
     <row r="665">
@@ -9787,7 +9787,7 @@
         <v>pending</v>
       </c>
       <c r="D665">
-        <v>3335.4580600077675</v>
+        <v>4289.928073248199</v>
       </c>
     </row>
     <row r="666">
@@ -9801,7 +9801,7 @@
         <v>approved</v>
       </c>
       <c r="D666">
-        <v>4274.802559723533</v>
+        <v>1255.64446073111</v>
       </c>
     </row>
     <row r="667">
@@ -9815,7 +9815,7 @@
         <v>pending</v>
       </c>
       <c r="D667">
-        <v>208.48183591233527</v>
+        <v>4430.970831752789</v>
       </c>
     </row>
     <row r="668">
@@ -9829,7 +9829,7 @@
         <v>approved</v>
       </c>
       <c r="D668">
-        <v>3611.8307165336173</v>
+        <v>433.2326090140004</v>
       </c>
     </row>
     <row r="669">
@@ -9843,7 +9843,7 @@
         <v>pending</v>
       </c>
       <c r="D669">
-        <v>3836.2326989089634</v>
+        <v>2973.479881897462</v>
       </c>
     </row>
     <row r="670">
@@ -9857,7 +9857,7 @@
         <v>approved</v>
       </c>
       <c r="D670">
-        <v>2660.453889271808</v>
+        <v>4742.658428742401</v>
       </c>
     </row>
     <row r="671">
@@ -9871,7 +9871,7 @@
         <v>pending</v>
       </c>
       <c r="D671">
-        <v>1694.5243501596685</v>
+        <v>3022.283875203532</v>
       </c>
     </row>
     <row r="672">
@@ -9885,7 +9885,7 @@
         <v>approved</v>
       </c>
       <c r="D672">
-        <v>707.488643931784</v>
+        <v>1326.06456881715</v>
       </c>
     </row>
     <row r="673">
@@ -9899,7 +9899,7 @@
         <v>pending</v>
       </c>
       <c r="D673">
-        <v>2666.208731188506</v>
+        <v>801.5167347967955</v>
       </c>
     </row>
     <row r="674">
@@ -9913,7 +9913,7 @@
         <v>approved</v>
       </c>
       <c r="D674">
-        <v>1108.4101080976195</v>
+        <v>2566.7708588868654</v>
       </c>
     </row>
     <row r="675">
@@ -9927,7 +9927,7 @@
         <v>pending</v>
       </c>
       <c r="D675">
-        <v>4242.873437458745</v>
+        <v>1809.000947943843</v>
       </c>
     </row>
     <row r="676">
@@ -9941,7 +9941,7 @@
         <v>approved</v>
       </c>
       <c r="D676">
-        <v>2515.0402663827954</v>
+        <v>1324.001914439098</v>
       </c>
     </row>
     <row r="677">
@@ -9955,7 +9955,7 @@
         <v>pending</v>
       </c>
       <c r="D677">
-        <v>2484.1988989815354</v>
+        <v>1071.8620794617527</v>
       </c>
     </row>
     <row r="678">
@@ -9969,7 +9969,7 @@
         <v>approved</v>
       </c>
       <c r="D678">
-        <v>4545.393044362287</v>
+        <v>4895.905590413424</v>
       </c>
     </row>
     <row r="679">
@@ -9983,7 +9983,7 @@
         <v>pending</v>
       </c>
       <c r="D679">
-        <v>21.87942757731376</v>
+        <v>3284.9713519147485</v>
       </c>
     </row>
     <row r="680">
@@ -9997,7 +9997,7 @@
         <v>approved</v>
       </c>
       <c r="D680">
-        <v>2695.650690327407</v>
+        <v>4209.225487651186</v>
       </c>
     </row>
     <row r="681">
@@ -10011,7 +10011,7 @@
         <v>pending</v>
       </c>
       <c r="D681">
-        <v>736.2572445041271</v>
+        <v>1004.2967201327957</v>
       </c>
     </row>
     <row r="682">
@@ -10025,7 +10025,7 @@
         <v>approved</v>
       </c>
       <c r="D682">
-        <v>4084.0491621571105</v>
+        <v>3609.4554423927616</v>
       </c>
     </row>
     <row r="683">
@@ -10039,7 +10039,7 @@
         <v>pending</v>
       </c>
       <c r="D683">
-        <v>4385.286616585301</v>
+        <v>3218.233099615784</v>
       </c>
     </row>
     <row r="684">
@@ -10053,7 +10053,7 @@
         <v>approved</v>
       </c>
       <c r="D684">
-        <v>1316.022674280618</v>
+        <v>1214.1204675064378</v>
       </c>
     </row>
     <row r="685">
@@ -10067,7 +10067,7 @@
         <v>pending</v>
       </c>
       <c r="D685">
-        <v>3771.0256050765</v>
+        <v>2329.038339238164</v>
       </c>
     </row>
     <row r="686">
@@ -10081,7 +10081,7 @@
         <v>approved</v>
       </c>
       <c r="D686">
-        <v>712.2776797541219</v>
+        <v>4058.0654373309344</v>
       </c>
     </row>
     <row r="687">
@@ -10095,7 +10095,7 @@
         <v>pending</v>
       </c>
       <c r="D687">
-        <v>4379.225385668581</v>
+        <v>3760.095854294757</v>
       </c>
     </row>
     <row r="688">
@@ -10109,7 +10109,7 @@
         <v>approved</v>
       </c>
       <c r="D688">
-        <v>4496.842107018505</v>
+        <v>1836.9330868585787</v>
       </c>
     </row>
     <row r="689">
@@ -10123,7 +10123,7 @@
         <v>pending</v>
       </c>
       <c r="D689">
-        <v>3283.1273555618222</v>
+        <v>3025.4936321475125</v>
       </c>
     </row>
     <row r="690">
@@ -10137,7 +10137,7 @@
         <v>approved</v>
       </c>
       <c r="D690">
-        <v>2215.7408281744874</v>
+        <v>4408.645716791238</v>
       </c>
     </row>
     <row r="691">
@@ -10151,7 +10151,7 @@
         <v>pending</v>
       </c>
       <c r="D691">
-        <v>4147.459895350834</v>
+        <v>2916.0171329765217</v>
       </c>
     </row>
     <row r="692">
@@ -10165,7 +10165,7 @@
         <v>approved</v>
       </c>
       <c r="D692">
-        <v>3829.798924835899</v>
+        <v>4770.3745979712685</v>
       </c>
     </row>
     <row r="693">
@@ -10179,7 +10179,7 @@
         <v>pending</v>
       </c>
       <c r="D693">
-        <v>1663.5675853544374</v>
+        <v>18.76615343777366</v>
       </c>
     </row>
     <row r="694">
@@ -10193,7 +10193,7 @@
         <v>approved</v>
       </c>
       <c r="D694">
-        <v>2945.188302420646</v>
+        <v>2086.860905575513</v>
       </c>
     </row>
     <row r="695">
@@ -10207,7 +10207,7 @@
         <v>pending</v>
       </c>
       <c r="D695">
-        <v>2543.978843964816</v>
+        <v>36.40855648072705</v>
       </c>
     </row>
     <row r="696">
@@ -10221,7 +10221,7 @@
         <v>approved</v>
       </c>
       <c r="D696">
-        <v>4163.268659354934</v>
+        <v>1357.355226016501</v>
       </c>
     </row>
     <row r="697">
@@ -10235,7 +10235,7 @@
         <v>pending</v>
       </c>
       <c r="D697">
-        <v>4139.060686611044</v>
+        <v>1375.1584356424041</v>
       </c>
     </row>
     <row r="698">
@@ -10249,7 +10249,7 @@
         <v>approved</v>
       </c>
       <c r="D698">
-        <v>2591.923779031434</v>
+        <v>1670.0120796163776</v>
       </c>
     </row>
     <row r="699">
@@ -10263,7 +10263,7 @@
         <v>pending</v>
       </c>
       <c r="D699">
-        <v>2799.0697884569536</v>
+        <v>3184.552604559917</v>
       </c>
     </row>
     <row r="700">
@@ -10277,7 +10277,7 @@
         <v>approved</v>
       </c>
       <c r="D700">
-        <v>4387.788724531586</v>
+        <v>1451.494537439112</v>
       </c>
     </row>
     <row r="701">
@@ -10291,7 +10291,7 @@
         <v>pending</v>
       </c>
       <c r="D701">
-        <v>1634.5430825467067</v>
+        <v>3589.869957802637</v>
       </c>
     </row>
     <row r="702">
@@ -10305,7 +10305,7 @@
         <v>approved</v>
       </c>
       <c r="D702">
-        <v>3736.223011191063</v>
+        <v>868.0884957576218</v>
       </c>
     </row>
     <row r="703">
@@ -10319,7 +10319,7 @@
         <v>pending</v>
       </c>
       <c r="D703">
-        <v>2653.104912438553</v>
+        <v>3193.6664698455784</v>
       </c>
     </row>
     <row r="704">
@@ -10333,7 +10333,7 @@
         <v>approved</v>
       </c>
       <c r="D704">
-        <v>1763.2248319139298</v>
+        <v>4877.092517594509</v>
       </c>
     </row>
     <row r="705">
@@ -10347,7 +10347,7 @@
         <v>pending</v>
       </c>
       <c r="D705">
-        <v>1821.6821570740572</v>
+        <v>2575.8587425243472</v>
       </c>
     </row>
     <row r="706">
@@ -10361,7 +10361,7 @@
         <v>approved</v>
       </c>
       <c r="D706">
-        <v>4353.684694317859</v>
+        <v>427.4156310319388</v>
       </c>
     </row>
     <row r="707">
@@ -10375,7 +10375,7 @@
         <v>pending</v>
       </c>
       <c r="D707">
-        <v>2513.774044577464</v>
+        <v>1785.7013955445188</v>
       </c>
     </row>
     <row r="708">
@@ -10389,7 +10389,7 @@
         <v>approved</v>
       </c>
       <c r="D708">
-        <v>2564.1059062402505</v>
+        <v>4167.278771809007</v>
       </c>
     </row>
     <row r="709">
@@ -10403,7 +10403,7 @@
         <v>pending</v>
       </c>
       <c r="D709">
-        <v>3461.23617793328</v>
+        <v>2989.301735633193</v>
       </c>
     </row>
     <row r="710">
@@ -10417,7 +10417,7 @@
         <v>approved</v>
       </c>
       <c r="D710">
-        <v>2744.294849664992</v>
+        <v>2217.1248445039782</v>
       </c>
     </row>
     <row r="711">
@@ -10431,7 +10431,7 @@
         <v>pending</v>
       </c>
       <c r="D711">
-        <v>4846.07027301022</v>
+        <v>4597.67938576917</v>
       </c>
     </row>
     <row r="712">
@@ -10445,7 +10445,7 @@
         <v>approved</v>
       </c>
       <c r="D712">
-        <v>2868.722617829366</v>
+        <v>245.48148375423628</v>
       </c>
     </row>
     <row r="713">
@@ -10459,7 +10459,7 @@
         <v>pending</v>
       </c>
       <c r="D713">
-        <v>3787.0595862753576</v>
+        <v>3807.9906372813566</v>
       </c>
     </row>
     <row r="714">
@@ -10473,7 +10473,7 @@
         <v>approved</v>
       </c>
       <c r="D714">
-        <v>3504.788206087458</v>
+        <v>2125.3673050563693</v>
       </c>
     </row>
     <row r="715">
@@ -10487,7 +10487,7 @@
         <v>pending</v>
       </c>
       <c r="D715">
-        <v>2511.821356733963</v>
+        <v>3504.6661583469863</v>
       </c>
     </row>
     <row r="716">
@@ -10501,7 +10501,7 @@
         <v>approved</v>
       </c>
       <c r="D716">
-        <v>2518.1547995353726</v>
+        <v>3322.4472164359186</v>
       </c>
     </row>
     <row r="717">
@@ -10515,7 +10515,7 @@
         <v>pending</v>
       </c>
       <c r="D717">
-        <v>2153.6799850918787</v>
+        <v>2095.1357162172235</v>
       </c>
     </row>
     <row r="718">
@@ -10529,7 +10529,7 @@
         <v>approved</v>
       </c>
       <c r="D718">
-        <v>1185.0183131668257</v>
+        <v>1875.429529131053</v>
       </c>
     </row>
     <row r="719">
@@ -10543,7 +10543,7 @@
         <v>pending</v>
       </c>
       <c r="D719">
-        <v>4494.443361084401</v>
+        <v>2101.600991690121</v>
       </c>
     </row>
     <row r="720">
@@ -10557,7 +10557,7 @@
         <v>approved</v>
       </c>
       <c r="D720">
-        <v>2829.5214717094273</v>
+        <v>4224.428431678715</v>
       </c>
     </row>
     <row r="721">
@@ -10571,7 +10571,7 @@
         <v>pending</v>
       </c>
       <c r="D721">
-        <v>3163.592124432351</v>
+        <v>3155.115885552483</v>
       </c>
     </row>
     <row r="722">
@@ -10585,7 +10585,7 @@
         <v>approved</v>
       </c>
       <c r="D722">
-        <v>2734.18768042905</v>
+        <v>3940.442018217857</v>
       </c>
     </row>
     <row r="723">
@@ -10599,7 +10599,7 @@
         <v>pending</v>
       </c>
       <c r="D723">
-        <v>4738.539961624265</v>
+        <v>2477.0850469306347</v>
       </c>
     </row>
     <row r="724">
@@ -10613,7 +10613,7 @@
         <v>approved</v>
       </c>
       <c r="D724">
-        <v>3937.448675220848</v>
+        <v>2480.5133232735443</v>
       </c>
     </row>
     <row r="725">
@@ -10627,7 +10627,7 @@
         <v>pending</v>
       </c>
       <c r="D725">
-        <v>4857.318857010173</v>
+        <v>2775.932885592962</v>
       </c>
     </row>
     <row r="726">
@@ -10641,7 +10641,7 @@
         <v>approved</v>
       </c>
       <c r="D726">
-        <v>4614.865699394241</v>
+        <v>3704.4926279838332</v>
       </c>
     </row>
     <row r="727">
@@ -10655,7 +10655,7 @@
         <v>pending</v>
       </c>
       <c r="D727">
-        <v>2180.29348957936</v>
+        <v>2912.3763148363623</v>
       </c>
     </row>
     <row r="728">
@@ -10669,7 +10669,7 @@
         <v>approved</v>
       </c>
       <c r="D728">
-        <v>1575.2463491041979</v>
+        <v>4618.639808176259</v>
       </c>
     </row>
     <row r="729">
@@ -10683,7 +10683,7 @@
         <v>pending</v>
       </c>
       <c r="D729">
-        <v>2081.8962658933206</v>
+        <v>2956.6490231551356</v>
       </c>
     </row>
     <row r="730">
@@ -10697,7 +10697,7 @@
         <v>approved</v>
       </c>
       <c r="D730">
-        <v>881.8138183302482</v>
+        <v>4595.312812303932</v>
       </c>
     </row>
     <row r="731">
@@ -10711,7 +10711,7 @@
         <v>pending</v>
       </c>
       <c r="D731">
-        <v>4355.042337661046</v>
+        <v>4407.521853106286</v>
       </c>
     </row>
     <row r="732">
@@ -10725,7 +10725,7 @@
         <v>approved</v>
       </c>
       <c r="D732">
-        <v>2510.5830732238887</v>
+        <v>4020.6609834281735</v>
       </c>
     </row>
     <row r="733">
@@ -10739,7 +10739,7 @@
         <v>pending</v>
       </c>
       <c r="D733">
-        <v>4882.253798499416</v>
+        <v>2766.9403745233003</v>
       </c>
     </row>
     <row r="734">
@@ -10753,7 +10753,7 @@
         <v>approved</v>
       </c>
       <c r="D734">
-        <v>948.0948978396142</v>
+        <v>245.01103203889875</v>
       </c>
     </row>
     <row r="735">
@@ -10767,7 +10767,7 @@
         <v>pending</v>
       </c>
       <c r="D735">
-        <v>3486.9918133576616</v>
+        <v>1382.5689440308774</v>
       </c>
     </row>
     <row r="736">
@@ -10781,7 +10781,7 @@
         <v>approved</v>
       </c>
       <c r="D736">
-        <v>901.8866256437286</v>
+        <v>2395.728940424329</v>
       </c>
     </row>
     <row r="737">
@@ -10795,7 +10795,7 @@
         <v>pending</v>
       </c>
       <c r="D737">
-        <v>882.7541433097452</v>
+        <v>1318.5450432015678</v>
       </c>
     </row>
     <row r="738">
@@ -10809,7 +10809,7 @@
         <v>approved</v>
       </c>
       <c r="D738">
-        <v>3024.9235639267813</v>
+        <v>211.12692517329168</v>
       </c>
     </row>
     <row r="739">
@@ -10823,7 +10823,7 @@
         <v>pending</v>
       </c>
       <c r="D739">
-        <v>4640.075774514868</v>
+        <v>4826.008524637162</v>
       </c>
     </row>
     <row r="740">
@@ -10837,7 +10837,7 @@
         <v>approved</v>
       </c>
       <c r="D740">
-        <v>2180.146633013613</v>
+        <v>2545.098959447969</v>
       </c>
     </row>
     <row r="741">
@@ -10851,7 +10851,7 @@
         <v>pending</v>
       </c>
       <c r="D741">
-        <v>911.8072237699248</v>
+        <v>3818.825313049188</v>
       </c>
     </row>
     <row r="742">
@@ -10865,7 +10865,7 @@
         <v>approved</v>
       </c>
       <c r="D742">
-        <v>2449.6729587267473</v>
+        <v>699.9685664734124</v>
       </c>
     </row>
     <row r="743">
@@ -10879,7 +10879,7 @@
         <v>pending</v>
       </c>
       <c r="D743">
-        <v>4270.376882994988</v>
+        <v>4897.876443771797</v>
       </c>
     </row>
     <row r="744">
@@ -10893,7 +10893,7 @@
         <v>approved</v>
       </c>
       <c r="D744">
-        <v>1174.613600408191</v>
+        <v>181.86498517038797</v>
       </c>
     </row>
     <row r="745">
@@ -10907,7 +10907,7 @@
         <v>pending</v>
       </c>
       <c r="D745">
-        <v>348.45290545506555</v>
+        <v>2476.1912536391605</v>
       </c>
     </row>
     <row r="746">
@@ -10921,7 +10921,7 @@
         <v>approved</v>
       </c>
       <c r="D746">
-        <v>2658.493309078601</v>
+        <v>1668.4217073293128</v>
       </c>
     </row>
     <row r="747">
@@ -10935,7 +10935,7 @@
         <v>pending</v>
       </c>
       <c r="D747">
-        <v>1999.802588632974</v>
+        <v>4020.7981468738053</v>
       </c>
     </row>
     <row r="748">
@@ -10949,7 +10949,7 @@
         <v>approved</v>
       </c>
       <c r="D748">
-        <v>767.3505438656003</v>
+        <v>2249.707532156442</v>
       </c>
     </row>
     <row r="749">
@@ -10963,7 +10963,7 @@
         <v>pending</v>
       </c>
       <c r="D749">
-        <v>2959.24481884312</v>
+        <v>3338.869260636532</v>
       </c>
     </row>
     <row r="750">
@@ -10977,7 +10977,7 @@
         <v>approved</v>
       </c>
       <c r="D750">
-        <v>4589.769454231821</v>
+        <v>637.5736218279393</v>
       </c>
     </row>
     <row r="751">
@@ -10991,7 +10991,7 @@
         <v>pending</v>
       </c>
       <c r="D751">
-        <v>4233.112721122459</v>
+        <v>4943.011554005649</v>
       </c>
     </row>
     <row r="752">
@@ -11005,7 +11005,7 @@
         <v>approved</v>
       </c>
       <c r="D752">
-        <v>262.47814111245884</v>
+        <v>3083.1958363499343</v>
       </c>
     </row>
     <row r="753">
@@ -11019,7 +11019,7 @@
         <v>pending</v>
       </c>
       <c r="D753">
-        <v>2798.9467105559875</v>
+        <v>1530.7457339702103</v>
       </c>
     </row>
     <row r="754">
@@ -11033,7 +11033,7 @@
         <v>approved</v>
       </c>
       <c r="D754">
-        <v>4243.571971265725</v>
+        <v>2252.088563519702</v>
       </c>
     </row>
     <row r="755">
@@ -11047,7 +11047,7 @@
         <v>pending</v>
       </c>
       <c r="D755">
-        <v>1601.1226362123386</v>
+        <v>4948.594421870781</v>
       </c>
     </row>
     <row r="756">
@@ -11061,7 +11061,7 @@
         <v>approved</v>
       </c>
       <c r="D756">
-        <v>1586.3679943865084</v>
+        <v>4578.802819593591</v>
       </c>
     </row>
     <row r="757">
@@ -11075,7 +11075,7 @@
         <v>pending</v>
       </c>
       <c r="D757">
-        <v>3023.3672867420214</v>
+        <v>1208.4187076792118</v>
       </c>
     </row>
     <row r="758">
@@ -11089,7 +11089,7 @@
         <v>approved</v>
       </c>
       <c r="D758">
-        <v>3329.7934419451135</v>
+        <v>627.0557448004377</v>
       </c>
     </row>
     <row r="759">
@@ -11103,7 +11103,7 @@
         <v>pending</v>
       </c>
       <c r="D759">
-        <v>3856.490230577535</v>
+        <v>3584.4371706654956</v>
       </c>
     </row>
     <row r="760">
@@ -11117,7 +11117,7 @@
         <v>approved</v>
       </c>
       <c r="D760">
-        <v>2641.375009431971</v>
+        <v>3381.6517766959873</v>
       </c>
     </row>
     <row r="761">
@@ -11131,7 +11131,7 @@
         <v>pending</v>
       </c>
       <c r="D761">
-        <v>3018.8017172522495</v>
+        <v>1619.983483901023</v>
       </c>
     </row>
     <row r="762">
@@ -11145,7 +11145,7 @@
         <v>approved</v>
       </c>
       <c r="D762">
-        <v>324.28684927703455</v>
+        <v>3325.242003360731</v>
       </c>
     </row>
     <row r="763">
@@ -11159,7 +11159,7 @@
         <v>pending</v>
       </c>
       <c r="D763">
-        <v>1893.963764766705</v>
+        <v>2843.6526124437687</v>
       </c>
     </row>
     <row r="764">
@@ -11173,7 +11173,7 @@
         <v>approved</v>
       </c>
       <c r="D764">
-        <v>1839.8387318477105</v>
+        <v>2285.831158078905</v>
       </c>
     </row>
     <row r="765">
@@ -11187,7 +11187,7 @@
         <v>pending</v>
       </c>
       <c r="D765">
-        <v>1998.805610028721</v>
+        <v>4418.15795061608</v>
       </c>
     </row>
     <row r="766">
@@ -11201,7 +11201,7 @@
         <v>approved</v>
       </c>
       <c r="D766">
-        <v>2846.4893480850706</v>
+        <v>3399.932517628672</v>
       </c>
     </row>
     <row r="767">
@@ -11215,7 +11215,7 @@
         <v>pending</v>
       </c>
       <c r="D767">
-        <v>2425.934401966896</v>
+        <v>3481.102581404859</v>
       </c>
     </row>
     <row r="768">
@@ -11229,7 +11229,7 @@
         <v>approved</v>
       </c>
       <c r="D768">
-        <v>1398.69312308469</v>
+        <v>2411.079051329689</v>
       </c>
     </row>
     <row r="769">
@@ -11243,7 +11243,7 @@
         <v>pending</v>
       </c>
       <c r="D769">
-        <v>2064.37249227744</v>
+        <v>2885.975452469055</v>
       </c>
     </row>
     <row r="770">
@@ -11257,7 +11257,7 @@
         <v>approved</v>
       </c>
       <c r="D770">
-        <v>3993.6798120398444</v>
+        <v>4228.580110228548</v>
       </c>
     </row>
     <row r="771">
@@ -11271,7 +11271,7 @@
         <v>pending</v>
       </c>
       <c r="D771">
-        <v>4529.903685086978</v>
+        <v>2908.893152312081</v>
       </c>
     </row>
     <row r="772">
@@ -11285,7 +11285,7 @@
         <v>approved</v>
       </c>
       <c r="D772">
-        <v>2637.34380859702</v>
+        <v>1338.7143819024006</v>
       </c>
     </row>
     <row r="773">
@@ -11299,7 +11299,7 @@
         <v>pending</v>
       </c>
       <c r="D773">
-        <v>882.3527716910129</v>
+        <v>4616.045495956624</v>
       </c>
     </row>
     <row r="774">
@@ -11313,7 +11313,7 @@
         <v>approved</v>
       </c>
       <c r="D774">
-        <v>490.44829612454487</v>
+        <v>4018.9304321493655</v>
       </c>
     </row>
     <row r="775">
@@ -11327,7 +11327,7 @@
         <v>pending</v>
       </c>
       <c r="D775">
-        <v>2619.9714515421315</v>
+        <v>1660.956415816437</v>
       </c>
     </row>
     <row r="776">
@@ -11341,7 +11341,7 @@
         <v>approved</v>
       </c>
       <c r="D776">
-        <v>4784.333360852436</v>
+        <v>2201.4963079135264</v>
       </c>
     </row>
     <row r="777">
@@ -11355,7 +11355,7 @@
         <v>pending</v>
       </c>
       <c r="D777">
-        <v>1826.678028663221</v>
+        <v>497.3448738366493</v>
       </c>
     </row>
     <row r="778">
@@ -11369,7 +11369,7 @@
         <v>approved</v>
       </c>
       <c r="D778">
-        <v>2532.190775584071</v>
+        <v>4837.55088978073</v>
       </c>
     </row>
     <row r="779">
@@ -11383,7 +11383,7 @@
         <v>pending</v>
       </c>
       <c r="D779">
-        <v>3095.0112695227263</v>
+        <v>2414.8139857740325</v>
       </c>
     </row>
     <row r="780">
@@ -11397,7 +11397,7 @@
         <v>approved</v>
       </c>
       <c r="D780">
-        <v>2491.2615874061516</v>
+        <v>4369.0409225785725</v>
       </c>
     </row>
     <row r="781">
@@ -11411,7 +11411,7 @@
         <v>pending</v>
       </c>
       <c r="D781">
-        <v>3398.750610649096</v>
+        <v>3054.412734782437</v>
       </c>
     </row>
     <row r="782">
@@ -11425,7 +11425,7 @@
         <v>approved</v>
       </c>
       <c r="D782">
-        <v>4246.873876487763</v>
+        <v>3077.388327483015</v>
       </c>
     </row>
     <row r="783">
@@ -11439,7 +11439,7 @@
         <v>pending</v>
       </c>
       <c r="D783">
-        <v>4868.565532831401</v>
+        <v>2876.6027527038395</v>
       </c>
     </row>
     <row r="784">
@@ -11453,7 +11453,7 @@
         <v>approved</v>
       </c>
       <c r="D784">
-        <v>4952.294746720034</v>
+        <v>729.580623128695</v>
       </c>
     </row>
     <row r="785">
@@ -11467,7 +11467,7 @@
         <v>pending</v>
       </c>
       <c r="D785">
-        <v>4807.060330248842</v>
+        <v>1186.5523709530157</v>
       </c>
     </row>
     <row r="786">
@@ -11481,7 +11481,7 @@
         <v>approved</v>
       </c>
       <c r="D786">
-        <v>4776.633379532395</v>
+        <v>3137.459590160494</v>
       </c>
     </row>
     <row r="787">
@@ -11495,7 +11495,7 @@
         <v>pending</v>
       </c>
       <c r="D787">
-        <v>3437.370465700135</v>
+        <v>1701.2582986522739</v>
       </c>
     </row>
     <row r="788">
@@ -11509,7 +11509,7 @@
         <v>approved</v>
       </c>
       <c r="D788">
-        <v>717.6259155696752</v>
+        <v>4475.452943271671</v>
       </c>
     </row>
     <row r="789">
@@ -11523,7 +11523,7 @@
         <v>pending</v>
       </c>
       <c r="D789">
-        <v>4697.646190806103</v>
+        <v>3712.0837257070793</v>
       </c>
     </row>
     <row r="790">
@@ -11537,7 +11537,7 @@
         <v>approved</v>
       </c>
       <c r="D790">
-        <v>3607.5254822029356</v>
+        <v>4233.7349148867</v>
       </c>
     </row>
     <row r="791">
@@ -11551,7 +11551,7 @@
         <v>pending</v>
       </c>
       <c r="D791">
-        <v>3716.5397183819928</v>
+        <v>1609.5460686844422</v>
       </c>
     </row>
     <row r="792">
@@ -11565,7 +11565,7 @@
         <v>approved</v>
       </c>
       <c r="D792">
-        <v>4881.451127764919</v>
+        <v>0.6690869149827972</v>
       </c>
     </row>
     <row r="793">
@@ -11579,7 +11579,7 @@
         <v>pending</v>
       </c>
       <c r="D793">
-        <v>390.3718766721664</v>
+        <v>902.898005099313</v>
       </c>
     </row>
     <row r="794">
@@ -11593,7 +11593,7 @@
         <v>approved</v>
       </c>
       <c r="D794">
-        <v>814.4186521555185</v>
+        <v>564.0144339305165</v>
       </c>
     </row>
     <row r="795">
@@ -11607,7 +11607,7 @@
         <v>pending</v>
       </c>
       <c r="D795">
-        <v>4164.91504627927</v>
+        <v>1596.611969633457</v>
       </c>
     </row>
     <row r="796">
@@ -11621,7 +11621,7 @@
         <v>approved</v>
       </c>
       <c r="D796">
-        <v>1253.7239415934675</v>
+        <v>1271.452336283758</v>
       </c>
     </row>
     <row r="797">
@@ -11635,7 +11635,7 @@
         <v>pending</v>
       </c>
       <c r="D797">
-        <v>665.4779406048073</v>
+        <v>2597.303139895277</v>
       </c>
     </row>
     <row r="798">
@@ -11649,7 +11649,7 @@
         <v>approved</v>
       </c>
       <c r="D798">
-        <v>4581.80638194634</v>
+        <v>576.9990952900739</v>
       </c>
     </row>
     <row r="799">
@@ -11663,7 +11663,7 @@
         <v>pending</v>
       </c>
       <c r="D799">
-        <v>4387.519453014986</v>
+        <v>4966.942908353748</v>
       </c>
     </row>
     <row r="800">
@@ -11677,7 +11677,7 @@
         <v>approved</v>
       </c>
       <c r="D800">
-        <v>2826.9681952869987</v>
+        <v>4463.622587041153</v>
       </c>
     </row>
     <row r="801">
@@ -11691,7 +11691,7 @@
         <v>pending</v>
       </c>
       <c r="D801">
-        <v>4120.057604558555</v>
+        <v>1246.5704350705598</v>
       </c>
     </row>
     <row r="802">
@@ -11705,7 +11705,7 @@
         <v>approved</v>
       </c>
       <c r="D802">
-        <v>2997.516904059865</v>
+        <v>2917.6922473584264</v>
       </c>
     </row>
     <row r="803">
@@ -11719,7 +11719,7 @@
         <v>pending</v>
       </c>
       <c r="D803">
-        <v>2474.435095752251</v>
+        <v>1140.3838191712102</v>
       </c>
     </row>
     <row r="804">
@@ -11733,7 +11733,7 @@
         <v>approved</v>
       </c>
       <c r="D804">
-        <v>2083.2482291743736</v>
+        <v>4682.2436170870205</v>
       </c>
     </row>
     <row r="805">
@@ -11747,7 +11747,7 @@
         <v>pending</v>
       </c>
       <c r="D805">
-        <v>2506.233799002483</v>
+        <v>1114.189580145345</v>
       </c>
     </row>
     <row r="806">
@@ -11761,7 +11761,7 @@
         <v>approved</v>
       </c>
       <c r="D806">
-        <v>2400.5607144583605</v>
+        <v>2365.0519169281138</v>
       </c>
     </row>
     <row r="807">
@@ -11775,7 +11775,7 @@
         <v>pending</v>
       </c>
       <c r="D807">
-        <v>508.18316810998465</v>
+        <v>2412.507672795914</v>
       </c>
     </row>
     <row r="808">
@@ -11789,7 +11789,7 @@
         <v>approved</v>
       </c>
       <c r="D808">
-        <v>3928.1783484614775</v>
+        <v>2839.4595253059174</v>
       </c>
     </row>
     <row r="809">
@@ -11803,7 +11803,7 @@
         <v>pending</v>
       </c>
       <c r="D809">
-        <v>4738.572913981521</v>
+        <v>1088.3813290064993</v>
       </c>
     </row>
     <row r="810">
@@ -11817,7 +11817,7 @@
         <v>approved</v>
       </c>
       <c r="D810">
-        <v>2326.8963690589726</v>
+        <v>3391.8965129389244</v>
       </c>
     </row>
     <row r="811">
@@ -11831,7 +11831,7 @@
         <v>pending</v>
       </c>
       <c r="D811">
-        <v>3104.0108840063194</v>
+        <v>2092.159355651738</v>
       </c>
     </row>
     <row r="812">
@@ -11845,7 +11845,7 @@
         <v>approved</v>
       </c>
       <c r="D812">
-        <v>1740.4074928663204</v>
+        <v>3773.537295646631</v>
       </c>
     </row>
     <row r="813">
@@ -11859,7 +11859,7 @@
         <v>pending</v>
       </c>
       <c r="D813">
-        <v>2155.5224876947677</v>
+        <v>139.70415353183662</v>
       </c>
     </row>
     <row r="814">
@@ -11873,7 +11873,7 @@
         <v>approved</v>
       </c>
       <c r="D814">
-        <v>85.0350854811266</v>
+        <v>3595.8665567606054</v>
       </c>
     </row>
     <row r="815">
@@ -11887,7 +11887,7 @@
         <v>pending</v>
       </c>
       <c r="D815">
-        <v>2148.5054586684582</v>
+        <v>1977.5572744247827</v>
       </c>
     </row>
     <row r="816">
@@ -11901,7 +11901,7 @@
         <v>approved</v>
       </c>
       <c r="D816">
-        <v>4748.791813554988</v>
+        <v>3092.8118596962695</v>
       </c>
     </row>
     <row r="817">
@@ -11915,7 +11915,7 @@
         <v>pending</v>
       </c>
       <c r="D817">
-        <v>1804.0637706672435</v>
+        <v>4983.324418419252</v>
       </c>
     </row>
     <row r="818">
@@ -11929,7 +11929,7 @@
         <v>approved</v>
       </c>
       <c r="D818">
-        <v>3531.1991621080506</v>
+        <v>960.5344019899553</v>
       </c>
     </row>
     <row r="819">
@@ -11943,7 +11943,7 @@
         <v>pending</v>
       </c>
       <c r="D819">
-        <v>2761.8410577491336</v>
+        <v>4385.770667630026</v>
       </c>
     </row>
     <row r="820">
@@ -11957,7 +11957,7 @@
         <v>approved</v>
       </c>
       <c r="D820">
-        <v>2886.6396342345033</v>
+        <v>241.84695853597503</v>
       </c>
     </row>
     <row r="821">
@@ -11971,7 +11971,7 @@
         <v>pending</v>
       </c>
       <c r="D821">
-        <v>1107.7202253074115</v>
+        <v>2775.6985345430717</v>
       </c>
     </row>
     <row r="822">
@@ -11985,7 +11985,7 @@
         <v>approved</v>
       </c>
       <c r="D822">
-        <v>4211.8403242229015</v>
+        <v>3121.6973756884536</v>
       </c>
     </row>
     <row r="823">
@@ -11999,7 +11999,7 @@
         <v>pending</v>
       </c>
       <c r="D823">
-        <v>4093.827750844932</v>
+        <v>1618.1685101828946</v>
       </c>
     </row>
     <row r="824">
@@ -12013,7 +12013,7 @@
         <v>approved</v>
       </c>
       <c r="D824">
-        <v>1316.4676850354028</v>
+        <v>3988.2302313338923</v>
       </c>
     </row>
     <row r="825">
@@ -12027,7 +12027,7 @@
         <v>pending</v>
       </c>
       <c r="D825">
-        <v>301.81861844641224</v>
+        <v>4539.89354568098</v>
       </c>
     </row>
     <row r="826">
@@ -12041,7 +12041,7 @@
         <v>approved</v>
       </c>
       <c r="D826">
-        <v>3141.4913684128855</v>
+        <v>4498.677705621554</v>
       </c>
     </row>
     <row r="827">
@@ -12055,7 +12055,7 @@
         <v>pending</v>
       </c>
       <c r="D827">
-        <v>4111.946516528273</v>
+        <v>1499.2936023176196</v>
       </c>
     </row>
     <row r="828">
@@ -12069,7 +12069,7 @@
         <v>approved</v>
       </c>
       <c r="D828">
-        <v>4683.329829943652</v>
+        <v>3814.9639446572983</v>
       </c>
     </row>
     <row r="829">
@@ -12083,7 +12083,7 @@
         <v>pending</v>
       </c>
       <c r="D829">
-        <v>4191.010547412849</v>
+        <v>1452.4512128003453</v>
       </c>
     </row>
     <row r="830">
@@ -12097,7 +12097,7 @@
         <v>approved</v>
       </c>
       <c r="D830">
-        <v>3409.08860750209</v>
+        <v>3019.769237308335</v>
       </c>
     </row>
     <row r="831">
@@ -12111,7 +12111,7 @@
         <v>pending</v>
       </c>
       <c r="D831">
-        <v>3873.8469739521843</v>
+        <v>450.0477197471886</v>
       </c>
     </row>
     <row r="832">
@@ -12125,7 +12125,7 @@
         <v>approved</v>
       </c>
       <c r="D832">
-        <v>591.1788125407069</v>
+        <v>4642.386064284012</v>
       </c>
     </row>
     <row r="833">
@@ -12139,7 +12139,7 @@
         <v>pending</v>
       </c>
       <c r="D833">
-        <v>2007.5575980707638</v>
+        <v>4175.109973858129</v>
       </c>
     </row>
     <row r="834">
@@ -12153,7 +12153,7 @@
         <v>approved</v>
       </c>
       <c r="D834">
-        <v>942.0253539307788</v>
+        <v>3414.1603641424367</v>
       </c>
     </row>
     <row r="835">
@@ -12167,7 +12167,7 @@
         <v>pending</v>
       </c>
       <c r="D835">
-        <v>4831.050414755035</v>
+        <v>142.6473173306464</v>
       </c>
     </row>
     <row r="836">
@@ -12181,7 +12181,7 @@
         <v>approved</v>
       </c>
       <c r="D836">
-        <v>3908.476865613304</v>
+        <v>511.9506728604661</v>
       </c>
     </row>
     <row r="837">
@@ -12195,7 +12195,7 @@
         <v>pending</v>
       </c>
       <c r="D837">
-        <v>831.8698914431221</v>
+        <v>4521.645891887644</v>
       </c>
     </row>
     <row r="838">
@@ -12209,7 +12209,7 @@
         <v>approved</v>
       </c>
       <c r="D838">
-        <v>2855.462098315286</v>
+        <v>1900.888450682504</v>
       </c>
     </row>
     <row r="839">
@@ -12223,7 +12223,7 @@
         <v>pending</v>
       </c>
       <c r="D839">
-        <v>597.5560244083744</v>
+        <v>1137.5902521792636</v>
       </c>
     </row>
     <row r="840">
@@ -12237,7 +12237,7 @@
         <v>approved</v>
       </c>
       <c r="D840">
-        <v>1064.5823044854742</v>
+        <v>3044.363112885068</v>
       </c>
     </row>
     <row r="841">
@@ -12251,7 +12251,7 @@
         <v>pending</v>
       </c>
       <c r="D841">
-        <v>3461.7052067613595</v>
+        <v>94.72527825243216</v>
       </c>
     </row>
     <row r="842">
@@ -12265,7 +12265,7 @@
         <v>approved</v>
       </c>
       <c r="D842">
-        <v>933.7405312001889</v>
+        <v>3927.6750900727066</v>
       </c>
     </row>
     <row r="843">
@@ -12279,7 +12279,7 @@
         <v>pending</v>
       </c>
       <c r="D843">
-        <v>1969.9293239678495</v>
+        <v>3415.1186866395</v>
       </c>
     </row>
     <row r="844">
@@ -12293,7 +12293,7 @@
         <v>approved</v>
       </c>
       <c r="D844">
-        <v>1610.289871175361</v>
+        <v>4451.7061211730415</v>
       </c>
     </row>
     <row r="845">
@@ -12307,7 +12307,7 @@
         <v>pending</v>
       </c>
       <c r="D845">
-        <v>1989.2020976738013</v>
+        <v>2697.788940491281</v>
       </c>
     </row>
     <row r="846">
@@ -12321,7 +12321,7 @@
         <v>approved</v>
       </c>
       <c r="D846">
-        <v>4422.43268195927</v>
+        <v>2355.2352594167437</v>
       </c>
     </row>
     <row r="847">
@@ -12335,7 +12335,7 @@
         <v>pending</v>
       </c>
       <c r="D847">
-        <v>920.3771703571462</v>
+        <v>1767.430698460818</v>
       </c>
     </row>
     <row r="848">
@@ -12349,7 +12349,7 @@
         <v>approved</v>
       </c>
       <c r="D848">
-        <v>1817.9557109220002</v>
+        <v>4624.783876656606</v>
       </c>
     </row>
     <row r="849">
@@ -12363,7 +12363,7 @@
         <v>pending</v>
       </c>
       <c r="D849">
-        <v>1231.4994936459545</v>
+        <v>3221.0547159479406</v>
       </c>
     </row>
     <row r="850">
@@ -12377,7 +12377,7 @@
         <v>approved</v>
       </c>
       <c r="D850">
-        <v>1876.4525699495039</v>
+        <v>3692.7091823941682</v>
       </c>
     </row>
     <row r="851">
@@ -12391,7 +12391,7 @@
         <v>pending</v>
       </c>
       <c r="D851">
-        <v>4693.705847748231</v>
+        <v>3949.3005438848427</v>
       </c>
     </row>
     <row r="852">
@@ -12405,7 +12405,7 @@
         <v>approved</v>
       </c>
       <c r="D852">
-        <v>3786.785792619791</v>
+        <v>220.16673436756173</v>
       </c>
     </row>
     <row r="853">
@@ -12419,7 +12419,7 @@
         <v>pending</v>
       </c>
       <c r="D853">
-        <v>2082.2843052115168</v>
+        <v>93.63697313064301</v>
       </c>
     </row>
     <row r="854">
@@ -12433,7 +12433,7 @@
         <v>approved</v>
       </c>
       <c r="D854">
-        <v>4479.777398844403</v>
+        <v>1439.0410625798545</v>
       </c>
     </row>
     <row r="855">
@@ -12447,7 +12447,7 @@
         <v>pending</v>
       </c>
       <c r="D855">
-        <v>915.9759458644135</v>
+        <v>3707.2580695666434</v>
       </c>
     </row>
     <row r="856">
@@ -12461,7 +12461,7 @@
         <v>approved</v>
       </c>
       <c r="D856">
-        <v>901.9445757907985</v>
+        <v>1395.7379457521336</v>
       </c>
     </row>
     <row r="857">
@@ -12475,7 +12475,7 @@
         <v>pending</v>
       </c>
       <c r="D857">
-        <v>2085.1465548409533</v>
+        <v>253.29647179710423</v>
       </c>
     </row>
     <row r="858">
@@ -12489,7 +12489,7 @@
         <v>approved</v>
       </c>
       <c r="D858">
-        <v>3182.809292575709</v>
+        <v>1098.9793850840235</v>
       </c>
     </row>
     <row r="859">
@@ -12503,7 +12503,7 @@
         <v>pending</v>
       </c>
       <c r="D859">
-        <v>302.7312627117107</v>
+        <v>2995.83475541624</v>
       </c>
     </row>
     <row r="860">
@@ -12517,7 +12517,7 @@
         <v>approved</v>
       </c>
       <c r="D860">
-        <v>1028.3896913220647</v>
+        <v>4204.535759949262</v>
       </c>
     </row>
     <row r="861">
@@ -12531,7 +12531,7 @@
         <v>pending</v>
       </c>
       <c r="D861">
-        <v>1754.3252605076132</v>
+        <v>3885.9555330728845</v>
       </c>
     </row>
     <row r="862">
@@ -12545,7 +12545,7 @@
         <v>approved</v>
       </c>
       <c r="D862">
-        <v>935.6768490139389</v>
+        <v>3901.6913400380104</v>
       </c>
     </row>
     <row r="863">
@@ -12559,7 +12559,7 @@
         <v>pending</v>
       </c>
       <c r="D863">
-        <v>3330.362357026605</v>
+        <v>4494.444074046692</v>
       </c>
     </row>
     <row r="864">
@@ -12573,7 +12573,7 @@
         <v>approved</v>
       </c>
       <c r="D864">
-        <v>1031.2477910260309</v>
+        <v>213.33942937377782</v>
       </c>
     </row>
     <row r="865">
@@ -12587,7 +12587,7 @@
         <v>pending</v>
       </c>
       <c r="D865">
-        <v>1049.1089056615488</v>
+        <v>1536.8256773111932</v>
       </c>
     </row>
     <row r="866">
@@ -12601,7 +12601,7 @@
         <v>approved</v>
       </c>
       <c r="D866">
-        <v>4956.011764636922</v>
+        <v>1824.0225900150997</v>
       </c>
     </row>
     <row r="867">
@@ -12615,7 +12615,7 @@
         <v>pending</v>
       </c>
       <c r="D867">
-        <v>859.6026246511224</v>
+        <v>1089.682066867993</v>
       </c>
     </row>
     <row r="868">
@@ -12629,7 +12629,7 @@
         <v>approved</v>
       </c>
       <c r="D868">
-        <v>2560.730172863126</v>
+        <v>2853.2695601376477</v>
       </c>
     </row>
     <row r="869">
@@ -12643,7 +12643,7 @@
         <v>pending</v>
       </c>
       <c r="D869">
-        <v>367.8660043362114</v>
+        <v>2989.896677404965</v>
       </c>
     </row>
     <row r="870">
@@ -12657,7 +12657,7 @@
         <v>approved</v>
       </c>
       <c r="D870">
-        <v>1064.539345178177</v>
+        <v>4166.738908581407</v>
       </c>
     </row>
     <row r="871">
@@ -12671,7 +12671,7 @@
         <v>pending</v>
       </c>
       <c r="D871">
-        <v>2533.581047142851</v>
+        <v>3338.1890660621884</v>
       </c>
     </row>
     <row r="872">
@@ -12685,7 +12685,7 @@
         <v>approved</v>
       </c>
       <c r="D872">
-        <v>3649.6001805548285</v>
+        <v>887.7505800033392</v>
       </c>
     </row>
     <row r="873">
@@ -12699,7 +12699,7 @@
         <v>pending</v>
       </c>
       <c r="D873">
-        <v>442.5383680450268</v>
+        <v>2040.7247168423992</v>
       </c>
     </row>
     <row r="874">
@@ -12713,7 +12713,7 @@
         <v>approved</v>
       </c>
       <c r="D874">
-        <v>4712.55622160494</v>
+        <v>2898.1428254101706</v>
       </c>
     </row>
     <row r="875">
@@ -12727,7 +12727,7 @@
         <v>pending</v>
       </c>
       <c r="D875">
-        <v>1309.6550966793209</v>
+        <v>1169.184315389339</v>
       </c>
     </row>
     <row r="876">
@@ -12741,7 +12741,7 @@
         <v>approved</v>
       </c>
       <c r="D876">
-        <v>1.0502516808230666</v>
+        <v>3529.2834673363336</v>
       </c>
     </row>
     <row r="877">
@@ -12755,7 +12755,7 @@
         <v>pending</v>
       </c>
       <c r="D877">
-        <v>4366.471569749231</v>
+        <v>3074.0029039989736</v>
       </c>
     </row>
     <row r="878">
@@ -12769,7 +12769,7 @@
         <v>approved</v>
       </c>
       <c r="D878">
-        <v>3128.3536546689684</v>
+        <v>1281.2497749842123</v>
       </c>
     </row>
     <row r="879">
@@ -12783,7 +12783,7 @@
         <v>pending</v>
       </c>
       <c r="D879">
-        <v>4816.436490819004</v>
+        <v>4762.022085675947</v>
       </c>
     </row>
     <row r="880">
@@ -12797,7 +12797,7 @@
         <v>approved</v>
       </c>
       <c r="D880">
-        <v>1726.0998832576945</v>
+        <v>2628.1465328669296</v>
       </c>
     </row>
     <row r="881">
@@ -12811,7 +12811,7 @@
         <v>pending</v>
       </c>
       <c r="D881">
-        <v>3441.4363624309754</v>
+        <v>1092.0669201610433</v>
       </c>
     </row>
     <row r="882">
@@ -12825,7 +12825,7 @@
         <v>approved</v>
       </c>
       <c r="D882">
-        <v>3185.12457255262</v>
+        <v>1056.226807287478</v>
       </c>
     </row>
     <row r="883">
@@ -12839,7 +12839,7 @@
         <v>pending</v>
       </c>
       <c r="D883">
-        <v>4462.5890053752555</v>
+        <v>3714.0701707250655</v>
       </c>
     </row>
     <row r="884">
@@ -12853,7 +12853,7 @@
         <v>approved</v>
       </c>
       <c r="D884">
-        <v>50.822659269317285</v>
+        <v>4935.657057301436</v>
       </c>
     </row>
     <row r="885">
@@ -12867,7 +12867,7 @@
         <v>pending</v>
       </c>
       <c r="D885">
-        <v>1220.3251398508862</v>
+        <v>3808.3621868417295</v>
       </c>
     </row>
     <row r="886">
@@ -12881,7 +12881,7 @@
         <v>approved</v>
       </c>
       <c r="D886">
-        <v>2238.6964002929176</v>
+        <v>1222.8447218182826</v>
       </c>
     </row>
     <row r="887">
@@ -12895,7 +12895,7 @@
         <v>pending</v>
       </c>
       <c r="D887">
-        <v>422.91483204387026</v>
+        <v>597.6837197652774</v>
       </c>
     </row>
     <row r="888">
@@ -12909,7 +12909,7 @@
         <v>approved</v>
       </c>
       <c r="D888">
-        <v>4408.75501956202</v>
+        <v>3748.762979905641</v>
       </c>
     </row>
     <row r="889">
@@ -12923,7 +12923,7 @@
         <v>pending</v>
       </c>
       <c r="D889">
-        <v>1464.0955601782557</v>
+        <v>4262.914348407299</v>
       </c>
     </row>
     <row r="890">
@@ -12937,7 +12937,7 @@
         <v>approved</v>
       </c>
       <c r="D890">
-        <v>4778.503998866394</v>
+        <v>524.5760070703586</v>
       </c>
     </row>
     <row r="891">
@@ -12951,7 +12951,7 @@
         <v>pending</v>
       </c>
       <c r="D891">
-        <v>4817.6641970777555</v>
+        <v>3124.1651610983813</v>
       </c>
     </row>
     <row r="892">
@@ -12965,7 +12965,7 @@
         <v>approved</v>
       </c>
       <c r="D892">
-        <v>696.2335893282057</v>
+        <v>2915.4765988213003</v>
       </c>
     </row>
     <row r="893">
@@ -12979,7 +12979,7 @@
         <v>pending</v>
       </c>
       <c r="D893">
-        <v>61.22162141430243</v>
+        <v>1557.2144208459592</v>
       </c>
     </row>
     <row r="894">
@@ -12993,7 +12993,7 @@
         <v>approved</v>
       </c>
       <c r="D894">
-        <v>1153.0483410655845</v>
+        <v>3724.3869255974373</v>
       </c>
     </row>
     <row r="895">
@@ -13007,7 +13007,7 @@
         <v>pending</v>
       </c>
       <c r="D895">
-        <v>227.39601219512463</v>
+        <v>1064.3260354560402</v>
       </c>
     </row>
     <row r="896">
@@ -13021,7 +13021,7 @@
         <v>approved</v>
       </c>
       <c r="D896">
-        <v>4639.155187578287</v>
+        <v>4582.168092795126</v>
       </c>
     </row>
     <row r="897">
@@ -13035,7 +13035,7 @@
         <v>pending</v>
       </c>
       <c r="D897">
-        <v>110.01341862848291</v>
+        <v>618.5208337983461</v>
       </c>
     </row>
     <row r="898">
@@ -13049,7 +13049,7 @@
         <v>approved</v>
       </c>
       <c r="D898">
-        <v>604.7498966042575</v>
+        <v>912.0111807887243</v>
       </c>
     </row>
     <row r="899">
@@ -13063,7 +13063,7 @@
         <v>pending</v>
       </c>
       <c r="D899">
-        <v>2079.184318746505</v>
+        <v>2158.3827575588552</v>
       </c>
     </row>
     <row r="900">
@@ -13077,7 +13077,7 @@
         <v>approved</v>
       </c>
       <c r="D900">
-        <v>3178.852103330633</v>
+        <v>406.26724482157874</v>
       </c>
     </row>
     <row r="901">
@@ -13091,7 +13091,7 @@
         <v>pending</v>
       </c>
       <c r="D901">
-        <v>2877.3190730537667</v>
+        <v>4197.817250703807</v>
       </c>
     </row>
     <row r="902">
@@ -13105,7 +13105,7 @@
         <v>approved</v>
       </c>
       <c r="D902">
-        <v>275.23115168021417</v>
+        <v>4810.148003519597</v>
       </c>
     </row>
     <row r="903">
@@ -13119,7 +13119,7 @@
         <v>pending</v>
       </c>
       <c r="D903">
-        <v>2546.9995270974377</v>
+        <v>4445.596791842407</v>
       </c>
     </row>
     <row r="904">
@@ -13133,7 +13133,7 @@
         <v>approved</v>
       </c>
       <c r="D904">
-        <v>198.9069728080506</v>
+        <v>4474.528992452663</v>
       </c>
     </row>
     <row r="905">
@@ -13147,7 +13147,7 @@
         <v>pending</v>
       </c>
       <c r="D905">
-        <v>799.9978230774585</v>
+        <v>3679.599004980446</v>
       </c>
     </row>
     <row r="906">
@@ -13161,7 +13161,7 @@
         <v>approved</v>
       </c>
       <c r="D906">
-        <v>4215.598676928734</v>
+        <v>2018.5930983962119</v>
       </c>
     </row>
     <row r="907">
@@ -13175,7 +13175,7 @@
         <v>pending</v>
       </c>
       <c r="D907">
-        <v>3931.0683086498475</v>
+        <v>3995.0216368449755</v>
       </c>
     </row>
     <row r="908">
@@ -13189,7 +13189,7 @@
         <v>approved</v>
       </c>
       <c r="D908">
-        <v>4234.112366927201</v>
+        <v>4321.715511799389</v>
       </c>
     </row>
     <row r="909">
@@ -13203,7 +13203,7 @@
         <v>pending</v>
       </c>
       <c r="D909">
-        <v>642.1757895190949</v>
+        <v>4210.641249916506</v>
       </c>
     </row>
     <row r="910">
@@ -13217,7 +13217,7 @@
         <v>approved</v>
       </c>
       <c r="D910">
-        <v>1486.170711573841</v>
+        <v>3057.6268359144287</v>
       </c>
     </row>
     <row r="911">
@@ -13231,7 +13231,7 @@
         <v>pending</v>
       </c>
       <c r="D911">
-        <v>4428.274366772217</v>
+        <v>808.7577727742635</v>
       </c>
     </row>
     <row r="912">
@@ -13245,7 +13245,7 @@
         <v>approved</v>
       </c>
       <c r="D912">
-        <v>2199.6121811693793</v>
+        <v>3082.2242241577856</v>
       </c>
     </row>
     <row r="913">
@@ -13259,7 +13259,7 @@
         <v>pending</v>
       </c>
       <c r="D913">
-        <v>4474.7724925350685</v>
+        <v>3883.041409792938</v>
       </c>
     </row>
     <row r="914">
@@ -13273,7 +13273,7 @@
         <v>approved</v>
       </c>
       <c r="D914">
-        <v>1332.70312501928</v>
+        <v>475.0384467738478</v>
       </c>
     </row>
     <row r="915">
@@ -13287,7 +13287,7 @@
         <v>pending</v>
       </c>
       <c r="D915">
-        <v>146.22548212594566</v>
+        <v>331.90715682908547</v>
       </c>
     </row>
     <row r="916">
@@ -13301,7 +13301,7 @@
         <v>approved</v>
       </c>
       <c r="D916">
-        <v>4308.069720445944</v>
+        <v>3893.043883134084</v>
       </c>
     </row>
     <row r="917">
@@ -13315,7 +13315,7 @@
         <v>pending</v>
       </c>
       <c r="D917">
-        <v>3337.383533812972</v>
+        <v>4923.455220927255</v>
       </c>
     </row>
     <row r="918">
@@ -13329,7 +13329,7 @@
         <v>approved</v>
       </c>
       <c r="D918">
-        <v>3649.5594973417155</v>
+        <v>1631.9259460916592</v>
       </c>
     </row>
     <row r="919">
@@ -13343,7 +13343,7 @@
         <v>pending</v>
       </c>
       <c r="D919">
-        <v>1663.0460441380224</v>
+        <v>4522.485900854313</v>
       </c>
     </row>
     <row r="920">
@@ -13357,7 +13357,7 @@
         <v>approved</v>
       </c>
       <c r="D920">
-        <v>4783.304992830991</v>
+        <v>767.6670404677333</v>
       </c>
     </row>
     <row r="921">
@@ -13371,7 +13371,7 @@
         <v>pending</v>
       </c>
       <c r="D921">
-        <v>4106.2834579490645</v>
+        <v>4734.397648481011</v>
       </c>
     </row>
     <row r="922">
@@ -13385,7 +13385,7 @@
         <v>approved</v>
       </c>
       <c r="D922">
-        <v>3833.4917337860575</v>
+        <v>927.4631606910366</v>
       </c>
     </row>
     <row r="923">
@@ -13399,7 +13399,7 @@
         <v>pending</v>
       </c>
       <c r="D923">
-        <v>4244.940763282645</v>
+        <v>2314.604920350698</v>
       </c>
     </row>
     <row r="924">
@@ -13413,7 +13413,7 @@
         <v>approved</v>
       </c>
       <c r="D924">
-        <v>3733.1525287503673</v>
+        <v>3103.5809384309864</v>
       </c>
     </row>
     <row r="925">
@@ -13427,7 +13427,7 @@
         <v>pending</v>
       </c>
       <c r="D925">
-        <v>3257.9068856500116</v>
+        <v>4588.652259177862</v>
       </c>
     </row>
     <row r="926">
@@ -13441,7 +13441,7 @@
         <v>approved</v>
       </c>
       <c r="D926">
-        <v>1204.9711597218616</v>
+        <v>1548.819680134904</v>
       </c>
     </row>
     <row r="927">
@@ -13455,7 +13455,7 @@
         <v>pending</v>
       </c>
       <c r="D927">
-        <v>1288.115294993225</v>
+        <v>3726.4806671667307</v>
       </c>
     </row>
     <row r="928">
@@ -13469,7 +13469,7 @@
         <v>approved</v>
       </c>
       <c r="D928">
-        <v>2885.99964115946</v>
+        <v>872.7448367454493</v>
       </c>
     </row>
     <row r="929">
@@ -13483,7 +13483,7 @@
         <v>pending</v>
       </c>
       <c r="D929">
-        <v>3675.782936657993</v>
+        <v>1914.4969814942426</v>
       </c>
     </row>
     <row r="930">
@@ -13497,7 +13497,7 @@
         <v>approved</v>
       </c>
       <c r="D930">
-        <v>2553.463385672271</v>
+        <v>357.3920505620143</v>
       </c>
     </row>
     <row r="931">
@@ -13511,7 +13511,7 @@
         <v>pending</v>
       </c>
       <c r="D931">
-        <v>1905.492765365947</v>
+        <v>452.06511259208384</v>
       </c>
     </row>
     <row r="932">
@@ -13525,7 +13525,7 @@
         <v>approved</v>
       </c>
       <c r="D932">
-        <v>1803.725807502271</v>
+        <v>1557.6984236413805</v>
       </c>
     </row>
     <row r="933">
@@ -13539,7 +13539,7 @@
         <v>pending</v>
       </c>
       <c r="D933">
-        <v>811.7348429543036</v>
+        <v>4820.062327616745</v>
       </c>
     </row>
     <row r="934">
@@ -13553,7 +13553,7 @@
         <v>approved</v>
       </c>
       <c r="D934">
-        <v>2143.0397602592952</v>
+        <v>4170.696391983585</v>
       </c>
     </row>
     <row r="935">
@@ -13567,7 +13567,7 @@
         <v>pending</v>
       </c>
       <c r="D935">
-        <v>267.0546099639115</v>
+        <v>575.4597443328324</v>
       </c>
     </row>
     <row r="936">
@@ -13581,7 +13581,7 @@
         <v>approved</v>
       </c>
       <c r="D936">
-        <v>2970.334272848921</v>
+        <v>2108.744762475311</v>
       </c>
     </row>
     <row r="937">
@@ -13595,7 +13595,7 @@
         <v>pending</v>
       </c>
       <c r="D937">
-        <v>3226.8245158638097</v>
+        <v>2107.910582398146</v>
       </c>
     </row>
     <row r="938">
@@ -13609,7 +13609,7 @@
         <v>approved</v>
       </c>
       <c r="D938">
-        <v>4747.064593673495</v>
+        <v>3901.522028840705</v>
       </c>
     </row>
     <row r="939">
@@ -13623,7 +13623,7 @@
         <v>pending</v>
       </c>
       <c r="D939">
-        <v>2896.4363095847766</v>
+        <v>1104.3492440189596</v>
       </c>
     </row>
     <row r="940">
@@ -13637,7 +13637,7 @@
         <v>approved</v>
       </c>
       <c r="D940">
-        <v>683.4667544475548</v>
+        <v>439.66705396403125</v>
       </c>
     </row>
     <row r="941">
@@ -13651,7 +13651,7 @@
         <v>pending</v>
       </c>
       <c r="D941">
-        <v>787.5641794033728</v>
+        <v>1575.7545797309901</v>
       </c>
     </row>
     <row r="942">
@@ -13665,7 +13665,7 @@
         <v>approved</v>
       </c>
       <c r="D942">
-        <v>2898.705375314257</v>
+        <v>4747.976871426891</v>
       </c>
     </row>
     <row r="943">
@@ -13679,7 +13679,7 @@
         <v>pending</v>
       </c>
       <c r="D943">
-        <v>3079.8453873587873</v>
+        <v>4414.1993644579115</v>
       </c>
     </row>
     <row r="944">
@@ -13693,7 +13693,7 @@
         <v>approved</v>
       </c>
       <c r="D944">
-        <v>2069.43832379016</v>
+        <v>1728.179625669869</v>
       </c>
     </row>
     <row r="945">
@@ -13707,7 +13707,7 @@
         <v>pending</v>
       </c>
       <c r="D945">
-        <v>478.03754974145016</v>
+        <v>56.12475948218565</v>
       </c>
     </row>
     <row r="946">
@@ -13721,7 +13721,7 @@
         <v>approved</v>
       </c>
       <c r="D946">
-        <v>1176.4063260345824</v>
+        <v>1213.7671664913962</v>
       </c>
     </row>
     <row r="947">
@@ -13735,7 +13735,7 @@
         <v>pending</v>
       </c>
       <c r="D947">
-        <v>1972.4829512367103</v>
+        <v>646.5787391106636</v>
       </c>
     </row>
     <row r="948">
@@ -13749,7 +13749,7 @@
         <v>approved</v>
       </c>
       <c r="D948">
-        <v>3078.38664706615</v>
+        <v>3261.6571936613805</v>
       </c>
     </row>
     <row r="949">
@@ -13763,7 +13763,7 @@
         <v>pending</v>
       </c>
       <c r="D949">
-        <v>4161.073072871409</v>
+        <v>1542.9799465846727</v>
       </c>
     </row>
     <row r="950">
@@ -13777,7 +13777,7 @@
         <v>approved</v>
       </c>
       <c r="D950">
-        <v>1141.3183505497416</v>
+        <v>4895.198390269974</v>
       </c>
     </row>
     <row r="951">
@@ -13791,7 +13791,7 @@
         <v>pending</v>
       </c>
       <c r="D951">
-        <v>3127.955978904481</v>
+        <v>465.54662858526166</v>
       </c>
     </row>
     <row r="952">
@@ -13805,7 +13805,7 @@
         <v>approved</v>
       </c>
       <c r="D952">
-        <v>1645.350340880928</v>
+        <v>3039.0569356465558</v>
       </c>
     </row>
     <row r="953">
@@ -13819,7 +13819,7 @@
         <v>pending</v>
       </c>
       <c r="D953">
-        <v>1961.8228459982213</v>
+        <v>3246.561983747468</v>
       </c>
     </row>
     <row r="954">
@@ -13833,7 +13833,7 @@
         <v>approved</v>
       </c>
       <c r="D954">
-        <v>1567.0671324566233</v>
+        <v>102.02719038276298</v>
       </c>
     </row>
     <row r="955">
@@ -13847,7 +13847,7 @@
         <v>pending</v>
       </c>
       <c r="D955">
-        <v>1069.3383275957947</v>
+        <v>3242.69176699835</v>
       </c>
     </row>
     <row r="956">
@@ -13861,7 +13861,7 @@
         <v>approved</v>
       </c>
       <c r="D956">
-        <v>1260.7140244612215</v>
+        <v>4474.48329571178</v>
       </c>
     </row>
     <row r="957">
@@ -13875,7 +13875,7 @@
         <v>pending</v>
       </c>
       <c r="D957">
-        <v>3849.394739032309</v>
+        <v>2190.3682947308066</v>
       </c>
     </row>
     <row r="958">
@@ -13889,7 +13889,7 @@
         <v>approved</v>
       </c>
       <c r="D958">
-        <v>3855.196388832998</v>
+        <v>3920.548776016333</v>
       </c>
     </row>
     <row r="959">
@@ -13903,7 +13903,7 @@
         <v>pending</v>
       </c>
       <c r="D959">
-        <v>3035.8198916202937</v>
+        <v>2530.1332610647196</v>
       </c>
     </row>
     <row r="960">
@@ -13917,7 +13917,7 @@
         <v>approved</v>
       </c>
       <c r="D960">
-        <v>3707.891041030511</v>
+        <v>728.2378814903956</v>
       </c>
     </row>
     <row r="961">
@@ -13931,7 +13931,7 @@
         <v>pending</v>
       </c>
       <c r="D961">
-        <v>2842.6025603910753</v>
+        <v>1180.6348541119128</v>
       </c>
     </row>
     <row r="962">
@@ -13945,7 +13945,7 @@
         <v>approved</v>
       </c>
       <c r="D962">
-        <v>3977.420274080693</v>
+        <v>2266.2534872123397</v>
       </c>
     </row>
     <row r="963">
@@ -13959,7 +13959,7 @@
         <v>pending</v>
       </c>
       <c r="D963">
-        <v>3368.93258226327</v>
+        <v>723.5458061166278</v>
       </c>
     </row>
     <row r="964">
@@ -13973,7 +13973,7 @@
         <v>approved</v>
       </c>
       <c r="D964">
-        <v>4258.012617603931</v>
+        <v>3824.9978861563127</v>
       </c>
     </row>
     <row r="965">
@@ -13987,7 +13987,7 @@
         <v>pending</v>
       </c>
       <c r="D965">
-        <v>4864.700770535624</v>
+        <v>4378.818885732821</v>
       </c>
     </row>
     <row r="966">
@@ -14001,7 +14001,7 @@
         <v>approved</v>
       </c>
       <c r="D966">
-        <v>330.88398137705923</v>
+        <v>2116.111702610527</v>
       </c>
     </row>
     <row r="967">
@@ -14015,7 +14015,7 @@
         <v>pending</v>
       </c>
       <c r="D967">
-        <v>1696.643082506346</v>
+        <v>4481.021410389318</v>
       </c>
     </row>
     <row r="968">
@@ -14029,7 +14029,7 @@
         <v>approved</v>
       </c>
       <c r="D968">
-        <v>1570.8679479146138</v>
+        <v>1990.8582718494183</v>
       </c>
     </row>
     <row r="969">
@@ -14043,7 +14043,7 @@
         <v>pending</v>
       </c>
       <c r="D969">
-        <v>2120.2471345629015</v>
+        <v>4208.654966140342</v>
       </c>
     </row>
     <row r="970">
@@ -14057,7 +14057,7 @@
         <v>approved</v>
       </c>
       <c r="D970">
-        <v>1527.8681806479156</v>
+        <v>556.0843249060565</v>
       </c>
     </row>
     <row r="971">
@@ -14071,7 +14071,7 @@
         <v>pending</v>
       </c>
       <c r="D971">
-        <v>4655.06958981162</v>
+        <v>1909.7701710849124</v>
       </c>
     </row>
     <row r="972">
@@ -14085,7 +14085,7 @@
         <v>approved</v>
       </c>
       <c r="D972">
-        <v>3684.2829659695044</v>
+        <v>55.494605115533616</v>
       </c>
     </row>
     <row r="973">
@@ -14099,7 +14099,7 @@
         <v>pending</v>
       </c>
       <c r="D973">
-        <v>2331.1746997868963</v>
+        <v>2624.024686605889</v>
       </c>
     </row>
     <row r="974">
@@ -14113,7 +14113,7 @@
         <v>approved</v>
       </c>
       <c r="D974">
-        <v>1281.122291529986</v>
+        <v>1487.0070122992995</v>
       </c>
     </row>
     <row r="975">
@@ -14127,7 +14127,7 @@
         <v>pending</v>
       </c>
       <c r="D975">
-        <v>4347.754065731663</v>
+        <v>3682.5480846199666</v>
       </c>
     </row>
     <row r="976">
@@ -14141,7 +14141,7 @@
         <v>approved</v>
       </c>
       <c r="D976">
-        <v>808.0290032715742</v>
+        <v>2443.560691807466</v>
       </c>
     </row>
     <row r="977">
@@ -14155,7 +14155,7 @@
         <v>pending</v>
       </c>
       <c r="D977">
-        <v>4189.560490822723</v>
+        <v>24.818034898523855</v>
       </c>
     </row>
     <row r="978">
@@ -14169,7 +14169,7 @@
         <v>approved</v>
       </c>
       <c r="D978">
-        <v>185.05392281785382</v>
+        <v>154.94375423856786</v>
       </c>
     </row>
     <row r="979">
@@ -14183,7 +14183,7 @@
         <v>pending</v>
       </c>
       <c r="D979">
-        <v>1676.7141458834533</v>
+        <v>1044.6853652620637</v>
       </c>
     </row>
     <row r="980">
@@ -14197,7 +14197,7 @@
         <v>approved</v>
       </c>
       <c r="D980">
-        <v>4230.730245450604</v>
+        <v>909.1425596699277</v>
       </c>
     </row>
     <row r="981">
@@ -14211,7 +14211,7 @@
         <v>pending</v>
       </c>
       <c r="D981">
-        <v>3880.7614426120585</v>
+        <v>2952.736348075884</v>
       </c>
     </row>
     <row r="982">
@@ -14225,7 +14225,7 @@
         <v>approved</v>
       </c>
       <c r="D982">
-        <v>1075.4568344859517</v>
+        <v>4493.507965702058</v>
       </c>
     </row>
     <row r="983">
@@ -14239,7 +14239,7 @@
         <v>pending</v>
       </c>
       <c r="D983">
-        <v>984.7919731188026</v>
+        <v>4538.802265574879</v>
       </c>
     </row>
     <row r="984">
@@ -14253,7 +14253,7 @@
         <v>approved</v>
       </c>
       <c r="D984">
-        <v>1356.4045728099882</v>
+        <v>4794.941535110037</v>
       </c>
     </row>
     <row r="985">
@@ -14267,7 +14267,7 @@
         <v>pending</v>
       </c>
       <c r="D985">
-        <v>4383.889789294588</v>
+        <v>2797.8983955307212</v>
       </c>
     </row>
     <row r="986">
@@ -14281,7 +14281,7 @@
         <v>approved</v>
       </c>
       <c r="D986">
-        <v>4537.519992630462</v>
+        <v>2081.5122507536075</v>
       </c>
     </row>
     <row r="987">
@@ -14295,7 +14295,7 @@
         <v>pending</v>
       </c>
       <c r="D987">
-        <v>2908.3702638874565</v>
+        <v>1730.348312504707</v>
       </c>
     </row>
     <row r="988">
@@ -14309,7 +14309,7 @@
         <v>approved</v>
       </c>
       <c r="D988">
-        <v>601.8855479083774</v>
+        <v>4695.570921495352</v>
       </c>
     </row>
     <row r="989">
@@ -14323,7 +14323,7 @@
         <v>pending</v>
       </c>
       <c r="D989">
-        <v>2083.546446125948</v>
+        <v>3081.774835526716</v>
       </c>
     </row>
     <row r="990">
@@ -14337,7 +14337,7 @@
         <v>approved</v>
       </c>
       <c r="D990">
-        <v>2701.7599301396035</v>
+        <v>1741.1870987289092</v>
       </c>
     </row>
     <row r="991">
@@ -14351,7 +14351,7 @@
         <v>pending</v>
       </c>
       <c r="D991">
-        <v>1686.7939909991858</v>
+        <v>428.7670951172995</v>
       </c>
     </row>
     <row r="992">
@@ -14365,7 +14365,7 @@
         <v>approved</v>
       </c>
       <c r="D992">
-        <v>899.6706877395644</v>
+        <v>3288.343484829511</v>
       </c>
     </row>
     <row r="993">
@@ -14379,7 +14379,7 @@
         <v>pending</v>
       </c>
       <c r="D993">
-        <v>272.9126571301166</v>
+        <v>2186.469925483976</v>
       </c>
     </row>
     <row r="994">
@@ -14393,7 +14393,7 @@
         <v>approved</v>
       </c>
       <c r="D994">
-        <v>985.962789437197</v>
+        <v>2000.7572366622694</v>
       </c>
     </row>
     <row r="995">
@@ -14407,7 +14407,7 @@
         <v>pending</v>
       </c>
       <c r="D995">
-        <v>864.004538731007</v>
+        <v>1167.2724463416396</v>
       </c>
     </row>
     <row r="996">
@@ -14421,7 +14421,7 @@
         <v>approved</v>
       </c>
       <c r="D996">
-        <v>104.37018033908507</v>
+        <v>1170.4763173336808</v>
       </c>
     </row>
     <row r="997">
@@ -14435,7 +14435,7 @@
         <v>pending</v>
       </c>
       <c r="D997">
-        <v>898.5221558182366</v>
+        <v>2484.503088297966</v>
       </c>
     </row>
     <row r="998">
@@ -14449,7 +14449,7 @@
         <v>approved</v>
       </c>
       <c r="D998">
-        <v>24.489262377392905</v>
+        <v>4618.08959177976</v>
       </c>
     </row>
     <row r="999">
@@ -14463,7 +14463,7 @@
         <v>pending</v>
       </c>
       <c r="D999">
-        <v>4666.082117825655</v>
+        <v>1652.6167277674276</v>
       </c>
     </row>
     <row r="1000">
@@ -14477,7 +14477,7 @@
         <v>approved</v>
       </c>
       <c r="D1000">
-        <v>2917.9140803387604</v>
+        <v>4500.727277487826</v>
       </c>
     </row>
     <row r="1001">
@@ -14491,7 +14491,7 @@
         <v>pending</v>
       </c>
       <c r="D1001">
-        <v>4278.170244142665</v>
+        <v>4706.869279175227</v>
       </c>
     </row>
   </sheetData>
